--- a/database/event/3703/event_3703_evp_summary.xlsx
+++ b/database/event/3703/event_3703_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.1378</v>
       </c>
       <c r="D2" t="n">
-        <v>2.815</v>
+        <v>2.7478</v>
       </c>
       <c r="E2" t="n">
         <v>8.0113</v>
@@ -548,7 +548,7 @@
         <v>1.5806</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9714</v>
+        <v>1.9158</v>
       </c>
       <c r="E3" t="n">
         <v>5.923</v>
@@ -594,7 +594,7 @@
         <v>1.5283</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8922</v>
+        <v>1.8377</v>
       </c>
       <c r="E4" t="n">
         <v>5.727</v>
@@ -640,7 +640,7 @@
         <v>1.4517</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7762</v>
+        <v>1.7233</v>
       </c>
       <c r="E5" t="n">
         <v>5.4399</v>
@@ -686,7 +686,7 @@
         <v>1.3657</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6461</v>
+        <v>1.595</v>
       </c>
       <c r="E6" t="n">
         <v>5.1178</v>
@@ -732,7 +732,7 @@
         <v>1.3186</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5748</v>
+        <v>1.5247</v>
       </c>
       <c r="E7" t="n">
         <v>4.9413</v>
@@ -778,7 +778,7 @@
         <v>1.2331</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4453</v>
+        <v>1.397</v>
       </c>
       <c r="E8" t="n">
         <v>4.6208</v>
@@ -824,7 +824,7 @@
         <v>1.1521</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3227</v>
+        <v>1.2761</v>
       </c>
       <c r="E9" t="n">
         <v>4.3172</v>
@@ -870,7 +870,7 @@
         <v>0.9385</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9993</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>3.5168</v>
@@ -916,7 +916,7 @@
         <v>0.9358</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9953</v>
+        <v>0.9532</v>
       </c>
       <c r="E11" t="n">
         <v>3.5069</v>
@@ -962,7 +962,7 @@
         <v>0.9154</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9644</v>
+        <v>0.9228</v>
       </c>
       <c r="E12" t="n">
         <v>3.4304</v>
@@ -1008,7 +1008,7 @@
         <v>0.7267</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6788</v>
+        <v>0.641</v>
       </c>
       <c r="E13" t="n">
         <v>2.7232</v>
@@ -1054,7 +1054,7 @@
         <v>0.5956</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4804</v>
+        <v>0.4454</v>
       </c>
       <c r="E14" t="n">
         <v>2.2321</v>
@@ -1100,7 +1100,7 @@
         <v>0.4289</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2279</v>
+        <v>0.1964</v>
       </c>
       <c r="E15" t="n">
         <v>1.6072</v>
@@ -1146,7 +1146,7 @@
         <v>0.4249</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2219</v>
+        <v>0.1905</v>
       </c>
       <c r="E16" t="n">
         <v>1.5924</v>
@@ -1192,7 +1192,7 @@
         <v>0.3991</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1827</v>
+        <v>0.1519</v>
       </c>
       <c r="E17" t="n">
         <v>1.4954</v>
@@ -1238,7 +1238,7 @@
         <v>0.2909</v>
       </c>
       <c r="D18" t="n">
-        <v>0.019</v>
+        <v>-0.0097</v>
       </c>
       <c r="E18" t="n">
         <v>1.09</v>
@@ -1284,7 +1284,7 @@
         <v>0.2725</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0371</v>
       </c>
       <c r="E19" t="n">
         <v>1.0212</v>
@@ -1330,7 +1330,7 @@
         <v>0.2602</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0275</v>
+        <v>-0.0555</v>
       </c>
       <c r="E20" t="n">
         <v>0.975</v>
@@ -1376,7 +1376,7 @@
         <v>0.2471</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0472</v>
+        <v>-0.075</v>
       </c>
       <c r="E21" t="n">
         <v>0.9261</v>
@@ -1422,7 +1422,7 @@
         <v>0.1026</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2661</v>
+        <v>-0.2908</v>
       </c>
       <c r="E22" t="n">
         <v>0.3843</v>
@@ -1468,7 +1468,7 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2852</v>
+        <v>-0.3096</v>
       </c>
       <c r="E23" t="n">
         <v>0.337</v>
@@ -1514,7 +1514,7 @@
         <v>0.0813</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2984</v>
+        <v>-0.3226</v>
       </c>
       <c r="E24" t="n">
         <v>0.3045</v>
@@ -1560,7 +1560,7 @@
         <v>0.0798</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3005</v>
+        <v>-0.3247</v>
       </c>
       <c r="E25" t="n">
         <v>0.2992</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0038</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4271</v>
+        <v>-0.4496</v>
       </c>
       <c r="E26" t="n">
         <v>-0.0143</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0266</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4616</v>
+        <v>-0.4836</v>
       </c>
       <c r="E27" t="n">
         <v>-0.09950000000000001</v>
@@ -1698,7 +1698,7 @@
         <v>-0.03</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4667</v>
+        <v>-0.4887</v>
       </c>
       <c r="E28" t="n">
         <v>-0.1123</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0339</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4727</v>
+        <v>-0.4946</v>
       </c>
       <c r="E29" t="n">
         <v>-0.1272</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0677</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5239</v>
+        <v>-0.545</v>
       </c>
       <c r="E30" t="n">
         <v>-0.2537</v>
@@ -1836,7 +1836,7 @@
         <v>-0.09909999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5714</v>
+        <v>-0.5918</v>
       </c>
       <c r="E31" t="n">
         <v>-0.3713</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1081</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5851</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="E32" t="n">
         <v>-0.4052</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1256</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6116</v>
+        <v>-0.6315</v>
       </c>
       <c r="E33" t="n">
         <v>-0.4708</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2417</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7872</v>
+        <v>-0.8047</v>
       </c>
       <c r="E34" t="n">
         <v>-0.9056</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2693</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.846</v>
       </c>
       <c r="E35" t="n">
         <v>-1.0093</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3244</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9125</v>
+        <v>-0.9282</v>
       </c>
       <c r="E36" t="n">
         <v>-1.2157</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3913</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0137</v>
+        <v>-1.0281</v>
       </c>
       <c r="E37" t="n">
         <v>-1.4663</v>
@@ -2158,7 +2158,7 @@
         <v>-0.5337</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E38" t="n">
         <v>-2</v>
@@ -2204,7 +2204,7 @@
         <v>-0.6627</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4246</v>
+        <v>-1.4333</v>
       </c>
       <c r="E39" t="n">
         <v>-2.4834</v>
@@ -2250,7 +2250,7 @@
         <v>-0.8622</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7266</v>
+        <v>-1.7311</v>
       </c>
       <c r="E40" t="n">
         <v>-3.2309</v>
@@ -2296,7 +2296,7 @@
         <v>-0.8961</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.778</v>
+        <v>-1.7818</v>
       </c>
       <c r="E41" t="n">
         <v>-3.3581</v>

--- a/database/event/3703/event_3703_evp_summary.xlsx
+++ b/database/event/3703/event_3703_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.0113</v>
+        <v>8.1419</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1378</v>
+        <v>2.1727</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7478</v>
+        <v>3.0376</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0113</v>
+        <v>8.1419</v>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.9242</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4513</v>
+        <v>5.2177</v>
       </c>
       <c r="H2" t="n">
-        <v>2.56</v>
+        <v>4.8168</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0749</v>
+        <v>2.5045</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4513</v>
+        <v>5.2177</v>
       </c>
       <c r="K2" t="n">
         <v>132</v>
@@ -529,7 +529,7 @@
         <v>178</v>
       </c>
       <c r="M2" t="n">
-        <v>7.526199999999999</v>
+        <v>7.7222</v>
       </c>
       <c r="N2" t="n">
         <v>310</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.923</v>
+        <v>5.5516</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5806</v>
+        <v>1.4815</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9158</v>
+        <v>1.8683</v>
       </c>
       <c r="E3" t="n">
-        <v>5.923</v>
+        <v>5.5516</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1925</v>
+        <v>2.878</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7305</v>
+        <v>2.6736</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3067</v>
+        <v>4.6541</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4907</v>
+        <v>2.4199</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7305</v>
+        <v>2.6736</v>
       </c>
       <c r="K3" t="n">
         <v>158</v>
@@ -575,7 +575,7 @@
         <v>192</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2212</v>
+        <v>5.093500000000001</v>
       </c>
       <c r="N3" t="n">
         <v>350</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.727</v>
+        <v>5.311</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5283</v>
+        <v>1.4173</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8377</v>
+        <v>1.7596</v>
       </c>
       <c r="E4" t="n">
-        <v>5.727</v>
+        <v>5.311</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8196</v>
+        <v>3.6782</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9074</v>
+        <v>1.6328</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8196</v>
+        <v>7.4734</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2854</v>
+        <v>3.8858</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9074</v>
+        <v>1.6328</v>
       </c>
       <c r="K4" t="n">
         <v>158</v>
@@ -621,7 +621,7 @@
         <v>192</v>
       </c>
       <c r="M4" t="n">
-        <v>5.1928</v>
+        <v>5.5186</v>
       </c>
       <c r="N4" t="n">
         <v>350</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4399</v>
+        <v>5.2719</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4517</v>
+        <v>1.4068</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7233</v>
+        <v>1.742</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4399</v>
+        <v>5.2719</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1131</v>
+        <v>3.0357</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3268</v>
+        <v>2.2362</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1131</v>
+        <v>5.2097</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5233</v>
+        <v>2.7088</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3268</v>
+        <v>2.2362</v>
       </c>
       <c r="K5" t="n">
         <v>132</v>
@@ -667,7 +667,7 @@
         <v>178</v>
       </c>
       <c r="M5" t="n">
-        <v>4.850099999999999</v>
+        <v>4.945</v>
       </c>
       <c r="N5" t="n">
         <v>310</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.1178</v>
+        <v>4.784</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3657</v>
+        <v>1.2766</v>
       </c>
       <c r="D6" t="n">
-        <v>1.595</v>
+        <v>1.5217</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1178</v>
+        <v>4.784</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8962</v>
+        <v>3.3786</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2216</v>
+        <v>1.4054</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8962</v>
+        <v>6.4177</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3475</v>
+        <v>3.3369</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2216</v>
+        <v>1.4054</v>
       </c>
       <c r="K6" t="n">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="L6" t="n">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="M6" t="n">
-        <v>4.569100000000001</v>
+        <v>4.7423</v>
       </c>
       <c r="N6" t="n">
-        <v>350</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.9413</v>
+        <v>4.6796</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3186</v>
+        <v>1.2488</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5247</v>
+        <v>1.4746</v>
       </c>
       <c r="E7" t="n">
-        <v>4.9413</v>
+        <v>4.6796</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6808</v>
+        <v>3.0012</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2605</v>
+        <v>1.6784</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6808</v>
+        <v>5.0879</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9834</v>
+        <v>2.6455</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2605</v>
+        <v>1.6784</v>
       </c>
       <c r="K7" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="L7" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2439</v>
+        <v>4.3239</v>
       </c>
       <c r="N7" t="n">
-        <v>310</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.6208</v>
+        <v>4.4712</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2331</v>
+        <v>1.1932</v>
       </c>
       <c r="D8" t="n">
-        <v>1.397</v>
+        <v>1.3805</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6208</v>
+        <v>4.4712</v>
       </c>
       <c r="F8" t="n">
-        <v>4.292</v>
+        <v>3.8621</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3288</v>
+        <v>0.6091</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7072</v>
+        <v>8.1213</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8153</v>
+        <v>4.2227</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3288</v>
+        <v>0.6091</v>
       </c>
       <c r="K8" t="n">
         <v>132</v>
@@ -805,7 +805,7 @@
         <v>178</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1441</v>
+        <v>4.831799999999999</v>
       </c>
       <c r="N8" t="n">
         <v>310</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3172</v>
+        <v>4.0867</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1521</v>
+        <v>1.0905</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2761</v>
+        <v>1.2069</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3172</v>
+        <v>4.0867</v>
       </c>
       <c r="F9" t="n">
-        <v>4.3635</v>
+        <v>2.7583</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0463</v>
+        <v>1.3284</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9949</v>
+        <v>4.2323</v>
       </c>
       <c r="I9" t="n">
-        <v>4.0485</v>
+        <v>2.2006</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0463</v>
+        <v>1.3284</v>
       </c>
       <c r="K9" t="n">
-        <v>205</v>
+        <v>132</v>
       </c>
       <c r="L9" t="n">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="M9" t="n">
-        <v>4.0022</v>
+        <v>3.529</v>
       </c>
       <c r="N9" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5168</v>
+        <v>3.7781</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9385</v>
+        <v>1.0082</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9572000000000001</v>
+        <v>1.0676</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5168</v>
+        <v>3.7781</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5168</v>
+        <v>3.73</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.0481</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5168</v>
+        <v>7.6559</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5168</v>
+        <v>3.9807</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.0481</v>
       </c>
       <c r="K10" t="n">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5168</v>
+        <v>4.0288</v>
       </c>
       <c r="N10" t="n">
-        <v>177</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5069</v>
+        <v>3.3561</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9358</v>
+        <v>0.8956</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9532</v>
+        <v>0.8771</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5069</v>
+        <v>3.3561</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4371</v>
+        <v>3.3561</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0698</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4371</v>
+        <v>4.0097</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9753</v>
+        <v>4.0097</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0698</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="L11" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0451</v>
+        <v>4.0097</v>
       </c>
       <c r="N11" t="n">
-        <v>310</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4304</v>
+        <v>3.2159</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9154</v>
+        <v>0.8582</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9228</v>
+        <v>0.8138</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4304</v>
+        <v>3.2159</v>
       </c>
       <c r="F12" t="n">
-        <v>4.2868</v>
+        <v>3.8588</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-0.6429</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6865</v>
+        <v>8.1096</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7985</v>
+        <v>4.2166</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-0.6429</v>
       </c>
       <c r="K12" t="n">
         <v>206</v>
@@ -989,7 +989,7 @@
         <v>41</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9421</v>
+        <v>3.5737</v>
       </c>
       <c r="N12" t="n">
         <v>247</v>
@@ -998,173 +998,173 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7232</v>
+        <v>3.1144</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7267</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.641</v>
+        <v>0.768</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7232</v>
+        <v>3.1144</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2439</v>
+        <v>2.5475</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5207000000000001</v>
+        <v>0.5669</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2439</v>
+        <v>3.4893</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6293</v>
+        <v>1.8143</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5207000000000001</v>
+        <v>0.5669</v>
       </c>
       <c r="K13" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L13" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1086</v>
+        <v>2.3812</v>
       </c>
       <c r="N13" t="n">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2321</v>
+        <v>2.835</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5956</v>
+        <v>0.7565</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4454</v>
+        <v>0.6418</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2321</v>
+        <v>2.835</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6839</v>
+        <v>1.513</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5482</v>
+        <v>1.322</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6839</v>
+        <v>1.513</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3649</v>
+        <v>0.7867</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5482</v>
+        <v>1.322</v>
       </c>
       <c r="K14" t="n">
-        <v>205</v>
+        <v>158</v>
       </c>
       <c r="L14" t="n">
-        <v>55</v>
+        <v>192</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9131</v>
+        <v>2.1087</v>
       </c>
       <c r="N14" t="n">
-        <v>260</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6072</v>
+        <v>2.7799</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4289</v>
+        <v>0.7418</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1964</v>
+        <v>0.617</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6072</v>
+        <v>2.7799</v>
       </c>
       <c r="F15" t="n">
-        <v>1.72</v>
+        <v>3.2267</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1128</v>
+        <v>-0.4468</v>
       </c>
       <c r="H15" t="n">
-        <v>1.72</v>
+        <v>5.8826</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3941</v>
+        <v>3.0587</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1128</v>
+        <v>-0.4468</v>
       </c>
       <c r="K15" t="n">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="L15" t="n">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2813</v>
+        <v>2.6119</v>
       </c>
       <c r="N15" t="n">
-        <v>350</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5924</v>
+        <v>2.2705</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4249</v>
+        <v>0.6059</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1905</v>
+        <v>0.387</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5924</v>
+        <v>2.2705</v>
       </c>
       <c r="F16" t="n">
-        <v>0.418</v>
+        <v>2.4345</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1744</v>
+        <v>-0.164</v>
       </c>
       <c r="H16" t="n">
-        <v>0.418</v>
+        <v>3.0914</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3388</v>
+        <v>1.6074</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1744</v>
+        <v>-0.164</v>
       </c>
       <c r="K16" t="n">
         <v>158</v>
@@ -1173,7 +1173,7 @@
         <v>192</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5132</v>
+        <v>1.4434</v>
       </c>
       <c r="N16" t="n">
         <v>350</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4954</v>
+        <v>2.1031</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3991</v>
+        <v>0.5612</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1519</v>
+        <v>0.3114</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4954</v>
+        <v>2.1031</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4954</v>
+        <v>2.1031</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4954</v>
+        <v>2.1031</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4954</v>
+        <v>2.1031</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4954</v>
+        <v>2.1031</v>
       </c>
       <c r="N17" t="n">
         <v>141</v>
@@ -1228,170 +1228,170 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.09</v>
+        <v>1.9845</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2909</v>
+        <v>0.5296</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0097</v>
+        <v>0.2579</v>
       </c>
       <c r="E18" t="n">
-        <v>1.09</v>
+        <v>1.9845</v>
       </c>
       <c r="F18" t="n">
-        <v>1.09</v>
+        <v>2.1791</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.1946</v>
       </c>
       <c r="H18" t="n">
-        <v>1.09</v>
+        <v>2.1913</v>
       </c>
       <c r="I18" t="n">
-        <v>1.09</v>
+        <v>1.1394</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.1946</v>
       </c>
       <c r="K18" t="n">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>0.9448</v>
       </c>
       <c r="N18" t="n">
-        <v>192</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0212</v>
+        <v>1.7624</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2725</v>
+        <v>0.4703</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0371</v>
+        <v>0.1576</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0212</v>
+        <v>1.7624</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0212</v>
+        <v>1.7624</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0212</v>
+        <v>1.7624</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0212</v>
+        <v>1.7624</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0212</v>
+        <v>1.7624</v>
       </c>
       <c r="N19" t="n">
-        <v>141</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.975</v>
+        <v>1.4948</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2602</v>
+        <v>0.3989</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0555</v>
+        <v>0.0368</v>
       </c>
       <c r="E20" t="n">
-        <v>0.975</v>
+        <v>1.4948</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2926</v>
+        <v>1.4948</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3176</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2926</v>
+        <v>1.4948</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0477</v>
+        <v>1.4948</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3176</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>205</v>
+        <v>141</v>
       </c>
       <c r="L20" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7301000000000001</v>
+        <v>1.4948</v>
       </c>
       <c r="N20" t="n">
-        <v>260</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9261</v>
+        <v>1.4769</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2471</v>
+        <v>0.3941</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.075</v>
+        <v>0.0287</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9261</v>
+        <v>1.4769</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9261</v>
+        <v>1.4769</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9261</v>
+        <v>1.4769</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9261</v>
+        <v>1.4769</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9261</v>
+        <v>1.4769</v>
       </c>
       <c r="N21" t="n">
         <v>177</v>
@@ -1412,277 +1412,277 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3843</v>
+        <v>1.3127</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1026</v>
+        <v>0.3503</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2908</v>
+        <v>-0.0454</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3843</v>
+        <v>1.3127</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3843</v>
+        <v>1.3127</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3843</v>
+        <v>1.3127</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3843</v>
+        <v>1.3127</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3843</v>
+        <v>1.3127</v>
       </c>
       <c r="N22" t="n">
-        <v>129</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.337</v>
+        <v>0.9608</v>
       </c>
       <c r="C23" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.2564</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3096</v>
+        <v>-0.2043</v>
       </c>
       <c r="E23" t="n">
-        <v>0.337</v>
+        <v>0.9608</v>
       </c>
       <c r="F23" t="n">
-        <v>0.337</v>
+        <v>1.7403</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.7795</v>
       </c>
       <c r="H23" t="n">
-        <v>0.337</v>
+        <v>1.7403</v>
       </c>
       <c r="I23" t="n">
-        <v>0.337</v>
+        <v>0.9049</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.7795</v>
       </c>
       <c r="K23" t="n">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M23" t="n">
-        <v>0.337</v>
+        <v>0.1254000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>177</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3045</v>
+        <v>0.7308</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0813</v>
+        <v>0.195</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3226</v>
+        <v>-0.3081</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3045</v>
+        <v>0.7308</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3045</v>
+        <v>0.7308</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3045</v>
+        <v>0.7308</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3045</v>
+        <v>0.7308</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3045</v>
+        <v>0.7308</v>
       </c>
       <c r="N24" t="n">
-        <v>141</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2992</v>
+        <v>0.6733</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0798</v>
+        <v>0.1797</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3247</v>
+        <v>-0.3341</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2992</v>
+        <v>0.6733</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2992</v>
+        <v>0.6733</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2992</v>
+        <v>0.6733</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2992</v>
+        <v>0.6733</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2992</v>
+        <v>0.6733</v>
       </c>
       <c r="N25" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0143</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0038</v>
+        <v>0.165</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4496</v>
+        <v>-0.3588</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0143</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0143</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0143</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0143</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0143</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>192</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.5891</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0266</v>
+        <v>0.1572</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4836</v>
+        <v>-0.3721</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.5891</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.5891</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.5891</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.5891</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.5891</v>
       </c>
       <c r="N27" t="n">
-        <v>177</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1123</v>
+        <v>0.3358</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.03</v>
+        <v>0.0896</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4887</v>
+        <v>-0.4864</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1123</v>
+        <v>0.3358</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1123</v>
+        <v>0.3358</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1123</v>
+        <v>0.3358</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1123</v>
+        <v>0.3358</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1123</v>
+        <v>0.3358</v>
       </c>
       <c r="N28" t="n">
         <v>192</v>
@@ -1734,124 +1734,124 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1272</v>
+        <v>0.2426</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0339</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4946</v>
+        <v>-0.5285</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1272</v>
+        <v>0.2426</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1272</v>
+        <v>1.0399</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.7973</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1272</v>
+        <v>1.0399</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1272</v>
+        <v>0.5407</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.7973</v>
       </c>
       <c r="K29" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1272</v>
+        <v>-0.2566000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>192</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2537</v>
+        <v>0.2307</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0677</v>
+        <v>0.0616</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.545</v>
+        <v>-0.5339</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2537</v>
+        <v>0.2307</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2537</v>
+        <v>0.2307</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2537</v>
+        <v>0.2307</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2537</v>
+        <v>0.2307</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2537</v>
+        <v>0.2307</v>
       </c>
       <c r="N30" t="n">
-        <v>129</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3713</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.024</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5918</v>
+        <v>-0.5974</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3713</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3713</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3713</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3713</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3713</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>177</v>
@@ -1872,231 +1872,231 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4052</v>
+        <v>0.0834</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1081</v>
+        <v>0.0223</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.6004</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4052</v>
+        <v>0.0834</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5948</v>
+        <v>0.0834</v>
       </c>
       <c r="G32" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5948</v>
+        <v>0.0834</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4821</v>
+        <v>0.0834</v>
       </c>
       <c r="J32" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>206</v>
+        <v>129</v>
       </c>
       <c r="L32" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5179</v>
+        <v>0.0834</v>
       </c>
       <c r="N32" t="n">
-        <v>247</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4708</v>
+        <v>0.0498</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1256</v>
+        <v>0.0133</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6315</v>
+        <v>-0.6155</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4708</v>
+        <v>0.0498</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4708</v>
+        <v>0.0498</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4708</v>
+        <v>0.0498</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4708</v>
+        <v>0.0498</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4708</v>
+        <v>0.0498</v>
       </c>
       <c r="N33" t="n">
-        <v>129</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9056</v>
+        <v>-0.1978</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2417</v>
+        <v>-0.0528</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8047</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9056</v>
+        <v>-0.1978</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0944</v>
+        <v>-0.1978</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0944</v>
+        <v>-0.1978</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0765</v>
+        <v>-0.1978</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>206</v>
+        <v>129</v>
       </c>
       <c r="L34" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9235</v>
+        <v>-0.1978</v>
       </c>
       <c r="N34" t="n">
-        <v>247</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0093</v>
+        <v>-0.4588</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2693</v>
+        <v>-0.1224</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.846</v>
+        <v>-0.8451</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0093</v>
+        <v>-0.4588</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0093</v>
+        <v>0.5412</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0093</v>
+        <v>0.5412</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0093</v>
+        <v>0.2814</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K35" t="n">
-        <v>129</v>
+        <v>206</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0093</v>
+        <v>-0.7186</v>
       </c>
       <c r="N35" t="n">
-        <v>129</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2157</v>
+        <v>-0.9093</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3244</v>
+        <v>-0.2426</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9282</v>
+        <v>-1.0485</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2157</v>
+        <v>-0.9093</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2157</v>
+        <v>-0.9093</v>
       </c>
       <c r="G36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2157</v>
+        <v>-0.9093</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1748</v>
+        <v>-0.9093</v>
       </c>
       <c r="J36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>206</v>
+        <v>129</v>
       </c>
       <c r="L36" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1748</v>
+        <v>-0.9093</v>
       </c>
       <c r="N36" t="n">
-        <v>247</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4663</v>
+        <v>-1.0405</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3913</v>
+        <v>-0.2777</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0281</v>
+        <v>-1.1077</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4663</v>
+        <v>-1.0405</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4663</v>
+        <v>-1.0405</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4663</v>
+        <v>-1.0405</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.4663</v>
+        <v>-1.0405</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4663</v>
+        <v>-1.0405</v>
       </c>
       <c r="N37" t="n">
         <v>141</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2</v>
+        <v>-1.3674</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5337</v>
+        <v>-0.3649</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2407</v>
+        <v>-1.2553</v>
       </c>
       <c r="E38" t="n">
-        <v>-2</v>
+        <v>-1.3674</v>
       </c>
       <c r="F38" t="n">
-        <v>-2</v>
+        <v>-1.3674</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-2</v>
+        <v>-1.3674</v>
       </c>
       <c r="I38" t="n">
-        <v>-2</v>
+        <v>-1.3674</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-2</v>
+        <v>-1.3674</v>
       </c>
       <c r="N38" t="n">
         <v>129</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.4834</v>
+        <v>-2.0589</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6627</v>
+        <v>-0.5494</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4333</v>
+        <v>-1.5675</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.4834</v>
+        <v>-2.0589</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5981</v>
+        <v>-1.4796</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.8853</v>
+        <v>-0.5793</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5981</v>
+        <v>-1.4796</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2953</v>
+        <v>-0.7693</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8853</v>
+        <v>-0.5793</v>
       </c>
       <c r="K39" t="n">
         <v>205</v>
@@ -2231,7 +2231,7 @@
         <v>55</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.1806</v>
+        <v>-1.3486</v>
       </c>
       <c r="N39" t="n">
         <v>260</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.2309</v>
+        <v>-2.3467</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8622</v>
+        <v>-0.6262</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7311</v>
+        <v>-1.6974</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.2309</v>
+        <v>-2.3467</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.2309</v>
+        <v>-2.3467</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.2309</v>
+        <v>-2.3467</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.2309</v>
+        <v>-2.3467</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.2309</v>
+        <v>-2.3467</v>
       </c>
       <c r="N40" t="n">
         <v>192</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.3581</v>
+        <v>-4.0525</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8961</v>
+        <v>-1.0814</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7818</v>
+        <v>-2.4675</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.3581</v>
+        <v>-4.0525</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.3581</v>
+        <v>-3.2934</v>
       </c>
       <c r="G41" t="n">
-        <v>-1</v>
+        <v>-0.7591</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.3581</v>
+        <v>-3.2934</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9113</v>
+        <v>-1.7124</v>
       </c>
       <c r="J41" t="n">
-        <v>-1</v>
+        <v>-0.7591</v>
       </c>
       <c r="K41" t="n">
         <v>205</v>
@@ -2323,7 +2323,7 @@
         <v>55</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.9113</v>
+        <v>-2.4715</v>
       </c>
       <c r="N41" t="n">
         <v>260</v>
@@ -2429,10 +2429,10 @@
         <v>1.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8966</v>
+        <v>0.9019</v>
       </c>
       <c r="J2" t="n">
-        <v>25.1048</v>
+        <v>25.2532</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8966</v>
+        <v>0.9019</v>
       </c>
       <c r="J3" t="n">
-        <v>25.1048</v>
+        <v>25.2532</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6569</v>
+        <v>0.6737</v>
       </c>
       <c r="J4" t="n">
-        <v>18.3932</v>
+        <v>18.8636</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5053</v>
+        <v>0.5578</v>
       </c>
       <c r="J5" t="n">
-        <v>14.1484</v>
+        <v>15.6184</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3656</v>
+        <v>-0.2872</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.2368</v>
+        <v>-8.041600000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.43</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7331</v>
+        <v>0.9164</v>
       </c>
       <c r="J7" t="n">
-        <v>20.5268</v>
+        <v>25.6592</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0747</v>
+        <v>-0.0738</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0916</v>
+        <v>-2.0664</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.7</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4888</v>
+        <v>-0.3189</v>
       </c>
       <c r="J9" t="n">
-        <v>-13.6864</v>
+        <v>-8.9292</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.66</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5433</v>
+        <v>-0.3568</v>
       </c>
       <c r="J10" t="n">
-        <v>-15.2124</v>
+        <v>-9.990399999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.57</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6594</v>
+        <v>-0.4407</v>
       </c>
       <c r="J11" t="n">
-        <v>-18.4632</v>
+        <v>-12.3396</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2058</v>
+        <v>0.152</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7334</v>
+        <v>3.496</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0291</v>
+        <v>-0.0059</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6693</v>
+        <v>-0.1357</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.86</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2441</v>
+        <v>-0.1634</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.6143</v>
+        <v>-3.7582</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2627</v>
+        <v>-0.1735</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.0421</v>
+        <v>-3.9905</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6117</v>
+        <v>-0.4055</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.0691</v>
+        <v>-9.326499999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.94</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1559</v>
+        <v>1.0452</v>
       </c>
       <c r="J17" t="n">
-        <v>26.5857</v>
+        <v>24.0396</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.45</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6365</v>
+        <v>0.5638</v>
       </c>
       <c r="J18" t="n">
-        <v>14.6395</v>
+        <v>12.9674</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0229</v>
+        <v>0.0567</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5266999999999999</v>
+        <v>1.3041</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1336</v>
+        <v>-0.0582</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.0728</v>
+        <v>-1.3386</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.72</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5271</v>
+        <v>-0.3392</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.1233</v>
+        <v>-7.8016</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.47</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7251</v>
+        <v>0.6874</v>
       </c>
       <c r="J22" t="n">
-        <v>18.8526</v>
+        <v>17.8724</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.99</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0474</v>
+        <v>-0.0215</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2324</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0741</v>
+        <v>-0.037</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9266</v>
+        <v>-0.962</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1597</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.1522</v>
+        <v>-2.3244</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.68</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5482</v>
+        <v>-0.3564</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.2532</v>
+        <v>-9.266400000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.44</v>
       </c>
       <c r="I27" t="n">
-        <v>0.68</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>17.68</v>
+        <v>15.4778</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3245</v>
+        <v>0.2643</v>
       </c>
       <c r="J28" t="n">
-        <v>8.436999999999999</v>
+        <v>6.8718</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.12</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2452</v>
+        <v>0.1968</v>
       </c>
       <c r="J29" t="n">
-        <v>6.3752</v>
+        <v>5.1168</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.03</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0612</v>
+        <v>0.0616</v>
       </c>
       <c r="J30" t="n">
-        <v>1.5912</v>
+        <v>1.6016</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.45</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8244</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>-21.4344</v>
+        <v>-14.742</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6844</v>
+        <v>0.6291</v>
       </c>
       <c r="J32" t="n">
-        <v>24.6384</v>
+        <v>22.6476</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3505</v>
+        <v>0.2854</v>
       </c>
       <c r="J33" t="n">
-        <v>12.618</v>
+        <v>10.2744</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3183</v>
+        <v>0.2536</v>
       </c>
       <c r="J34" t="n">
-        <v>11.4588</v>
+        <v>9.1296</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.67</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9505</v>
+        <v>-0.9267</v>
       </c>
       <c r="J35" t="n">
-        <v>-34.218</v>
+        <v>-33.3612</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.67</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9505</v>
+        <v>-0.9267</v>
       </c>
       <c r="J36" t="n">
-        <v>-34.218</v>
+        <v>-33.3612</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.53</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7575</v>
+        <v>0.9436</v>
       </c>
       <c r="J37" t="n">
-        <v>27.27</v>
+        <v>33.9696</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.18</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3076</v>
+        <v>0.3709</v>
       </c>
       <c r="J38" t="n">
-        <v>11.0736</v>
+        <v>13.3524</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.08</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1244</v>
+        <v>0.1848</v>
       </c>
       <c r="J39" t="n">
-        <v>4.4784</v>
+        <v>6.6528</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1737</v>
+        <v>-0.0892</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.2532</v>
+        <v>-3.2112</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2602</v>
+        <v>-0.1481</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.3672</v>
+        <v>-5.3316</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.65</v>
       </c>
       <c r="I42" t="n">
-        <v>1.4904</v>
+        <v>1.3181</v>
       </c>
       <c r="J42" t="n">
-        <v>35.7696</v>
+        <v>31.6344</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.45</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0985</v>
+        <v>1.0675</v>
       </c>
       <c r="J43" t="n">
-        <v>26.364</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.33</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8363</v>
+        <v>0.85</v>
       </c>
       <c r="J44" t="n">
-        <v>20.0712</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.98</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2383</v>
+        <v>-0.1556</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.7192</v>
+        <v>-3.7344</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7165</v>
+        <v>-0.6594</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.196</v>
+        <v>-15.8256</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.22</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4375</v>
+        <v>0.5023</v>
       </c>
       <c r="J47" t="n">
-        <v>10.5</v>
+        <v>12.0552</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.06</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1845</v>
+        <v>0.1803</v>
       </c>
       <c r="J48" t="n">
-        <v>4.428</v>
+        <v>4.3272</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1653</v>
+        <v>0.1572</v>
       </c>
       <c r="J49" t="n">
-        <v>3.9672</v>
+        <v>3.7728</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.82</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3342</v>
+        <v>-0.2102</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.020799999999999</v>
+        <v>-5.0448</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.49</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.5214</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.3984</v>
+        <v>-12.5136</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.84</v>
       </c>
       <c r="I52" t="n">
-        <v>1.7268</v>
+        <v>1.2208</v>
       </c>
       <c r="J52" t="n">
-        <v>37.9896</v>
+        <v>26.8576</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.6</v>
       </c>
       <c r="I53" t="n">
-        <v>1.3027</v>
+        <v>0.9429</v>
       </c>
       <c r="J53" t="n">
-        <v>28.6594</v>
+        <v>20.7438</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.44</v>
       </c>
       <c r="I54" t="n">
-        <v>0.9486</v>
+        <v>0.754</v>
       </c>
       <c r="J54" t="n">
-        <v>20.8692</v>
+        <v>16.588</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.26</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5401</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>11.8822</v>
+        <v>11.4994</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.1</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1507</v>
+        <v>0.2465</v>
       </c>
       <c r="J56" t="n">
-        <v>3.3154</v>
+        <v>5.423</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.91</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0588</v>
+        <v>-0.0767</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.2936</v>
+        <v>-1.6874</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.79</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2576</v>
+        <v>-0.2114</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.6672</v>
+        <v>-4.6508</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.67</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4721</v>
+        <v>-0.3248</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.3862</v>
+        <v>-7.1456</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4882</v>
+        <v>-0.3341</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.7404</v>
+        <v>-7.3502</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.49</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.726</v>
+        <v>-0.4927</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.972</v>
+        <v>-10.8394</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.23</v>
       </c>
       <c r="I62" t="n">
-        <v>2.058</v>
+        <v>1.6221</v>
       </c>
       <c r="J62" t="n">
-        <v>39.102</v>
+        <v>30.8199</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.8</v>
       </c>
       <c r="I63" t="n">
-        <v>1.6208</v>
+        <v>1.1528</v>
       </c>
       <c r="J63" t="n">
-        <v>30.7952</v>
+        <v>21.9032</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.33</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6532</v>
+        <v>0.602</v>
       </c>
       <c r="J64" t="n">
-        <v>12.4108</v>
+        <v>11.438</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.33</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6532</v>
+        <v>0.602</v>
       </c>
       <c r="J65" t="n">
-        <v>12.4108</v>
+        <v>11.438</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.19</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3441</v>
+        <v>0.4079</v>
       </c>
       <c r="J66" t="n">
-        <v>6.5379</v>
+        <v>7.7501</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.63</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.3843</v>
+        <v>-0.3181</v>
       </c>
       <c r="J67" t="n">
-        <v>-7.3017</v>
+        <v>-6.0439</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.58</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.4619</v>
+        <v>-0.3701</v>
       </c>
       <c r="J68" t="n">
-        <v>-8.7761</v>
+        <v>-7.0319</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.48</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.6495</v>
+        <v>-0.4632</v>
       </c>
       <c r="J69" t="n">
-        <v>-12.3405</v>
+        <v>-8.800800000000001</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.43</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7326</v>
+        <v>-0.5098</v>
       </c>
       <c r="J70" t="n">
-        <v>-13.9194</v>
+        <v>-9.686199999999999</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.37</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.821</v>
+        <v>-0.5681</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.599</v>
+        <v>-10.7939</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.79</v>
       </c>
       <c r="I72" t="n">
-        <v>1.7538</v>
+        <v>1.242</v>
       </c>
       <c r="J72" t="n">
-        <v>49.1064</v>
+        <v>34.776</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8811</v>
+        <v>0.652</v>
       </c>
       <c r="J73" t="n">
-        <v>24.6708</v>
+        <v>18.256</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4048</v>
+        <v>0.3988</v>
       </c>
       <c r="J74" t="n">
-        <v>11.3344</v>
+        <v>11.1664</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.78</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.768</v>
+        <v>-0.7177</v>
       </c>
       <c r="J75" t="n">
-        <v>-21.504</v>
+        <v>-20.0956</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.77</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7912</v>
+        <v>-0.7431</v>
       </c>
       <c r="J76" t="n">
-        <v>-22.1536</v>
+        <v>-20.8068</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.09</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2483</v>
+        <v>0.2552</v>
       </c>
       <c r="J77" t="n">
-        <v>6.9524</v>
+        <v>7.1456</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2309</v>
+        <v>0.2335</v>
       </c>
       <c r="J78" t="n">
-        <v>6.4652</v>
+        <v>6.538</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.02</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1122</v>
+        <v>0.089</v>
       </c>
       <c r="J79" t="n">
-        <v>3.1416</v>
+        <v>2.492</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.71</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4861</v>
+        <v>-0.3149</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.6108</v>
+        <v>-8.8172</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.61</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6173</v>
+        <v>-0.409</v>
       </c>
       <c r="J81" t="n">
-        <v>-17.2844</v>
+        <v>-11.452</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.61</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4058</v>
+        <v>0.9902</v>
       </c>
       <c r="J82" t="n">
-        <v>37.9566</v>
+        <v>26.7354</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.29</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7261</v>
+        <v>0.5826</v>
       </c>
       <c r="J83" t="n">
-        <v>19.6047</v>
+        <v>15.7302</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.27</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6714</v>
+        <v>0.5564</v>
       </c>
       <c r="J84" t="n">
-        <v>18.1278</v>
+        <v>15.0228</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.25</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6067</v>
+        <v>0.5303</v>
       </c>
       <c r="J85" t="n">
-        <v>16.3809</v>
+        <v>14.3181</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.9</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4939</v>
+        <v>-0.4189</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.3353</v>
+        <v>-11.3103</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3173</v>
+        <v>0.3334</v>
       </c>
       <c r="J87" t="n">
-        <v>8.5671</v>
+        <v>9.001799999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2946</v>
+        <v>-0.2071</v>
       </c>
       <c r="J88" t="n">
-        <v>-7.9542</v>
+        <v>-5.5917</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.75</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3992</v>
+        <v>-0.2644</v>
       </c>
       <c r="J89" t="n">
-        <v>-10.7784</v>
+        <v>-7.1388</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.73</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4298</v>
+        <v>-0.2836</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.6046</v>
+        <v>-7.6572</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.66</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5303</v>
+        <v>-0.3501</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.3181</v>
+        <v>-9.4527</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.31</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8878</v>
+        <v>0.8636</v>
       </c>
       <c r="J92" t="n">
-        <v>31.073</v>
+        <v>30.226</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.3</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8651</v>
+        <v>0.8396</v>
       </c>
       <c r="J93" t="n">
-        <v>30.2785</v>
+        <v>29.386</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0629</v>
+        <v>-0.0152</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.2015</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.99</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1233</v>
+        <v>-0.0699</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.3155</v>
+        <v>-2.4465</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.75</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.7692</v>
       </c>
       <c r="J96" t="n">
-        <v>-28.42</v>
+        <v>-26.922</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.22</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3997</v>
+        <v>0.4639</v>
       </c>
       <c r="J97" t="n">
-        <v>13.9895</v>
+        <v>16.2365</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2135</v>
+        <v>0.2382</v>
       </c>
       <c r="J98" t="n">
-        <v>7.4725</v>
+        <v>8.337</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1958</v>
+        <v>0.218</v>
       </c>
       <c r="J99" t="n">
-        <v>6.853</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.08</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1774</v>
+        <v>0.1974</v>
       </c>
       <c r="J100" t="n">
-        <v>6.209</v>
+        <v>6.909</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5393</v>
+        <v>-0.3496</v>
       </c>
       <c r="J101" t="n">
-        <v>-18.8755</v>
+        <v>-12.236</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.46</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1905</v>
+        <v>1.1153</v>
       </c>
       <c r="J102" t="n">
-        <v>32.1435</v>
+        <v>30.1131</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8689</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="J103" t="n">
-        <v>23.4603</v>
+        <v>22.9311</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0606</v>
+        <v>0.1085</v>
       </c>
       <c r="J104" t="n">
-        <v>1.6362</v>
+        <v>2.9295</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.88</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4994</v>
+        <v>-0.4355</v>
       </c>
       <c r="J105" t="n">
-        <v>-13.4838</v>
+        <v>-11.7585</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.84</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6046</v>
+        <v>-0.5453</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.3242</v>
+        <v>-14.7231</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.61</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8742</v>
+        <v>1.0652</v>
       </c>
       <c r="J107" t="n">
-        <v>23.6034</v>
+        <v>28.7604</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2127</v>
+        <v>0.2378</v>
       </c>
       <c r="J108" t="n">
-        <v>5.7429</v>
+        <v>6.4206</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1765</v>
+        <v>0.1971</v>
       </c>
       <c r="J109" t="n">
-        <v>4.7655</v>
+        <v>5.3217</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.78</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.42</v>
+        <v>-0.2632</v>
       </c>
       <c r="J110" t="n">
-        <v>-11.34</v>
+        <v>-7.1064</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.62</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6269</v>
+        <v>-0.4148</v>
       </c>
       <c r="J111" t="n">
-        <v>-16.9263</v>
+        <v>-11.1996</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6167</v>
+        <v>0.7482</v>
       </c>
       <c r="J112" t="n">
-        <v>16.6509</v>
+        <v>20.2014</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.04</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1076</v>
+        <v>0.1136</v>
       </c>
       <c r="J113" t="n">
-        <v>2.9052</v>
+        <v>3.0672</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1974</v>
+        <v>-0.1132</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.3298</v>
+        <v>-3.0564</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.89</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.249</v>
+        <v>-0.1468</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.723</v>
+        <v>-3.9636</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3279</v>
+        <v>-0.2</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.853300000000001</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.42</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1208</v>
+        <v>1.0688</v>
       </c>
       <c r="J117" t="n">
-        <v>30.2616</v>
+        <v>28.8576</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.25</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7426</v>
+        <v>0.7141</v>
       </c>
       <c r="J118" t="n">
-        <v>20.0502</v>
+        <v>19.2807</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2111</v>
+        <v>-0.1506</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.6997</v>
+        <v>-4.0662</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.89</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4627</v>
+        <v>-0.4005</v>
       </c>
       <c r="J120" t="n">
-        <v>-12.4929</v>
+        <v>-10.8135</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5175</v>
+        <v>-0.4568</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.9725</v>
+        <v>-12.3336</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.35</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5985</v>
+        <v>0.7217</v>
       </c>
       <c r="J122" t="n">
-        <v>17.955</v>
+        <v>21.651</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.99</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0174</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.264</v>
+        <v>-0.522</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.98</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0356</v>
+        <v>-0.033</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.068</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.82</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3433</v>
+        <v>-0.2139</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.299</v>
+        <v>-6.417</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.65</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.577</v>
+        <v>-0.3785</v>
       </c>
       <c r="J126" t="n">
-        <v>-17.31</v>
+        <v>-11.355</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.39</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0414</v>
+        <v>1.015</v>
       </c>
       <c r="J127" t="n">
-        <v>31.242</v>
+        <v>30.45</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.17</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5205</v>
+        <v>0.5044</v>
       </c>
       <c r="J128" t="n">
-        <v>15.615</v>
+        <v>15.132</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.14</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4351</v>
+        <v>0.4271</v>
       </c>
       <c r="J129" t="n">
-        <v>13.053</v>
+        <v>12.813</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0848</v>
+        <v>-0.0255</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.544</v>
+        <v>-0.765</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.85</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5809</v>
+        <v>-0.5199</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.427</v>
+        <v>-15.597</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.13</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4316</v>
+        <v>0.5109</v>
       </c>
       <c r="J132" t="n">
-        <v>9.063599999999999</v>
+        <v>10.7289</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.58</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.578</v>
+        <v>-0.3974</v>
       </c>
       <c r="J133" t="n">
-        <v>-12.138</v>
+        <v>-8.3454</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.52</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.6654</v>
+        <v>-0.4533</v>
       </c>
       <c r="J134" t="n">
-        <v>-13.9734</v>
+        <v>-9.519299999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.5</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.4721</v>
       </c>
       <c r="J135" t="n">
-        <v>-14.553</v>
+        <v>-9.914099999999999</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.46</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7468</v>
+        <v>-0.5098</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.6828</v>
+        <v>-10.7058</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.01</v>
       </c>
       <c r="I137" t="n">
-        <v>1.9662</v>
+        <v>1.6689</v>
       </c>
       <c r="J137" t="n">
-        <v>41.2902</v>
+        <v>35.0469</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.64</v>
       </c>
       <c r="I138" t="n">
-        <v>1.3454</v>
+        <v>1.2528</v>
       </c>
       <c r="J138" t="n">
-        <v>28.2534</v>
+        <v>26.3088</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.55</v>
       </c>
       <c r="I139" t="n">
-        <v>1.1605</v>
+        <v>1.1495</v>
       </c>
       <c r="J139" t="n">
-        <v>24.3705</v>
+        <v>24.1395</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4715</v>
+        <v>0.5916</v>
       </c>
       <c r="J140" t="n">
-        <v>9.9015</v>
+        <v>12.4236</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.18</v>
       </c>
       <c r="I141" t="n">
-        <v>0.3329</v>
+        <v>0.4444</v>
       </c>
       <c r="J141" t="n">
-        <v>6.9909</v>
+        <v>9.3324</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4588</v>
+        <v>0.5317</v>
       </c>
       <c r="J142" t="n">
-        <v>13.3052</v>
+        <v>15.4193</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.1</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2485</v>
+        <v>0.2615</v>
       </c>
       <c r="J143" t="n">
-        <v>7.2065</v>
+        <v>7.5835</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.85</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2929</v>
+        <v>-0.1816</v>
       </c>
       <c r="J144" t="n">
-        <v>-8.4941</v>
+        <v>-5.2664</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3549</v>
+        <v>-0.2225</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.2921</v>
+        <v>-6.4525</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4693</v>
+        <v>-0.3012</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.6097</v>
+        <v>-8.7348</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.49</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2151</v>
+        <v>1.1351</v>
       </c>
       <c r="J147" t="n">
-        <v>35.2379</v>
+        <v>32.9179</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.32</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8529</v>
+        <v>0.8474</v>
       </c>
       <c r="J148" t="n">
-        <v>24.7341</v>
+        <v>24.5746</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.16</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4262</v>
+        <v>0.4674</v>
       </c>
       <c r="J149" t="n">
-        <v>12.3598</v>
+        <v>13.5546</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.05</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0949</v>
+        <v>0.1587</v>
       </c>
       <c r="J150" t="n">
-        <v>2.7521</v>
+        <v>4.6023</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.85</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6006</v>
+        <v>-0.5367</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.4174</v>
+        <v>-15.5643</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.48</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6932</v>
+        <v>0.6121</v>
       </c>
       <c r="J152" t="n">
-        <v>18.7164</v>
+        <v>16.5267</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.26</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4165</v>
+        <v>0.3589</v>
       </c>
       <c r="J153" t="n">
-        <v>11.2455</v>
+        <v>9.690300000000001</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0606</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="J154" t="n">
-        <v>1.6362</v>
+        <v>2.2302</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0599</v>
+        <v>-0.014</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.6173</v>
+        <v>-0.378</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1398</v>
+        <v>-0.0653</v>
       </c>
       <c r="J156" t="n">
-        <v>-3.7746</v>
+        <v>-1.7631</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.13</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3332</v>
+        <v>0.2755</v>
       </c>
       <c r="J157" t="n">
-        <v>8.9964</v>
+        <v>7.4385</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0513</v>
+        <v>-0.0599</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.3851</v>
+        <v>-1.6173</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.8</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3372</v>
+        <v>-0.2209</v>
       </c>
       <c r="J159" t="n">
-        <v>-9.1044</v>
+        <v>-5.9643</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3997</v>
+        <v>-0.2601</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.7919</v>
+        <v>-7.0227</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.62</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5941</v>
+        <v>-0.3933</v>
       </c>
       <c r="J161" t="n">
-        <v>-16.0407</v>
+        <v>-10.6191</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.81</v>
       </c>
       <c r="I162" t="n">
-        <v>1.0831</v>
+        <v>1.2467</v>
       </c>
       <c r="J162" t="n">
-        <v>29.2437</v>
+        <v>33.6609</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.22</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3977</v>
+        <v>0.4622</v>
       </c>
       <c r="J163" t="n">
-        <v>10.7379</v>
+        <v>12.4794</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2886</v>
+        <v>-0.1716</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.7922</v>
+        <v>-4.6332</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.76</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4483</v>
+        <v>-0.2833</v>
       </c>
       <c r="J165" t="n">
-        <v>-12.1041</v>
+        <v>-7.6491</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.55</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7107</v>
+        <v>-0.4786</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.1889</v>
+        <v>-12.9222</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.29</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8287</v>
+        <v>0.8056</v>
       </c>
       <c r="J167" t="n">
-        <v>22.3749</v>
+        <v>21.7512</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.22</v>
       </c>
       <c r="I168" t="n">
-        <v>0.661</v>
+        <v>0.635</v>
       </c>
       <c r="J168" t="n">
-        <v>17.847</v>
+        <v>17.145</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.2</v>
       </c>
       <c r="I169" t="n">
-        <v>0.6103</v>
+        <v>0.585</v>
       </c>
       <c r="J169" t="n">
-        <v>16.4781</v>
+        <v>15.795</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0766</v>
+        <v>-0.0214</v>
       </c>
       <c r="J170" t="n">
-        <v>-2.0682</v>
+        <v>-0.5778</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.76</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7958</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>-21.4866</v>
+        <v>-20.2635</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.11</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3823</v>
+        <v>0.4345</v>
       </c>
       <c r="J172" t="n">
-        <v>8.410600000000001</v>
+        <v>9.558999999999999</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.79</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2396</v>
+        <v>-0.2036</v>
       </c>
       <c r="J173" t="n">
-        <v>-5.2712</v>
+        <v>-4.4792</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.66</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4657</v>
+        <v>-0.3295</v>
       </c>
       <c r="J174" t="n">
-        <v>-10.2454</v>
+        <v>-7.249</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.45</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J175" t="n">
-        <v>-16.9092</v>
+        <v>-11.5434</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.34</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.9048</v>
+        <v>-0.6281</v>
       </c>
       <c r="J176" t="n">
-        <v>-19.9056</v>
+        <v>-13.8182</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.44</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0153</v>
+        <v>1.0336</v>
       </c>
       <c r="J177" t="n">
-        <v>22.3366</v>
+        <v>22.7392</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.43</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9933</v>
+        <v>1.0193</v>
       </c>
       <c r="J178" t="n">
-        <v>21.8526</v>
+        <v>22.4246</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.36</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8168</v>
+        <v>0.893</v>
       </c>
       <c r="J179" t="n">
-        <v>17.9696</v>
+        <v>19.646</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.32</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.8073</v>
       </c>
       <c r="J180" t="n">
-        <v>15.7344</v>
+        <v>17.7606</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.27</v>
       </c>
       <c r="I181" t="n">
-        <v>0.5965</v>
+        <v>0.6947</v>
       </c>
       <c r="J181" t="n">
-        <v>13.123</v>
+        <v>15.2834</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.11</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2599</v>
+        <v>0.2778</v>
       </c>
       <c r="J182" t="n">
-        <v>9.356400000000001</v>
+        <v>10.0008</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.1</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2432</v>
+        <v>0.2573</v>
       </c>
       <c r="J183" t="n">
-        <v>8.7552</v>
+        <v>9.2628</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.99</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0098</v>
+        <v>-0.0176</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.3528</v>
+        <v>-0.6336000000000001</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1771</v>
+        <v>-0.1075</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.3756</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.68</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.3505</v>
       </c>
       <c r="J186" t="n">
-        <v>-19.3968</v>
+        <v>-12.618</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.14</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4688</v>
+        <v>0.439</v>
       </c>
       <c r="J187" t="n">
-        <v>16.8768</v>
+        <v>15.804</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.13</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4403</v>
+        <v>0.4122</v>
       </c>
       <c r="J188" t="n">
-        <v>15.8508</v>
+        <v>14.8392</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4112</v>
+        <v>0.385</v>
       </c>
       <c r="J189" t="n">
-        <v>14.8032</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.98</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1636</v>
+        <v>-0.1092</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.8896</v>
+        <v>-3.9312</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.95</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2735</v>
+        <v>-0.2144</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.846</v>
+        <v>-7.7184</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.38</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.8732</v>
       </c>
       <c r="J192" t="n">
-        <v>17.4525</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.78</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3424</v>
+        <v>-0.2341</v>
       </c>
       <c r="J193" t="n">
-        <v>-8.56</v>
+        <v>-5.8525</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.7</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.469</v>
+        <v>-0.3102</v>
       </c>
       <c r="J194" t="n">
-        <v>-11.725</v>
+        <v>-7.755</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.61</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5939</v>
+        <v>-0.3951</v>
       </c>
       <c r="J195" t="n">
-        <v>-14.8475</v>
+        <v>-9.8775</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.52</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7095</v>
+        <v>-0.4787</v>
       </c>
       <c r="J196" t="n">
-        <v>-17.7375</v>
+        <v>-11.9675</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.65</v>
       </c>
       <c r="I197" t="n">
-        <v>1.4801</v>
+        <v>1.3125</v>
       </c>
       <c r="J197" t="n">
-        <v>37.0025</v>
+        <v>32.8125</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.27</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.7113</v>
       </c>
       <c r="J198" t="n">
-        <v>16.7225</v>
+        <v>17.7825</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.27</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.7113</v>
       </c>
       <c r="J199" t="n">
-        <v>16.7225</v>
+        <v>17.7825</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.14</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3167</v>
+        <v>0.3964</v>
       </c>
       <c r="J200" t="n">
-        <v>7.9175</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1457</v>
+        <v>-0.0648</v>
       </c>
       <c r="J201" t="n">
-        <v>-3.6425</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.61</v>
       </c>
       <c r="I202" t="n">
-        <v>1.4077</v>
+        <v>1.2649</v>
       </c>
       <c r="J202" t="n">
-        <v>32.3771</v>
+        <v>29.0927</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.57</v>
       </c>
       <c r="I203" t="n">
-        <v>1.331</v>
+        <v>1.2154</v>
       </c>
       <c r="J203" t="n">
-        <v>30.613</v>
+        <v>27.9542</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.47</v>
       </c>
       <c r="I204" t="n">
-        <v>1.1319</v>
+        <v>1.09</v>
       </c>
       <c r="J204" t="n">
-        <v>26.0337</v>
+        <v>25.07</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.87</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5723</v>
+        <v>-0.5027</v>
       </c>
       <c r="J205" t="n">
-        <v>-13.1629</v>
+        <v>-11.5621</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.78</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7899</v>
+        <v>-0.7399</v>
       </c>
       <c r="J206" t="n">
-        <v>-18.1677</v>
+        <v>-17.0177</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.14</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3543</v>
+        <v>0.3875</v>
       </c>
       <c r="J207" t="n">
-        <v>8.148899999999999</v>
+        <v>8.9125</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.99</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0442</v>
+        <v>0.0015</v>
       </c>
       <c r="J208" t="n">
-        <v>1.0166</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.79</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3471</v>
+        <v>-0.229</v>
       </c>
       <c r="J209" t="n">
-        <v>-7.9833</v>
+        <v>-5.267</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.76</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3944</v>
+        <v>-0.2582</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.071199999999999</v>
+        <v>-5.9386</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.51</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7292999999999999</v>
+        <v>-0.4931</v>
       </c>
       <c r="J211" t="n">
-        <v>-16.7739</v>
+        <v>-11.3413</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.57</v>
       </c>
       <c r="I212" t="n">
-        <v>1.3012</v>
+        <v>1.2018</v>
       </c>
       <c r="J212" t="n">
-        <v>31.2288</v>
+        <v>28.8432</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.37</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8808</v>
+        <v>0.9192</v>
       </c>
       <c r="J213" t="n">
-        <v>21.1392</v>
+        <v>22.0608</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.26</v>
       </c>
       <c r="I214" t="n">
-        <v>0.5925</v>
+        <v>0.6795</v>
       </c>
       <c r="J214" t="n">
-        <v>14.22</v>
+        <v>16.308</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.25</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.6563</v>
       </c>
       <c r="J215" t="n">
-        <v>13.632</v>
+        <v>15.7512</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.17</v>
       </c>
       <c r="I216" t="n">
-        <v>0.3704</v>
+        <v>0.4613</v>
       </c>
       <c r="J216" t="n">
-        <v>8.8896</v>
+        <v>11.0712</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.31</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.6821</v>
       </c>
       <c r="J217" t="n">
-        <v>13.6824</v>
+        <v>16.3704</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.18</v>
       </c>
       <c r="I218" t="n">
-        <v>0.392</v>
+        <v>0.4401</v>
       </c>
       <c r="J218" t="n">
-        <v>9.407999999999999</v>
+        <v>10.5624</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3389</v>
+        <v>-0.2164</v>
       </c>
       <c r="J219" t="n">
-        <v>-8.133599999999999</v>
+        <v>-5.1936</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.61</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.6161</v>
+        <v>-0.4082</v>
       </c>
       <c r="J220" t="n">
-        <v>-14.7864</v>
+        <v>-9.796799999999999</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.57</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.666</v>
+        <v>-0.4452</v>
       </c>
       <c r="J221" t="n">
-        <v>-15.984</v>
+        <v>-10.6848</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9385</v>
+        <v>0.8562</v>
       </c>
       <c r="J222" t="n">
-        <v>33.786</v>
+        <v>30.8232</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.06</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1111</v>
+        <v>0.1074</v>
       </c>
       <c r="J223" t="n">
-        <v>3.9996</v>
+        <v>3.8664</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.02</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0235</v>
+        <v>0.04</v>
       </c>
       <c r="J224" t="n">
-        <v>0.846</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.9</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2478</v>
+        <v>-0.1422</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.9208</v>
+        <v>-5.1192</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.7</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5322</v>
+        <v>-0.3439</v>
       </c>
       <c r="J226" t="n">
-        <v>-19.1592</v>
+        <v>-12.3804</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.5</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7245</v>
+        <v>0.6891</v>
       </c>
       <c r="J227" t="n">
-        <v>26.082</v>
+        <v>24.8076</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.33</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5189</v>
+        <v>0.4801</v>
       </c>
       <c r="J228" t="n">
-        <v>18.6804</v>
+        <v>17.2836</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.17</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2934</v>
+        <v>0.2707</v>
       </c>
       <c r="J229" t="n">
-        <v>10.5624</v>
+        <v>9.745200000000001</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3365</v>
+        <v>-0.2015</v>
       </c>
       <c r="J230" t="n">
-        <v>-12.114</v>
+        <v>-7.254</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.77</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4488</v>
+        <v>-0.2821</v>
       </c>
       <c r="J231" t="n">
-        <v>-16.1568</v>
+        <v>-10.1556</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.03</v>
       </c>
       <c r="I232" t="n">
-        <v>0.12</v>
+        <v>0.1055</v>
       </c>
       <c r="J232" t="n">
-        <v>3.12</v>
+        <v>2.743</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>0.0364</v>
+        <v>0.0109</v>
       </c>
       <c r="J233" t="n">
-        <v>0.9464</v>
+        <v>0.2834</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.98</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0251</v>
+        <v>-0.031</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.6526</v>
+        <v>-0.806</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.93</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1447</v>
+        <v>-0.0941</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.7622</v>
+        <v>-2.4466</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.75</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4397</v>
+        <v>-0.2809</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.4322</v>
+        <v>-7.3034</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.55</v>
       </c>
       <c r="I237" t="n">
-        <v>1.352</v>
+        <v>1.2228</v>
       </c>
       <c r="J237" t="n">
-        <v>35.152</v>
+        <v>31.7928</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.18</v>
       </c>
       <c r="I238" t="n">
-        <v>0.528</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="J238" t="n">
-        <v>13.728</v>
+        <v>13.5902</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.11</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3033</v>
+        <v>0.3439</v>
       </c>
       <c r="J239" t="n">
-        <v>7.8858</v>
+        <v>8.9414</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.99</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1572</v>
+        <v>-0.0876</v>
       </c>
       <c r="J240" t="n">
-        <v>-4.0872</v>
+        <v>-2.2776</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.86</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5641</v>
+        <v>-0.5002</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.6666</v>
+        <v>-13.0052</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>0.86</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.09</v>
+        <v>-0.1011</v>
       </c>
       <c r="J242" t="n">
-        <v>-1.8</v>
+        <v>-2.022</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.72</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.3102</v>
+        <v>-0.2581</v>
       </c>
       <c r="J243" t="n">
-        <v>-6.204</v>
+        <v>-5.162</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.61</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.4895</v>
+        <v>-0.3653</v>
       </c>
       <c r="J244" t="n">
-        <v>-9.789999999999999</v>
+        <v>-7.306</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.588</v>
+        <v>-0.4092</v>
       </c>
       <c r="J245" t="n">
-        <v>-11.76</v>
+        <v>-8.183999999999999</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.25</v>
       </c>
       <c r="I246" t="n">
-        <v>-1.0014</v>
+        <v>-0.7043</v>
       </c>
       <c r="J246" t="n">
-        <v>-20.028</v>
+        <v>-14.086</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.81</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6612</v>
+        <v>1.4468</v>
       </c>
       <c r="J247" t="n">
-        <v>33.224</v>
+        <v>28.936</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>1.3859</v>
+        <v>1.2763</v>
       </c>
       <c r="J248" t="n">
-        <v>27.718</v>
+        <v>25.526</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.51</v>
       </c>
       <c r="I249" t="n">
-        <v>1.0611</v>
+        <v>1.1044</v>
       </c>
       <c r="J249" t="n">
-        <v>21.222</v>
+        <v>22.088</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.33</v>
       </c>
       <c r="I250" t="n">
-        <v>0.6706</v>
+        <v>0.7997</v>
       </c>
       <c r="J250" t="n">
-        <v>13.412</v>
+        <v>15.994</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>1.29</v>
       </c>
       <c r="I251" t="n">
-        <v>0.5837</v>
+        <v>0.7093</v>
       </c>
       <c r="J251" t="n">
-        <v>11.674</v>
+        <v>14.186</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.31</v>
       </c>
       <c r="I252" t="n">
-        <v>0.5213</v>
+        <v>0.6212</v>
       </c>
       <c r="J252" t="n">
-        <v>15.1177</v>
+        <v>18.0148</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.19</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3565</v>
+        <v>0.4096</v>
       </c>
       <c r="J253" t="n">
-        <v>10.3385</v>
+        <v>11.8784</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.05</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1172</v>
+        <v>0.1331</v>
       </c>
       <c r="J254" t="n">
-        <v>3.3988</v>
+        <v>3.8599</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2713</v>
+        <v>-0.1602</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.8677</v>
+        <v>-4.6458</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.75</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4607</v>
+        <v>-0.2923</v>
       </c>
       <c r="J256" t="n">
-        <v>-13.3603</v>
+        <v>-8.476699999999999</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.46</v>
       </c>
       <c r="I257" t="n">
-        <v>1.181</v>
+        <v>1.11</v>
       </c>
       <c r="J257" t="n">
-        <v>34.249</v>
+        <v>32.19</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.22</v>
       </c>
       <c r="I258" t="n">
-        <v>0.6439</v>
+        <v>0.626</v>
       </c>
       <c r="J258" t="n">
-        <v>18.6731</v>
+        <v>18.154</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1217</v>
+        <v>0.1715</v>
       </c>
       <c r="J259" t="n">
-        <v>3.5293</v>
+        <v>4.9735</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2998</v>
+        <v>-0.2301</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.6942</v>
+        <v>-6.6729</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.93</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3629</v>
+        <v>-0.2936</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.5241</v>
+        <v>-8.5144</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.61</v>
       </c>
       <c r="I262" t="n">
-        <v>0.777</v>
+        <v>0.7071</v>
       </c>
       <c r="J262" t="n">
-        <v>16.317</v>
+        <v>14.8491</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.56</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7211</v>
+        <v>0.6558</v>
       </c>
       <c r="J263" t="n">
-        <v>15.1431</v>
+        <v>13.7718</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.51</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6632</v>
+        <v>0.6042</v>
       </c>
       <c r="J264" t="n">
-        <v>13.9272</v>
+        <v>12.6882</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.43</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5647</v>
+        <v>0.5208</v>
       </c>
       <c r="J265" t="n">
-        <v>11.8587</v>
+        <v>10.9368</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.8</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4409</v>
+        <v>-0.2747</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.258900000000001</v>
+        <v>-5.7687</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.05</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2153</v>
+        <v>0.1565</v>
       </c>
       <c r="J267" t="n">
-        <v>4.5213</v>
+        <v>3.2865</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.95</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0302</v>
+        <v>-0.0509</v>
       </c>
       <c r="J268" t="n">
-        <v>-0.6342</v>
+        <v>-1.0689</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3461</v>
+        <v>-0.2347</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.2681</v>
+        <v>-4.9287</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.7</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4711</v>
+        <v>-0.3111</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.8931</v>
+        <v>-6.5331</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.54</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6857</v>
+        <v>-0.461</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.3997</v>
+        <v>-9.680999999999999</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.64</v>
       </c>
       <c r="I272" t="n">
-        <v>0.881</v>
+        <v>1.0701</v>
       </c>
       <c r="J272" t="n">
-        <v>26.43</v>
+        <v>32.103</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.21</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3562</v>
+        <v>0.4252</v>
       </c>
       <c r="J273" t="n">
-        <v>10.686</v>
+        <v>12.756</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.17</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2951</v>
+        <v>0.3544</v>
       </c>
       <c r="J274" t="n">
-        <v>8.853</v>
+        <v>10.632</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.8</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4072</v>
+        <v>-0.2521</v>
       </c>
       <c r="J275" t="n">
-        <v>-12.216</v>
+        <v>-7.563</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.78</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4346</v>
+        <v>-0.2719</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.038</v>
+        <v>-8.157</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.27</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8387</v>
+        <v>0.8015</v>
       </c>
       <c r="J277" t="n">
-        <v>25.161</v>
+        <v>24.045</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.06</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2731</v>
+        <v>0.2302</v>
       </c>
       <c r="J278" t="n">
-        <v>8.193</v>
+        <v>6.906</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.97</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1571</v>
+        <v>-0.1291</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.713</v>
+        <v>-3.873</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5626</v>
+        <v>-0.5142</v>
       </c>
       <c r="J280" t="n">
-        <v>-16.878</v>
+        <v>-15.426</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.84</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5626</v>
+        <v>-0.5142</v>
       </c>
       <c r="J281" t="n">
-        <v>-16.878</v>
+        <v>-15.426</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.49</v>
       </c>
       <c r="I282" t="n">
-        <v>0.7221</v>
+        <v>0.6379</v>
       </c>
       <c r="J282" t="n">
-        <v>20.2188</v>
+        <v>17.8612</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.2</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3508</v>
+        <v>0.2942</v>
       </c>
       <c r="J283" t="n">
-        <v>9.8224</v>
+        <v>8.2376</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.13</v>
       </c>
       <c r="I284" t="n">
-        <v>0.2403</v>
+        <v>0.2034</v>
       </c>
       <c r="J284" t="n">
-        <v>6.7284</v>
+        <v>5.6952</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.89</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2691</v>
+        <v>-0.1556</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.5348</v>
+        <v>-4.3568</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.76</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4573</v>
+        <v>-0.2888</v>
       </c>
       <c r="J286" t="n">
-        <v>-12.8044</v>
+        <v>-8.086399999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.45</v>
       </c>
       <c r="I287" t="n">
-        <v>0.707</v>
+        <v>0.668</v>
       </c>
       <c r="J287" t="n">
-        <v>19.796</v>
+        <v>18.704</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.25</v>
       </c>
       <c r="I288" t="n">
-        <v>0.455</v>
+        <v>0.406</v>
       </c>
       <c r="J288" t="n">
-        <v>12.74</v>
+        <v>11.368</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.95</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1337</v>
+        <v>-0.0755</v>
       </c>
       <c r="J289" t="n">
-        <v>-3.7436</v>
+        <v>-2.114</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.71</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.5064</v>
+        <v>-0.3263</v>
       </c>
       <c r="J290" t="n">
-        <v>-14.1792</v>
+        <v>-9.1364</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.62</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6208</v>
+        <v>-0.4105</v>
       </c>
       <c r="J291" t="n">
-        <v>-17.3824</v>
+        <v>-11.494</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.11</v>
       </c>
       <c r="I292" t="n">
-        <v>0.2576</v>
+        <v>0.276</v>
       </c>
       <c r="J292" t="n">
-        <v>9.016</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.09</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2238</v>
+        <v>0.2347</v>
       </c>
       <c r="J293" t="n">
-        <v>7.833</v>
+        <v>8.214499999999999</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0476</v>
       </c>
       <c r="J294" t="n">
-        <v>-2.331</v>
+        <v>-1.666</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.85</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2993</v>
+        <v>-0.184</v>
       </c>
       <c r="J295" t="n">
-        <v>-10.4755</v>
+        <v>-6.44</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3605</v>
+        <v>-0.2249</v>
       </c>
       <c r="J296" t="n">
-        <v>-12.6175</v>
+        <v>-7.8715</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.26</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7687</v>
+        <v>0.7401</v>
       </c>
       <c r="J297" t="n">
-        <v>26.9045</v>
+        <v>25.9035</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.12</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4022</v>
+        <v>0.3819</v>
       </c>
       <c r="J298" t="n">
-        <v>14.077</v>
+        <v>13.3665</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.1152</v>
       </c>
       <c r="J299" t="n">
-        <v>2.7405</v>
+        <v>4.032</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.01</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.006</v>
+        <v>0.0379</v>
       </c>
       <c r="J300" t="n">
-        <v>-0.21</v>
+        <v>1.3265</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.96</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.2452</v>
+        <v>-0.1844</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.582000000000001</v>
+        <v>-6.454</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>0.93</v>
       </c>
       <c r="I302" t="n">
-        <v>0.0497</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="J302" t="n">
-        <v>0.9443</v>
+        <v>0.1824</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.65</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.3994</v>
+        <v>-0.3205</v>
       </c>
       <c r="J303" t="n">
-        <v>-7.5886</v>
+        <v>-6.0895</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.62</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.4471</v>
+        <v>-0.35</v>
       </c>
       <c r="J304" t="n">
-        <v>-8.494899999999999</v>
+        <v>-6.65</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.38</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.8316</v>
+        <v>-0.5732</v>
       </c>
       <c r="J305" t="n">
-        <v>-15.8004</v>
+        <v>-10.8908</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.26</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.984</v>
+        <v>-0.6901</v>
       </c>
       <c r="J306" t="n">
-        <v>-18.696</v>
+        <v>-13.1119</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>2.22</v>
       </c>
       <c r="I307" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J307" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.69</v>
       </c>
       <c r="I308" t="n">
-        <v>1.4288</v>
+        <v>1.3063</v>
       </c>
       <c r="J308" t="n">
-        <v>27.1472</v>
+        <v>24.8197</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.59</v>
       </c>
       <c r="I309" t="n">
-        <v>1.2299</v>
+        <v>1.1927</v>
       </c>
       <c r="J309" t="n">
-        <v>23.3681</v>
+        <v>22.6613</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.13</v>
       </c>
       <c r="I310" t="n">
-        <v>0.2044</v>
+        <v>0.3086</v>
       </c>
       <c r="J310" t="n">
-        <v>3.8836</v>
+        <v>5.8634</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>1.13</v>
       </c>
       <c r="I311" t="n">
-        <v>0.2044</v>
+        <v>0.3086</v>
       </c>
       <c r="J311" t="n">
-        <v>3.8836</v>
+        <v>5.8634</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>0.98</v>
       </c>
       <c r="I312" t="n">
-        <v>0.0484</v>
+        <v>-0.0002</v>
       </c>
       <c r="J312" t="n">
-        <v>0.968</v>
+        <v>-0.004</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.83</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.2266</v>
+        <v>-0.1822</v>
       </c>
       <c r="J313" t="n">
-        <v>-4.532</v>
+        <v>-3.644</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.74</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.3945</v>
+        <v>-0.2686</v>
       </c>
       <c r="J314" t="n">
-        <v>-7.89</v>
+        <v>-5.372</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.67</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.5023</v>
+        <v>-0.3345</v>
       </c>
       <c r="J315" t="n">
-        <v>-10.046</v>
+        <v>-6.69</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.63</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5587</v>
+        <v>-0.3722</v>
       </c>
       <c r="J316" t="n">
-        <v>-11.174</v>
+        <v>-7.444</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.65</v>
       </c>
       <c r="I317" t="n">
-        <v>1.435</v>
+        <v>1.29</v>
       </c>
       <c r="J317" t="n">
-        <v>28.7</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.41</v>
       </c>
       <c r="I318" t="n">
-        <v>0.9469</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="J318" t="n">
-        <v>18.938</v>
+        <v>19.748</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.32</v>
       </c>
       <c r="I319" t="n">
-        <v>0.714</v>
+        <v>0.8069</v>
       </c>
       <c r="J319" t="n">
-        <v>14.28</v>
+        <v>16.138</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.26</v>
       </c>
       <c r="I320" t="n">
-        <v>0.572</v>
+        <v>0.6711</v>
       </c>
       <c r="J320" t="n">
-        <v>11.44</v>
+        <v>13.422</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>1.19</v>
       </c>
       <c r="I321" t="n">
-        <v>0.4042</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="J321" t="n">
-        <v>8.084</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.61</v>
       </c>
       <c r="I322" t="n">
-        <v>0.8063</v>
+        <v>0.7269</v>
       </c>
       <c r="J322" t="n">
-        <v>21.7701</v>
+        <v>19.6263</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.23</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3154</v>
+        <v>0.3117</v>
       </c>
       <c r="J323" t="n">
-        <v>8.5158</v>
+        <v>8.415900000000001</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.2</v>
       </c>
       <c r="I324" t="n">
-        <v>0.2708</v>
+        <v>0.2755</v>
       </c>
       <c r="J324" t="n">
-        <v>7.3116</v>
+        <v>7.4385</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.17</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2263</v>
+        <v>0.238</v>
       </c>
       <c r="J325" t="n">
-        <v>6.1101</v>
+        <v>6.426</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.14</v>
       </c>
       <c r="I326" t="n">
-        <v>0.181</v>
+        <v>0.1989</v>
       </c>
       <c r="J326" t="n">
-        <v>4.887</v>
+        <v>5.3703</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.25</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5107</v>
+        <v>0.4594</v>
       </c>
       <c r="J327" t="n">
-        <v>13.7889</v>
+        <v>12.4038</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.9</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1423</v>
+        <v>-0.1184</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.8421</v>
+        <v>-3.1968</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.85</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.236</v>
+        <v>-0.1712</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.372</v>
+        <v>-4.6224</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.73</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4413</v>
+        <v>-0.288</v>
       </c>
       <c r="J330" t="n">
-        <v>-11.9151</v>
+        <v>-7.776</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.49</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.7544</v>
+        <v>-0.5121</v>
       </c>
       <c r="J331" t="n">
-        <v>-20.3688</v>
+        <v>-13.8267</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.06</v>
       </c>
       <c r="I332" t="n">
-        <v>0.1924</v>
+        <v>0.1866</v>
       </c>
       <c r="J332" t="n">
-        <v>5.0024</v>
+        <v>4.8516</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1</v>
       </c>
       <c r="I333" t="n">
-        <v>0.0495</v>
+        <v>0.0185</v>
       </c>
       <c r="J333" t="n">
-        <v>1.287</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.96</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.0563</v>
+        <v>-0.0551</v>
       </c>
       <c r="J334" t="n">
-        <v>-1.4638</v>
+        <v>-1.4326</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.85</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2789</v>
+        <v>-0.1772</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.2514</v>
+        <v>-4.6072</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.67</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5412</v>
+        <v>-0.3536</v>
       </c>
       <c r="J336" t="n">
-        <v>-14.0712</v>
+        <v>-9.1936</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.65</v>
       </c>
       <c r="I337" t="n">
-        <v>1.482</v>
+        <v>1.3135</v>
       </c>
       <c r="J337" t="n">
-        <v>38.532</v>
+        <v>34.151</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.54</v>
       </c>
       <c r="I338" t="n">
-        <v>1.2715</v>
+        <v>1.1776</v>
       </c>
       <c r="J338" t="n">
-        <v>33.059</v>
+        <v>30.6176</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.15</v>
       </c>
       <c r="I339" t="n">
-        <v>0.345</v>
+        <v>0.4235</v>
       </c>
       <c r="J339" t="n">
-        <v>8.970000000000001</v>
+        <v>11.011</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.12</v>
       </c>
       <c r="I340" t="n">
-        <v>0.2644</v>
+        <v>0.3435</v>
       </c>
       <c r="J340" t="n">
-        <v>6.8744</v>
+        <v>8.930999999999999</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.85</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6234</v>
+        <v>-0.5578</v>
       </c>
       <c r="J341" t="n">
-        <v>-16.2084</v>
+        <v>-14.5028</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3703/event_3703_evp_summary.xlsx
+++ b/database/event/3703/event_3703_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.1419</v>
+        <v>8.312200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1727</v>
+        <v>2.2181</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0376</v>
+        <v>3.1597</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1419</v>
+        <v>8.312200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9242</v>
+        <v>2.895</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2177</v>
+        <v>5.4172</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8168</v>
+        <v>4.6575</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5045</v>
+        <v>2.515</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2177</v>
+        <v>5.4172</v>
       </c>
       <c r="K2" t="n">
         <v>132</v>
@@ -529,7 +529,7 @@
         <v>178</v>
       </c>
       <c r="M2" t="n">
-        <v>7.7222</v>
+        <v>7.9322</v>
       </c>
       <c r="N2" t="n">
         <v>310</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5516</v>
+        <v>5.5076</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4815</v>
+        <v>1.4697</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8683</v>
+        <v>1.883</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5516</v>
+        <v>5.5076</v>
       </c>
       <c r="F3" t="n">
-        <v>2.878</v>
+        <v>2.8237</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6736</v>
+        <v>2.6839</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6541</v>
+        <v>4.4223</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4199</v>
+        <v>2.388</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6736</v>
+        <v>2.6839</v>
       </c>
       <c r="K3" t="n">
         <v>158</v>
@@ -575,7 +575,7 @@
         <v>192</v>
       </c>
       <c r="M3" t="n">
-        <v>5.093500000000001</v>
+        <v>5.071899999999999</v>
       </c>
       <c r="N3" t="n">
         <v>350</v>
@@ -584,185 +584,185 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.311</v>
+        <v>5.4158</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4173</v>
+        <v>1.4452</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7596</v>
+        <v>1.8412</v>
       </c>
       <c r="E4" t="n">
-        <v>5.311</v>
+        <v>5.4158</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6782</v>
+        <v>2.9803</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6328</v>
+        <v>2.4355</v>
       </c>
       <c r="H4" t="n">
-        <v>7.4734</v>
+        <v>4.9388</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8858</v>
+        <v>2.6669</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6328</v>
+        <v>2.4355</v>
       </c>
       <c r="K4" t="n">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="L4" t="n">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5186</v>
+        <v>5.1024</v>
       </c>
       <c r="N4" t="n">
-        <v>350</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2719</v>
+        <v>5.3039</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4068</v>
+        <v>1.4154</v>
       </c>
       <c r="D5" t="n">
-        <v>1.742</v>
+        <v>1.7902</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2719</v>
+        <v>5.3039</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0357</v>
+        <v>3.5811</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2362</v>
+        <v>1.7228</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2097</v>
+        <v>6.921</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7088</v>
+        <v>3.7373</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2362</v>
+        <v>1.7228</v>
       </c>
       <c r="K5" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="L5" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="M5" t="n">
-        <v>4.945</v>
+        <v>5.4601</v>
       </c>
       <c r="N5" t="n">
-        <v>310</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.784</v>
+        <v>4.8806</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2766</v>
+        <v>1.3024</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5217</v>
+        <v>1.5975</v>
       </c>
       <c r="E6" t="n">
-        <v>4.784</v>
+        <v>4.8806</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3786</v>
+        <v>2.9631</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4054</v>
+        <v>1.9175</v>
       </c>
       <c r="H6" t="n">
-        <v>6.4177</v>
+        <v>4.8823</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3369</v>
+        <v>2.6364</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4054</v>
+        <v>1.9175</v>
       </c>
       <c r="K6" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="L6" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7423</v>
+        <v>4.553900000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>310</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6796</v>
+        <v>4.8371</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2488</v>
+        <v>1.2908</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4746</v>
+        <v>1.5777</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6796</v>
+        <v>4.8371</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0012</v>
+        <v>3.2927</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6784</v>
+        <v>1.5444</v>
       </c>
       <c r="H7" t="n">
-        <v>5.0879</v>
+        <v>5.9697</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6455</v>
+        <v>3.2236</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6784</v>
+        <v>1.5444</v>
       </c>
       <c r="K7" t="n">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="L7" t="n">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3239</v>
+        <v>4.768</v>
       </c>
       <c r="N7" t="n">
-        <v>350</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4712</v>
+        <v>4.5403</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1932</v>
+        <v>1.2116</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3805</v>
+        <v>1.4426</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4712</v>
+        <v>4.5403</v>
       </c>
       <c r="F8" t="n">
-        <v>3.8621</v>
+        <v>3.821</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6091</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>8.1213</v>
+        <v>7.7127</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2227</v>
+        <v>4.1648</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6091</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>132</v>
@@ -805,7 +805,7 @@
         <v>178</v>
       </c>
       <c r="M8" t="n">
-        <v>4.831799999999999</v>
+        <v>4.8841</v>
       </c>
       <c r="N8" t="n">
         <v>310</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.0867</v>
+        <v>4.1602</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0905</v>
+        <v>1.1102</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2069</v>
+        <v>1.2696</v>
       </c>
       <c r="E9" t="n">
-        <v>4.0867</v>
+        <v>4.1602</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7583</v>
+        <v>2.7117</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3284</v>
+        <v>1.4485</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2323</v>
+        <v>4.0527</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2006</v>
+        <v>2.1884</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3284</v>
+        <v>1.4485</v>
       </c>
       <c r="K9" t="n">
         <v>132</v>
@@ -851,7 +851,7 @@
         <v>178</v>
       </c>
       <c r="M9" t="n">
-        <v>3.529</v>
+        <v>3.6369</v>
       </c>
       <c r="N9" t="n">
         <v>310</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7781</v>
+        <v>3.6378</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0082</v>
+        <v>0.9708</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0676</v>
+        <v>1.0318</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7781</v>
+        <v>3.6378</v>
       </c>
       <c r="F10" t="n">
-        <v>3.73</v>
+        <v>3.6092</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0481</v>
+        <v>0.0286</v>
       </c>
       <c r="H10" t="n">
-        <v>7.6559</v>
+        <v>7.0138</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9807</v>
+        <v>3.7874</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0481</v>
+        <v>0.0286</v>
       </c>
       <c r="K10" t="n">
         <v>205</v>
@@ -897,7 +897,7 @@
         <v>55</v>
       </c>
       <c r="M10" t="n">
-        <v>4.0288</v>
+        <v>3.816</v>
       </c>
       <c r="N10" t="n">
         <v>260</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3561</v>
+        <v>3.0734</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8956</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8771</v>
+        <v>0.7749</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3561</v>
+        <v>3.0734</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3561</v>
+        <v>3.7632</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.6898</v>
       </c>
       <c r="H11" t="n">
-        <v>4.0097</v>
+        <v>7.522</v>
       </c>
       <c r="I11" t="n">
-        <v>4.0097</v>
+        <v>4.0618</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.6898</v>
       </c>
       <c r="K11" t="n">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M11" t="n">
-        <v>4.0097</v>
+        <v>3.372</v>
       </c>
       <c r="N11" t="n">
-        <v>177</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2159</v>
+        <v>3.0143</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8582</v>
+        <v>0.8044</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8138</v>
+        <v>0.748</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2159</v>
+        <v>3.0143</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8588</v>
+        <v>3.0143</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6429</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>8.1096</v>
+        <v>3.8725</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2166</v>
+        <v>3.8725</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6429</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5737</v>
+        <v>3.8725</v>
       </c>
       <c r="N12" t="n">
-        <v>247</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1144</v>
+        <v>2.9952</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.7993</v>
       </c>
       <c r="D13" t="n">
-        <v>0.768</v>
+        <v>0.7393</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1144</v>
+        <v>2.9952</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5475</v>
+        <v>2.4381</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5669</v>
+        <v>0.5571</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4893</v>
+        <v>3.1499</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8143</v>
+        <v>1.7009</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5669</v>
+        <v>0.5571</v>
       </c>
       <c r="K13" t="n">
         <v>205</v>
@@ -1035,7 +1035,7 @@
         <v>55</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3812</v>
+        <v>2.258</v>
       </c>
       <c r="N13" t="n">
         <v>260</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.835</v>
+        <v>2.7804</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7565</v>
+        <v>0.742</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6418</v>
+        <v>0.6415</v>
       </c>
       <c r="E14" t="n">
-        <v>2.835</v>
+        <v>2.7804</v>
       </c>
       <c r="F14" t="n">
-        <v>1.513</v>
+        <v>1.3967</v>
       </c>
       <c r="G14" t="n">
-        <v>1.322</v>
+        <v>1.3837</v>
       </c>
       <c r="H14" t="n">
-        <v>1.513</v>
+        <v>1.3967</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7867</v>
+        <v>0.7542</v>
       </c>
       <c r="J14" t="n">
-        <v>1.322</v>
+        <v>1.3837</v>
       </c>
       <c r="K14" t="n">
         <v>158</v>
@@ -1081,7 +1081,7 @@
         <v>192</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1087</v>
+        <v>2.1379</v>
       </c>
       <c r="N14" t="n">
         <v>350</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7799</v>
+        <v>2.5928</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7418</v>
+        <v>0.6919</v>
       </c>
       <c r="D15" t="n">
-        <v>0.617</v>
+        <v>0.5561</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7799</v>
+        <v>2.5928</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2267</v>
+        <v>3.0867</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4468</v>
+        <v>-0.4939</v>
       </c>
       <c r="H15" t="n">
-        <v>5.8826</v>
+        <v>5.2901</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0587</v>
+        <v>2.8566</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4468</v>
+        <v>-0.4939</v>
       </c>
       <c r="K15" t="n">
         <v>206</v>
@@ -1127,7 +1127,7 @@
         <v>41</v>
       </c>
       <c r="M15" t="n">
-        <v>2.6119</v>
+        <v>2.3627</v>
       </c>
       <c r="N15" t="n">
         <v>247</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2705</v>
+        <v>2.3364</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6059</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.387</v>
+        <v>0.4394</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2705</v>
+        <v>2.3364</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4345</v>
+        <v>2.3482</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.164</v>
+        <v>-0.0118</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0914</v>
+        <v>2.8534</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6074</v>
+        <v>1.5408</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.164</v>
+        <v>-0.0118</v>
       </c>
       <c r="K16" t="n">
         <v>158</v>
@@ -1173,7 +1173,7 @@
         <v>192</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4434</v>
+        <v>1.529</v>
       </c>
       <c r="N16" t="n">
         <v>350</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1031</v>
+        <v>2.0601</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5612</v>
+        <v>0.5497</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3114</v>
+        <v>0.3136</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1031</v>
+        <v>2.0601</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1031</v>
+        <v>2.0601</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1031</v>
+        <v>2.0601</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1031</v>
+        <v>2.0601</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1031</v>
+        <v>2.0601</v>
       </c>
       <c r="N17" t="n">
         <v>141</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9845</v>
+        <v>1.8235</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5296</v>
+        <v>0.4866</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2579</v>
+        <v>0.2059</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9845</v>
+        <v>1.8235</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1791</v>
+        <v>2.0347</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1946</v>
+        <v>-0.2112</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1913</v>
+        <v>2.0347</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1394</v>
+        <v>1.0987</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1946</v>
+        <v>-0.2112</v>
       </c>
       <c r="K18" t="n">
         <v>205</v>
@@ -1265,7 +1265,7 @@
         <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9448</v>
+        <v>0.8875</v>
       </c>
       <c r="N18" t="n">
         <v>260</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7624</v>
+        <v>1.6167</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4703</v>
+        <v>0.4314</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1576</v>
+        <v>0.1118</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7624</v>
+        <v>1.6167</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7624</v>
+        <v>1.6167</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7624</v>
+        <v>1.6167</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7624</v>
+        <v>1.6167</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7624</v>
+        <v>1.6167</v>
       </c>
       <c r="N19" t="n">
         <v>192</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4948</v>
+        <v>1.4102</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3989</v>
+        <v>0.3763</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0368</v>
+        <v>0.0177</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4948</v>
+        <v>1.4102</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4948</v>
+        <v>1.4102</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4948</v>
+        <v>1.4102</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4948</v>
+        <v>1.4102</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4948</v>
+        <v>1.4102</v>
       </c>
       <c r="N20" t="n">
         <v>141</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4769</v>
+        <v>1.3747</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3941</v>
+        <v>0.3668</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0287</v>
+        <v>0.0016</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4769</v>
+        <v>1.3747</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4769</v>
+        <v>1.3747</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4769</v>
+        <v>1.3747</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4769</v>
+        <v>1.3747</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4769</v>
+        <v>1.3747</v>
       </c>
       <c r="N21" t="n">
         <v>177</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3127</v>
+        <v>1.2574</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3503</v>
+        <v>0.3355</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0454</v>
+        <v>-0.0518</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3127</v>
+        <v>1.2574</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3127</v>
+        <v>1.2574</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3127</v>
+        <v>1.2574</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3127</v>
+        <v>1.2574</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3127</v>
+        <v>1.2574</v>
       </c>
       <c r="N22" t="n">
         <v>177</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9608</v>
+        <v>0.8026</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2564</v>
+        <v>0.2142</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2043</v>
+        <v>-0.2588</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9608</v>
+        <v>0.8026</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7403</v>
+        <v>1.6145</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7795</v>
+        <v>-0.8119</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7403</v>
+        <v>1.6145</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9049</v>
+        <v>0.8718</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7795</v>
+        <v>-0.8119</v>
       </c>
       <c r="K23" t="n">
         <v>206</v>
@@ -1495,7 +1495,7 @@
         <v>41</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1254000000000001</v>
+        <v>0.05990000000000006</v>
       </c>
       <c r="N23" t="n">
         <v>247</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7308</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>0.195</v>
+        <v>0.168</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3081</v>
+        <v>-0.3376</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7308</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7308</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7308</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7308</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7308</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="N24" t="n">
         <v>192</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6733</v>
+        <v>0.6163</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1797</v>
+        <v>0.1645</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3341</v>
+        <v>-0.3437</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6733</v>
+        <v>0.6163</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6733</v>
+        <v>0.6163</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6733</v>
+        <v>0.6163</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6733</v>
+        <v>0.6163</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6733</v>
+        <v>0.6163</v>
       </c>
       <c r="N25" t="n">
         <v>129</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.5876</v>
       </c>
       <c r="C26" t="n">
-        <v>0.165</v>
+        <v>0.1568</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3588</v>
+        <v>-0.3567</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.5876</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.5876</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.5876</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.5876</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.5876</v>
       </c>
       <c r="N26" t="n">
         <v>141</v>
@@ -1642,32 +1642,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5891</v>
+        <v>0.5788</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1572</v>
+        <v>0.1545</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3721</v>
+        <v>-0.3607</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5891</v>
+        <v>0.5788</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5891</v>
+        <v>0.5788</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5891</v>
+        <v>0.5788</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5891</v>
+        <v>0.5788</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5891</v>
+        <v>0.5788</v>
       </c>
       <c r="N27" t="n">
         <v>141</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3358</v>
+        <v>0.3371</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0896</v>
+        <v>0.09</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4864</v>
+        <v>-0.4707</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3358</v>
+        <v>0.3371</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3358</v>
+        <v>0.3371</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3358</v>
+        <v>0.3371</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3358</v>
+        <v>0.3371</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3358</v>
+        <v>0.3371</v>
       </c>
       <c r="N28" t="n">
         <v>192</v>
@@ -1734,231 +1734,231 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2426</v>
+        <v>0.1972</v>
       </c>
       <c r="C29" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0526</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5285</v>
+        <v>-0.5344</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2426</v>
+        <v>0.1972</v>
       </c>
       <c r="F29" t="n">
-        <v>1.0399</v>
+        <v>0.1972</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.7973</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.0399</v>
+        <v>0.1972</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5407</v>
+        <v>0.1972</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.7973</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="L29" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2566000000000001</v>
+        <v>0.1972</v>
       </c>
       <c r="N29" t="n">
-        <v>247</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2307</v>
+        <v>0.0731</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0616</v>
+        <v>0.0195</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5339</v>
+        <v>-0.5909</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2307</v>
+        <v>0.0731</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2307</v>
+        <v>0.0731</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2307</v>
+        <v>0.0731</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2307</v>
+        <v>0.0731</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2307</v>
+        <v>0.0731</v>
       </c>
       <c r="N30" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0659</v>
       </c>
       <c r="C31" t="n">
-        <v>0.024</v>
+        <v>0.0176</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5974</v>
+        <v>-0.5942</v>
       </c>
       <c r="E31" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0659</v>
       </c>
       <c r="F31" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.9006</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.8347</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.9006</v>
       </c>
       <c r="I31" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.4863</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.8347</v>
       </c>
       <c r="K31" t="n">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M31" t="n">
-        <v>0.08989999999999999</v>
+        <v>-0.3484</v>
       </c>
       <c r="N31" t="n">
-        <v>177</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0834</v>
+        <v>0.0532</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0223</v>
+        <v>0.0142</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6004</v>
+        <v>-0.6</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0834</v>
+        <v>0.0532</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0834</v>
+        <v>0.0532</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0834</v>
+        <v>0.0532</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0834</v>
+        <v>0.0532</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0834</v>
+        <v>0.0532</v>
       </c>
       <c r="N32" t="n">
-        <v>129</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0498</v>
+        <v>0.0524</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0133</v>
+        <v>0.014</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6155</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0498</v>
+        <v>0.0524</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0498</v>
+        <v>0.0524</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0498</v>
+        <v>0.0524</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0498</v>
+        <v>0.0524</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0498</v>
+        <v>0.0524</v>
       </c>
       <c r="N33" t="n">
-        <v>177</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1978</v>
+        <v>-0.2449</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0528</v>
+        <v>-0.0654</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.7357</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1978</v>
+        <v>-0.2449</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1978</v>
+        <v>-0.2449</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1978</v>
+        <v>-0.2449</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1978</v>
+        <v>-0.2449</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1978</v>
+        <v>-0.2449</v>
       </c>
       <c r="N34" t="n">
         <v>129</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4588</v>
+        <v>-0.4259</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1224</v>
+        <v>-0.1137</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8451</v>
+        <v>-0.8181</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4588</v>
+        <v>-0.4259</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5412</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5412</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2814</v>
+        <v>0.31</v>
       </c>
       <c r="J35" t="n">
         <v>-1</v>
@@ -2047,7 +2047,7 @@
         <v>41</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7186</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>247</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9093</v>
+        <v>-0.9635</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2426</v>
+        <v>-0.2571</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0485</v>
+        <v>-1.0628</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9093</v>
+        <v>-0.9635</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9093</v>
+        <v>-0.9635</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9093</v>
+        <v>-0.9635</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9093</v>
+        <v>-0.9635</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9093</v>
+        <v>-0.9635</v>
       </c>
       <c r="N36" t="n">
         <v>129</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0405</v>
+        <v>-1.0749</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2777</v>
+        <v>-0.2868</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1077</v>
+        <v>-1.1135</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0405</v>
+        <v>-1.0749</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0405</v>
+        <v>-1.0749</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0405</v>
+        <v>-1.0749</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0405</v>
+        <v>-1.0749</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0405</v>
+        <v>-1.0749</v>
       </c>
       <c r="N37" t="n">
         <v>141</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3674</v>
+        <v>-1.4446</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3649</v>
+        <v>-0.3855</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2553</v>
+        <v>-1.2818</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3674</v>
+        <v>-1.4446</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3674</v>
+        <v>-1.4446</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3674</v>
+        <v>-1.4446</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3674</v>
+        <v>-1.4446</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3674</v>
+        <v>-1.4446</v>
       </c>
       <c r="N38" t="n">
         <v>129</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.0589</v>
+        <v>-2.0338</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5494</v>
+        <v>-0.5427</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.5675</v>
+        <v>-1.55</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.0589</v>
+        <v>-2.0338</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4796</v>
+        <v>-1.4222</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.5793</v>
+        <v>-0.6116</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4796</v>
+        <v>-1.4222</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7693</v>
+        <v>-0.768</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5793</v>
+        <v>-0.6116</v>
       </c>
       <c r="K39" t="n">
         <v>205</v>
@@ -2231,7 +2231,7 @@
         <v>55</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3486</v>
+        <v>-1.3796</v>
       </c>
       <c r="N39" t="n">
         <v>260</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3467</v>
+        <v>-2.3813</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6262</v>
+        <v>-0.6355</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6974</v>
+        <v>-1.7082</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3467</v>
+        <v>-2.3813</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.3467</v>
+        <v>-2.3813</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.3467</v>
+        <v>-2.3813</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.3467</v>
+        <v>-2.3813</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.3467</v>
+        <v>-2.3813</v>
       </c>
       <c r="N40" t="n">
         <v>192</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.0525</v>
+        <v>-3.8513</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0814</v>
+        <v>-1.0277</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.4675</v>
+        <v>-2.3774</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.0525</v>
+        <v>-3.8513</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.2934</v>
+        <v>-3.0662</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.7591</v>
+        <v>-0.7851</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.2934</v>
+        <v>-3.0662</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7124</v>
+        <v>-1.6557</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7591</v>
+        <v>-0.7851</v>
       </c>
       <c r="K41" t="n">
         <v>205</v>
@@ -2323,7 +2323,7 @@
         <v>55</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4715</v>
+        <v>-2.4408</v>
       </c>
       <c r="N41" t="n">
         <v>260</v>
@@ -2429,10 +2429,10 @@
         <v>1.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9019</v>
+        <v>0.849</v>
       </c>
       <c r="J2" t="n">
-        <v>25.2532</v>
+        <v>23.772</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9019</v>
+        <v>0.849</v>
       </c>
       <c r="J3" t="n">
-        <v>25.2532</v>
+        <v>23.772</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6737</v>
+        <v>0.6478</v>
       </c>
       <c r="J4" t="n">
-        <v>18.8636</v>
+        <v>18.1384</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5578</v>
+        <v>0.5436</v>
       </c>
       <c r="J5" t="n">
-        <v>15.6184</v>
+        <v>15.2208</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2872</v>
+        <v>-0.2709</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.041600000000001</v>
+        <v>-7.5852</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.43</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9164</v>
+        <v>0.8548</v>
       </c>
       <c r="J7" t="n">
-        <v>25.6592</v>
+        <v>23.9344</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0738</v>
+        <v>-0.0881</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0664</v>
+        <v>-2.4668</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.7</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3189</v>
+        <v>-0.3341</v>
       </c>
       <c r="J9" t="n">
-        <v>-8.9292</v>
+        <v>-9.354799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.66</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3568</v>
+        <v>-0.3707</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.990399999999999</v>
+        <v>-10.3796</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.57</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4407</v>
+        <v>-0.4508</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.3396</v>
+        <v>-12.6224</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.152</v>
+        <v>0.1543</v>
       </c>
       <c r="J12" t="n">
-        <v>3.496</v>
+        <v>3.5489</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0059</v>
+        <v>-0.014</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1357</v>
+        <v>-0.322</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.86</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1634</v>
+        <v>-0.1801</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.7582</v>
+        <v>-4.1423</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1735</v>
+        <v>-0.1903</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.9905</v>
+        <v>-4.3769</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4055</v>
+        <v>-0.4169</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.326499999999999</v>
+        <v>-9.588699999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.94</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0452</v>
+        <v>1.0428</v>
       </c>
       <c r="J17" t="n">
-        <v>24.0396</v>
+        <v>23.9844</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.45</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5638</v>
+        <v>0.57</v>
       </c>
       <c r="J18" t="n">
-        <v>12.9674</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0567</v>
+        <v>0.0732</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3041</v>
+        <v>1.6836</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0582</v>
+        <v>-0.0599</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3386</v>
+        <v>-1.3777</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.72</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3392</v>
+        <v>-0.3465</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.8016</v>
+        <v>-7.9695</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.47</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6874</v>
+        <v>0.6663</v>
       </c>
       <c r="J22" t="n">
-        <v>17.8724</v>
+        <v>17.3238</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.99</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0215</v>
+        <v>-0.0259</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.6734</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.037</v>
+        <v>-0.0435</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.962</v>
+        <v>-1.131</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.3244</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.68</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3564</v>
+        <v>-0.367</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.266400000000001</v>
+        <v>-9.542</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.44</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5923</v>
       </c>
       <c r="J27" t="n">
-        <v>15.4778</v>
+        <v>15.3998</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2643</v>
+        <v>0.2774</v>
       </c>
       <c r="J28" t="n">
-        <v>6.8718</v>
+        <v>7.2124</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.12</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1968</v>
+        <v>0.2107</v>
       </c>
       <c r="J29" t="n">
-        <v>5.1168</v>
+        <v>5.4782</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.03</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0616</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>1.6016</v>
+        <v>1.859</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.45</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.5674</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.742</v>
+        <v>-14.7524</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6291</v>
+        <v>0.5881</v>
       </c>
       <c r="J32" t="n">
-        <v>22.6476</v>
+        <v>21.1716</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2854</v>
+        <v>0.2771</v>
       </c>
       <c r="J33" t="n">
-        <v>10.2744</v>
+        <v>9.9756</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2536</v>
+        <v>0.2474</v>
       </c>
       <c r="J34" t="n">
-        <v>9.1296</v>
+        <v>8.9064</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.67</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9267</v>
+        <v>-0.8583</v>
       </c>
       <c r="J35" t="n">
-        <v>-33.3612</v>
+        <v>-30.8988</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.67</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9267</v>
+        <v>-0.8583</v>
       </c>
       <c r="J36" t="n">
-        <v>-33.3612</v>
+        <v>-30.8988</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.53</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9436</v>
+        <v>0.9002</v>
       </c>
       <c r="J37" t="n">
-        <v>33.9696</v>
+        <v>32.4072</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.18</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3709</v>
+        <v>0.3769</v>
       </c>
       <c r="J38" t="n">
-        <v>13.3524</v>
+        <v>13.5684</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.08</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1848</v>
+        <v>0.1981</v>
       </c>
       <c r="J39" t="n">
-        <v>6.6528</v>
+        <v>7.1316</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0892</v>
+        <v>-0.0963</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.2112</v>
+        <v>-3.4668</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1481</v>
+        <v>-0.1577</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.3316</v>
+        <v>-5.6772</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.65</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3181</v>
+        <v>1.3969</v>
       </c>
       <c r="J42" t="n">
-        <v>31.6344</v>
+        <v>33.5256</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.45</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0675</v>
+        <v>1.0346</v>
       </c>
       <c r="J43" t="n">
-        <v>25.62</v>
+        <v>24.8304</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.33</v>
       </c>
       <c r="I44" t="n">
-        <v>0.85</v>
+        <v>0.8047</v>
       </c>
       <c r="J44" t="n">
-        <v>20.4</v>
+        <v>19.3128</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.98</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1556</v>
+        <v>-0.1425</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.7344</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6594</v>
+        <v>-0.6095</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.8256</v>
+        <v>-14.628</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.22</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5023</v>
+        <v>0.4874</v>
       </c>
       <c r="J47" t="n">
-        <v>12.0552</v>
+        <v>11.6976</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.06</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1803</v>
+        <v>0.1836</v>
       </c>
       <c r="J48" t="n">
-        <v>4.3272</v>
+        <v>4.4064</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1572</v>
+        <v>0.1608</v>
       </c>
       <c r="J49" t="n">
-        <v>3.7728</v>
+        <v>3.8592</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.82</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2102</v>
+        <v>-0.2257</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.0448</v>
+        <v>-5.4168</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.49</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5214</v>
+        <v>-0.5259</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.5136</v>
+        <v>-12.6216</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.84</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2208</v>
+        <v>1.3422</v>
       </c>
       <c r="J52" t="n">
-        <v>26.8576</v>
+        <v>29.5284</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.6</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9429</v>
+        <v>1.0469</v>
       </c>
       <c r="J53" t="n">
-        <v>20.7438</v>
+        <v>23.0318</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.44</v>
       </c>
       <c r="I54" t="n">
-        <v>0.754</v>
+        <v>0.8421</v>
       </c>
       <c r="J54" t="n">
-        <v>16.588</v>
+        <v>18.5262</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.26</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5869</v>
       </c>
       <c r="J55" t="n">
-        <v>11.4994</v>
+        <v>12.9118</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.1</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2465</v>
+        <v>0.2711</v>
       </c>
       <c r="J56" t="n">
-        <v>5.423</v>
+        <v>5.9642</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.91</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0767</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.6874</v>
+        <v>-2.189</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.79</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2114</v>
+        <v>-0.2333</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.6508</v>
+        <v>-5.1326</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.67</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3248</v>
+        <v>-0.3441</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.1456</v>
+        <v>-7.5702</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3341</v>
+        <v>-0.353</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.3502</v>
+        <v>-7.766</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.49</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4927</v>
+        <v>-0.5033</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.8394</v>
+        <v>-11.0726</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.23</v>
       </c>
       <c r="I62" t="n">
-        <v>1.6221</v>
+        <v>1.7659</v>
       </c>
       <c r="J62" t="n">
-        <v>30.8199</v>
+        <v>33.5521</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.8</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1528</v>
+        <v>1.2745</v>
       </c>
       <c r="J63" t="n">
-        <v>21.9032</v>
+        <v>24.2155</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.33</v>
       </c>
       <c r="I64" t="n">
-        <v>0.602</v>
+        <v>0.6783</v>
       </c>
       <c r="J64" t="n">
-        <v>11.438</v>
+        <v>12.8877</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.33</v>
       </c>
       <c r="I65" t="n">
-        <v>0.602</v>
+        <v>0.6783</v>
       </c>
       <c r="J65" t="n">
-        <v>11.438</v>
+        <v>12.8877</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.19</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4079</v>
+        <v>0.4617</v>
       </c>
       <c r="J66" t="n">
-        <v>7.7501</v>
+        <v>8.7723</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.63</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.3181</v>
+        <v>-0.3457</v>
       </c>
       <c r="J67" t="n">
-        <v>-6.0439</v>
+        <v>-6.5683</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.58</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3701</v>
+        <v>-0.3944</v>
       </c>
       <c r="J68" t="n">
-        <v>-7.0319</v>
+        <v>-7.4936</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.48</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4632</v>
+        <v>-0.4817</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.800800000000001</v>
+        <v>-9.1523</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.43</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5098</v>
+        <v>-0.5249</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.686199999999999</v>
+        <v>-9.973100000000001</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.37</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5681</v>
+        <v>-0.5786</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.7939</v>
+        <v>-10.9934</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.79</v>
       </c>
       <c r="I72" t="n">
-        <v>1.242</v>
+        <v>1.3515</v>
       </c>
       <c r="J72" t="n">
-        <v>34.776</v>
+        <v>37.842</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.652</v>
+        <v>0.7215</v>
       </c>
       <c r="J73" t="n">
-        <v>18.256</v>
+        <v>20.202</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3988</v>
+        <v>0.4355</v>
       </c>
       <c r="J74" t="n">
-        <v>11.1664</v>
+        <v>12.194</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.78</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.7177</v>
+        <v>-0.6647</v>
       </c>
       <c r="J75" t="n">
-        <v>-20.0956</v>
+        <v>-18.6116</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.77</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7431</v>
+        <v>-0.6871</v>
       </c>
       <c r="J76" t="n">
-        <v>-20.8068</v>
+        <v>-19.2388</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.09</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2552</v>
+        <v>0.2541</v>
       </c>
       <c r="J77" t="n">
-        <v>7.1456</v>
+        <v>7.1148</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2335</v>
+        <v>0.2332</v>
       </c>
       <c r="J78" t="n">
-        <v>6.538</v>
+        <v>6.5296</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.02</v>
       </c>
       <c r="I79" t="n">
-        <v>0.089</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>2.492</v>
+        <v>2.5172</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.71</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3149</v>
+        <v>-0.3292</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.8172</v>
+        <v>-9.217599999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.61</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.409</v>
+        <v>-0.4197</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.452</v>
+        <v>-11.7516</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.61</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9902</v>
+        <v>1.0907</v>
       </c>
       <c r="J82" t="n">
-        <v>26.7354</v>
+        <v>29.4489</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.29</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5826</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>15.7302</v>
+        <v>17.5149</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.27</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5564</v>
+        <v>0.6194</v>
       </c>
       <c r="J84" t="n">
-        <v>15.0228</v>
+        <v>16.7238</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.25</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5303</v>
+        <v>0.59</v>
       </c>
       <c r="J85" t="n">
-        <v>14.3181</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.9</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4189</v>
+        <v>-0.391</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.3103</v>
+        <v>-10.557</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3334</v>
+        <v>0.3239</v>
       </c>
       <c r="J87" t="n">
-        <v>9.001799999999999</v>
+        <v>8.7453</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2071</v>
+        <v>-0.2255</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.5917</v>
+        <v>-6.0885</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.75</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2644</v>
+        <v>-0.2824</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.1388</v>
+        <v>-7.6248</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.73</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2836</v>
+        <v>-0.3011</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.6572</v>
+        <v>-8.1297</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.66</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3501</v>
+        <v>-0.3654</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.4527</v>
+        <v>-9.8658</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.31</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8636</v>
+        <v>0.806</v>
       </c>
       <c r="J92" t="n">
-        <v>30.226</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.3</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8396</v>
+        <v>0.7851</v>
       </c>
       <c r="J93" t="n">
-        <v>29.386</v>
+        <v>27.4785</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0152</v>
+        <v>-0.0104</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.532</v>
+        <v>-0.364</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.99</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.0699</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.4465</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.75</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7692</v>
+        <v>-0.7144</v>
       </c>
       <c r="J96" t="n">
-        <v>-26.922</v>
+        <v>-25.004</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.22</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4639</v>
+        <v>0.4592</v>
       </c>
       <c r="J97" t="n">
-        <v>16.2365</v>
+        <v>16.072</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2382</v>
+        <v>0.2466</v>
       </c>
       <c r="J98" t="n">
-        <v>8.337</v>
+        <v>8.631</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.218</v>
+        <v>0.227</v>
       </c>
       <c r="J99" t="n">
-        <v>7.63</v>
+        <v>7.945</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.08</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1974</v>
+        <v>0.207</v>
       </c>
       <c r="J100" t="n">
-        <v>6.909</v>
+        <v>7.245</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3496</v>
+        <v>-0.3599</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.236</v>
+        <v>-12.5965</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.46</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1153</v>
+        <v>1.071</v>
       </c>
       <c r="J102" t="n">
-        <v>30.1131</v>
+        <v>28.917</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.796</v>
       </c>
       <c r="J103" t="n">
-        <v>22.9311</v>
+        <v>21.492</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1085</v>
+        <v>0.1208</v>
       </c>
       <c r="J104" t="n">
-        <v>2.9295</v>
+        <v>3.2616</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.88</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4355</v>
+        <v>-0.4147</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.7585</v>
+        <v>-11.1969</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.84</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5453</v>
+        <v>-0.5141</v>
       </c>
       <c r="J106" t="n">
-        <v>-14.7231</v>
+        <v>-13.8807</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.61</v>
       </c>
       <c r="I107" t="n">
-        <v>1.0652</v>
+        <v>1.028</v>
       </c>
       <c r="J107" t="n">
-        <v>28.7604</v>
+        <v>27.756</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2378</v>
+        <v>0.2463</v>
       </c>
       <c r="J108" t="n">
-        <v>6.4206</v>
+        <v>6.6501</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1971</v>
+        <v>0.2067</v>
       </c>
       <c r="J109" t="n">
-        <v>5.3217</v>
+        <v>5.5809</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.78</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2632</v>
+        <v>-0.2755</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.1064</v>
+        <v>-7.4385</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.62</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4148</v>
+        <v>-0.4227</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.1996</v>
+        <v>-11.4129</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7482</v>
+        <v>0.7167</v>
       </c>
       <c r="J112" t="n">
-        <v>20.2014</v>
+        <v>19.3509</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.04</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1136</v>
+        <v>0.1228</v>
       </c>
       <c r="J113" t="n">
-        <v>3.0672</v>
+        <v>3.3156</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1132</v>
+        <v>-0.1248</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.0564</v>
+        <v>-3.3696</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.89</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1468</v>
+        <v>-0.1594</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.9636</v>
+        <v>-4.3038</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2</v>
+        <v>-0.2132</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.4</v>
+        <v>-5.7564</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.42</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0688</v>
+        <v>1.016</v>
       </c>
       <c r="J117" t="n">
-        <v>28.8576</v>
+        <v>27.432</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.25</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7141</v>
+        <v>0.6757</v>
       </c>
       <c r="J118" t="n">
-        <v>19.2807</v>
+        <v>18.2439</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1506</v>
+        <v>-0.1496</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.0662</v>
+        <v>-4.0392</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.89</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4005</v>
+        <v>-0.3842</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.8135</v>
+        <v>-10.3734</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4568</v>
+        <v>-0.4355</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.3336</v>
+        <v>-11.7585</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.35</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7217</v>
+        <v>0.6889</v>
       </c>
       <c r="J122" t="n">
-        <v>21.651</v>
+        <v>20.667</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.99</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0174</v>
+        <v>-0.0229</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.522</v>
+        <v>-0.6870000000000001</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.98</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.033</v>
+        <v>-0.0405</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.99</v>
+        <v>-1.215</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.82</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2139</v>
+        <v>-0.2285</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.417</v>
+        <v>-6.855</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.65</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3785</v>
+        <v>-0.3893</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.355</v>
+        <v>-11.679</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.39</v>
       </c>
       <c r="I127" t="n">
-        <v>1.015</v>
+        <v>0.9542</v>
       </c>
       <c r="J127" t="n">
-        <v>30.45</v>
+        <v>28.626</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.17</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5044</v>
+        <v>0.4909</v>
       </c>
       <c r="J128" t="n">
-        <v>15.132</v>
+        <v>14.727</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.14</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4271</v>
+        <v>0.4207</v>
       </c>
       <c r="J129" t="n">
-        <v>12.813</v>
+        <v>12.621</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0255</v>
+        <v>-0.0175</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.765</v>
+        <v>-0.525</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.85</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5199</v>
+        <v>-0.4909</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.597</v>
+        <v>-14.727</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.13</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5109</v>
+        <v>0.461</v>
       </c>
       <c r="J132" t="n">
-        <v>10.7289</v>
+        <v>9.680999999999999</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.58</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3974</v>
+        <v>-0.4153</v>
       </c>
       <c r="J133" t="n">
-        <v>-8.3454</v>
+        <v>-8.721299999999999</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.52</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4533</v>
+        <v>-0.4681</v>
       </c>
       <c r="J134" t="n">
-        <v>-9.519299999999999</v>
+        <v>-9.8301</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.5</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4721</v>
+        <v>-0.4857</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.914099999999999</v>
+        <v>-10.1997</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.46</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5098</v>
+        <v>-0.5208</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.7058</v>
+        <v>-10.9368</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.01</v>
       </c>
       <c r="I137" t="n">
-        <v>1.6689</v>
+        <v>1.6752</v>
       </c>
       <c r="J137" t="n">
-        <v>35.0469</v>
+        <v>35.1792</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.64</v>
       </c>
       <c r="I138" t="n">
-        <v>1.2528</v>
+        <v>1.2351</v>
       </c>
       <c r="J138" t="n">
-        <v>26.3088</v>
+        <v>25.9371</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.55</v>
       </c>
       <c r="I139" t="n">
-        <v>1.1495</v>
+        <v>1.1237</v>
       </c>
       <c r="J139" t="n">
-        <v>24.1395</v>
+        <v>23.5977</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5916</v>
+        <v>0.5865</v>
       </c>
       <c r="J140" t="n">
-        <v>12.4236</v>
+        <v>12.3165</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.18</v>
       </c>
       <c r="I141" t="n">
-        <v>0.4444</v>
+        <v>0.4547</v>
       </c>
       <c r="J141" t="n">
-        <v>9.3324</v>
+        <v>9.5487</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5317</v>
+        <v>0.5157</v>
       </c>
       <c r="J142" t="n">
-        <v>15.4193</v>
+        <v>14.9553</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.1</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2615</v>
+        <v>0.2635</v>
       </c>
       <c r="J143" t="n">
-        <v>7.5835</v>
+        <v>7.6415</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.85</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1816</v>
+        <v>-0.1966</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.2664</v>
+        <v>-5.7014</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2225</v>
+        <v>-0.2374</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.4525</v>
+        <v>-6.8846</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3012</v>
+        <v>-0.3148</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.7348</v>
+        <v>-9.129200000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.49</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1351</v>
+        <v>1.0962</v>
       </c>
       <c r="J147" t="n">
-        <v>32.9179</v>
+        <v>31.7898</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.32</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8474</v>
+        <v>0.7988</v>
       </c>
       <c r="J148" t="n">
-        <v>24.5746</v>
+        <v>23.1652</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.16</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4674</v>
+        <v>0.46</v>
       </c>
       <c r="J149" t="n">
-        <v>13.5546</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.05</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1587</v>
+        <v>0.1739</v>
       </c>
       <c r="J150" t="n">
-        <v>4.6023</v>
+        <v>5.0431</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.85</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5367</v>
+        <v>-0.5027</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.5643</v>
+        <v>-14.5783</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.48</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6121</v>
+        <v>0.6127</v>
       </c>
       <c r="J152" t="n">
-        <v>16.5267</v>
+        <v>16.5429</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.26</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3589</v>
+        <v>0.3731</v>
       </c>
       <c r="J153" t="n">
-        <v>9.690300000000001</v>
+        <v>10.0737</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0975</v>
       </c>
       <c r="J154" t="n">
-        <v>2.2302</v>
+        <v>2.6325</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.014</v>
+        <v>-0.0108</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.378</v>
+        <v>-0.2916</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.0653</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J156" t="n">
-        <v>-1.7631</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.13</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2755</v>
+        <v>0.2734</v>
       </c>
       <c r="J157" t="n">
-        <v>7.4385</v>
+        <v>7.3818</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0599</v>
+        <v>-0.0738</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.6173</v>
+        <v>-1.9926</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.8</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2209</v>
+        <v>-0.2384</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.9643</v>
+        <v>-6.4368</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2601</v>
+        <v>-0.277</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.0227</v>
+        <v>-7.479</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.62</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3933</v>
+        <v>-0.4058</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.6191</v>
+        <v>-10.9566</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.81</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2467</v>
+        <v>1.2295</v>
       </c>
       <c r="J162" t="n">
-        <v>33.6609</v>
+        <v>33.1965</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.22</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4622</v>
+        <v>0.4579</v>
       </c>
       <c r="J163" t="n">
-        <v>12.4794</v>
+        <v>12.3633</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1716</v>
+        <v>-0.1839</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.6332</v>
+        <v>-4.9653</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.76</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2833</v>
+        <v>-0.2951</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.6491</v>
+        <v>-7.9677</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.55</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4786</v>
+        <v>-0.4836</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.9222</v>
+        <v>-13.0572</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.29</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8056</v>
+        <v>0.7571</v>
       </c>
       <c r="J167" t="n">
-        <v>21.7512</v>
+        <v>20.4417</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.22</v>
       </c>
       <c r="I168" t="n">
-        <v>0.635</v>
+        <v>0.6067</v>
       </c>
       <c r="J168" t="n">
-        <v>17.145</v>
+        <v>16.3809</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.2</v>
       </c>
       <c r="I169" t="n">
-        <v>0.585</v>
+        <v>0.5622</v>
       </c>
       <c r="J169" t="n">
-        <v>15.795</v>
+        <v>15.1794</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0214</v>
+        <v>-0.0146</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.5778</v>
+        <v>-0.3942</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.76</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.6968</v>
       </c>
       <c r="J171" t="n">
-        <v>-20.2635</v>
+        <v>-18.8136</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.11</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4345</v>
+        <v>0.3958</v>
       </c>
       <c r="J172" t="n">
-        <v>9.558999999999999</v>
+        <v>8.707599999999999</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.79</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2036</v>
+        <v>-0.2272</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.4792</v>
+        <v>-4.9984</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.66</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3295</v>
+        <v>-0.3494</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.249</v>
+        <v>-7.6868</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.45</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5339</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.5434</v>
+        <v>-11.7458</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.34</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6281</v>
+        <v>-0.6296</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.8182</v>
+        <v>-13.8512</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.44</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0336</v>
+        <v>0.9881</v>
       </c>
       <c r="J177" t="n">
-        <v>22.7392</v>
+        <v>21.7382</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.43</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0193</v>
+        <v>0.9717</v>
       </c>
       <c r="J178" t="n">
-        <v>22.4246</v>
+        <v>21.3774</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.36</v>
       </c>
       <c r="I179" t="n">
-        <v>0.893</v>
+        <v>0.8469</v>
       </c>
       <c r="J179" t="n">
-        <v>19.646</v>
+        <v>18.6318</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.32</v>
       </c>
       <c r="I180" t="n">
-        <v>0.8073</v>
+        <v>0.7713</v>
       </c>
       <c r="J180" t="n">
-        <v>17.7606</v>
+        <v>16.9686</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.27</v>
       </c>
       <c r="I181" t="n">
-        <v>0.6947</v>
+        <v>0.6717</v>
       </c>
       <c r="J181" t="n">
-        <v>15.2834</v>
+        <v>14.7774</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.11</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2778</v>
+        <v>0.28</v>
       </c>
       <c r="J182" t="n">
-        <v>10.0008</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.1</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2573</v>
+        <v>0.2604</v>
       </c>
       <c r="J183" t="n">
-        <v>9.2628</v>
+        <v>9.3744</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.99</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0176</v>
+        <v>-0.023</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.828</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1075</v>
+        <v>-0.1204</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.87</v>
+        <v>-4.3344</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.68</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3505</v>
+        <v>-0.3624</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.618</v>
+        <v>-13.0464</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.14</v>
       </c>
       <c r="I187" t="n">
-        <v>0.439</v>
+        <v>0.4289</v>
       </c>
       <c r="J187" t="n">
-        <v>15.804</v>
+        <v>15.4404</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.13</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4122</v>
+        <v>0.4045</v>
       </c>
       <c r="J188" t="n">
-        <v>14.8392</v>
+        <v>14.562</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.385</v>
+        <v>0.3797</v>
       </c>
       <c r="J189" t="n">
-        <v>13.86</v>
+        <v>13.6692</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.98</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1092</v>
+        <v>-0.1102</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.9312</v>
+        <v>-3.9672</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.95</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2144</v>
+        <v>-0.2121</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.7184</v>
+        <v>-7.6356</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.38</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8732</v>
+        <v>0.8094</v>
       </c>
       <c r="J192" t="n">
-        <v>21.83</v>
+        <v>20.235</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.78</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2341</v>
+        <v>-0.2528</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.8525</v>
+        <v>-6.32</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.7</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3102</v>
+        <v>-0.3273</v>
       </c>
       <c r="J194" t="n">
-        <v>-7.755</v>
+        <v>-8.182499999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.61</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3951</v>
+        <v>-0.4088</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.8775</v>
+        <v>-10.22</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.52</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4787</v>
+        <v>-0.488</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.9675</v>
+        <v>-12.2</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.65</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3125</v>
+        <v>1.2898</v>
       </c>
       <c r="J197" t="n">
-        <v>32.8125</v>
+        <v>32.245</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.27</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7113</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J198" t="n">
-        <v>17.7825</v>
+        <v>17.075</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.27</v>
       </c>
       <c r="I199" t="n">
-        <v>0.7113</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>17.7825</v>
+        <v>17.075</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.14</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3964</v>
+        <v>0.3998</v>
       </c>
       <c r="J200" t="n">
-        <v>9.91</v>
+        <v>9.994999999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.0648</v>
+        <v>-0.0449</v>
       </c>
       <c r="J201" t="n">
-        <v>-1.62</v>
+        <v>-1.1225</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.61</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2649</v>
+        <v>1.2389</v>
       </c>
       <c r="J202" t="n">
-        <v>29.0927</v>
+        <v>28.4947</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.57</v>
       </c>
       <c r="I203" t="n">
-        <v>1.2154</v>
+        <v>1.1861</v>
       </c>
       <c r="J203" t="n">
-        <v>27.9542</v>
+        <v>27.2803</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.47</v>
       </c>
       <c r="I204" t="n">
-        <v>1.09</v>
+        <v>1.0505</v>
       </c>
       <c r="J204" t="n">
-        <v>25.07</v>
+        <v>24.1615</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.87</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5027</v>
+        <v>-0.4678</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.5621</v>
+        <v>-10.7594</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.78</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7399</v>
+        <v>-0.6804</v>
       </c>
       <c r="J206" t="n">
-        <v>-17.0177</v>
+        <v>-15.6492</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.14</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3875</v>
+        <v>0.3734</v>
       </c>
       <c r="J207" t="n">
-        <v>8.9125</v>
+        <v>8.588200000000001</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.99</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0015</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J208" t="n">
-        <v>0.0345</v>
+        <v>-0.2024</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.79</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.229</v>
+        <v>-0.2468</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.267</v>
+        <v>-5.6764</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.76</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2582</v>
+        <v>-0.2755</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.9386</v>
+        <v>-6.3365</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.51</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4931</v>
+        <v>-0.5008</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.3413</v>
+        <v>-11.5184</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.57</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2018</v>
+        <v>1.1741</v>
       </c>
       <c r="J212" t="n">
-        <v>28.8432</v>
+        <v>28.1784</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.37</v>
       </c>
       <c r="I213" t="n">
-        <v>0.9192</v>
+        <v>0.8694</v>
       </c>
       <c r="J213" t="n">
-        <v>22.0608</v>
+        <v>20.8656</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.26</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6795</v>
+        <v>0.6566</v>
       </c>
       <c r="J214" t="n">
-        <v>16.308</v>
+        <v>15.7584</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.25</v>
       </c>
       <c r="I215" t="n">
-        <v>0.6563</v>
+        <v>0.636</v>
       </c>
       <c r="J215" t="n">
-        <v>15.7512</v>
+        <v>15.264</v>
       </c>
     </row>
     <row r="216">
@@ -11029,10 +11029,10 @@
         <v>1.31</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6821</v>
+        <v>0.6483</v>
       </c>
       <c r="J217" t="n">
-        <v>16.3704</v>
+        <v>15.5592</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.18</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4401</v>
+        <v>0.4275</v>
       </c>
       <c r="J218" t="n">
-        <v>10.5624</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2164</v>
+        <v>-0.2327</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.1936</v>
+        <v>-5.5848</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.61</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4082</v>
+        <v>-0.4191</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.796799999999999</v>
+        <v>-10.0584</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.57</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4452</v>
+        <v>-0.4543</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.6848</v>
+        <v>-10.9032</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8562</v>
+        <v>0.8343</v>
       </c>
       <c r="J222" t="n">
-        <v>30.8232</v>
+        <v>30.0348</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.06</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1074</v>
+        <v>0.1207</v>
       </c>
       <c r="J223" t="n">
-        <v>3.8664</v>
+        <v>4.3452</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.02</v>
       </c>
       <c r="I224" t="n">
-        <v>0.04</v>
+        <v>0.0493</v>
       </c>
       <c r="J224" t="n">
-        <v>1.44</v>
+        <v>1.7748</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.9</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1422</v>
+        <v>-0.1531</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.1192</v>
+        <v>-5.5116</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.7</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3439</v>
+        <v>-0.3537</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.3804</v>
+        <v>-12.7332</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.5</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6891</v>
+        <v>0.6732</v>
       </c>
       <c r="J227" t="n">
-        <v>24.8076</v>
+        <v>24.2352</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.33</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4801</v>
+        <v>0.4808</v>
       </c>
       <c r="J228" t="n">
-        <v>17.2836</v>
+        <v>17.3088</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.17</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2707</v>
+        <v>0.2825</v>
       </c>
       <c r="J229" t="n">
-        <v>9.745200000000001</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2015</v>
+        <v>-0.2121</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.254</v>
+        <v>-7.6356</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.77</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2821</v>
+        <v>-0.2922</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.1556</v>
+        <v>-10.5192</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.03</v>
       </c>
       <c r="I232" t="n">
-        <v>0.1055</v>
+        <v>0.1098</v>
       </c>
       <c r="J232" t="n">
-        <v>2.743</v>
+        <v>2.8548</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>0.0109</v>
+        <v>0.0078</v>
       </c>
       <c r="J233" t="n">
-        <v>0.2834</v>
+        <v>0.2028</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.98</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.031</v>
+        <v>-0.0389</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.806</v>
+        <v>-1.0114</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.93</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0941</v>
+        <v>-0.107</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.4466</v>
+        <v>-2.782</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.75</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2809</v>
+        <v>-0.2951</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.3034</v>
+        <v>-7.6726</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.55</v>
       </c>
       <c r="I237" t="n">
-        <v>1.2228</v>
+        <v>1.188</v>
       </c>
       <c r="J237" t="n">
-        <v>31.7928</v>
+        <v>30.888</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.18</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5089</v>
       </c>
       <c r="J238" t="n">
-        <v>13.5902</v>
+        <v>13.2314</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.11</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3439</v>
+        <v>0.3453</v>
       </c>
       <c r="J239" t="n">
-        <v>8.9414</v>
+        <v>8.9778</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.99</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0876</v>
+        <v>-0.0823</v>
       </c>
       <c r="J240" t="n">
-        <v>-2.2776</v>
+        <v>-2.1398</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.86</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5002</v>
+        <v>-0.4716</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.0052</v>
+        <v>-12.2616</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>0.86</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.1011</v>
+        <v>-0.1315</v>
       </c>
       <c r="J242" t="n">
-        <v>-2.022</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.72</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2581</v>
+        <v>-0.2834</v>
       </c>
       <c r="J243" t="n">
-        <v>-5.162</v>
+        <v>-5.668</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.61</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3653</v>
+        <v>-0.3857</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.306</v>
+        <v>-7.714</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4092</v>
+        <v>-0.4277</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.183999999999999</v>
+        <v>-8.554</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.25</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7043</v>
+        <v>-0.7006</v>
       </c>
       <c r="J246" t="n">
-        <v>-14.086</v>
+        <v>-14.012</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.81</v>
       </c>
       <c r="I247" t="n">
-        <v>1.4468</v>
+        <v>1.4415</v>
       </c>
       <c r="J247" t="n">
-        <v>28.936</v>
+        <v>28.83</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>1.2763</v>
+        <v>1.2602</v>
       </c>
       <c r="J248" t="n">
-        <v>25.526</v>
+        <v>25.204</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.51</v>
       </c>
       <c r="I249" t="n">
-        <v>1.1044</v>
+        <v>1.0743</v>
       </c>
       <c r="J249" t="n">
-        <v>22.088</v>
+        <v>21.486</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.33</v>
       </c>
       <c r="I250" t="n">
-        <v>0.7997</v>
+        <v>0.7702</v>
       </c>
       <c r="J250" t="n">
-        <v>15.994</v>
+        <v>15.404</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>1.29</v>
       </c>
       <c r="I251" t="n">
-        <v>0.7093</v>
+        <v>0.6906</v>
       </c>
       <c r="J251" t="n">
-        <v>14.186</v>
+        <v>13.812</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.31</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6212</v>
+        <v>0.6034</v>
       </c>
       <c r="J252" t="n">
-        <v>18.0148</v>
+        <v>17.4986</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.19</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4096</v>
+        <v>0.4088</v>
       </c>
       <c r="J253" t="n">
-        <v>11.8784</v>
+        <v>11.8552</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.05</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1331</v>
+        <v>0.1435</v>
       </c>
       <c r="J254" t="n">
-        <v>3.8599</v>
+        <v>4.1615</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1602</v>
+        <v>-0.1725</v>
       </c>
       <c r="J255" t="n">
-        <v>-4.6458</v>
+        <v>-5.0025</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.75</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2923</v>
+        <v>-0.3041</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.476699999999999</v>
+        <v>-8.818899999999999</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.46</v>
       </c>
       <c r="I257" t="n">
-        <v>1.11</v>
+        <v>1.0662</v>
       </c>
       <c r="J257" t="n">
-        <v>32.19</v>
+        <v>30.9198</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.22</v>
       </c>
       <c r="I258" t="n">
-        <v>0.626</v>
+        <v>0.6005</v>
       </c>
       <c r="J258" t="n">
-        <v>18.154</v>
+        <v>17.4145</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1715</v>
+        <v>0.1827</v>
       </c>
       <c r="J259" t="n">
-        <v>4.9735</v>
+        <v>5.2983</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2301</v>
+        <v>-0.2231</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.6729</v>
+        <v>-6.4699</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.93</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2936</v>
+        <v>-0.2829</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.5144</v>
+        <v>-8.2041</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.61</v>
       </c>
       <c r="I262" t="n">
-        <v>0.7071</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="J262" t="n">
-        <v>14.8491</v>
+        <v>14.8722</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.56</v>
       </c>
       <c r="I263" t="n">
-        <v>0.6558</v>
+        <v>0.6605</v>
       </c>
       <c r="J263" t="n">
-        <v>13.7718</v>
+        <v>13.8705</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.51</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6042</v>
+        <v>0.6122</v>
       </c>
       <c r="J264" t="n">
-        <v>12.6882</v>
+        <v>12.8562</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.43</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5208</v>
+        <v>0.5335</v>
       </c>
       <c r="J265" t="n">
-        <v>10.9368</v>
+        <v>11.2035</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.8</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2747</v>
+        <v>-0.2805</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.7687</v>
+        <v>-5.8905</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.05</v>
       </c>
       <c r="I267" t="n">
-        <v>0.1565</v>
+        <v>0.1532</v>
       </c>
       <c r="J267" t="n">
-        <v>3.2865</v>
+        <v>3.2172</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.95</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0509</v>
+        <v>-0.0668</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.0689</v>
+        <v>-1.4028</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2347</v>
+        <v>-0.2533</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.9287</v>
+        <v>-5.3193</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.7</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3111</v>
+        <v>-0.328</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.5331</v>
+        <v>-6.888</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.54</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.461</v>
+        <v>-0.4712</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.680999999999999</v>
+        <v>-9.895200000000001</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.64</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0701</v>
+        <v>1.0381</v>
       </c>
       <c r="J272" t="n">
-        <v>32.103</v>
+        <v>31.143</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.21</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4252</v>
+        <v>0.4275</v>
       </c>
       <c r="J273" t="n">
-        <v>12.756</v>
+        <v>12.825</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.17</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3544</v>
+        <v>0.3611</v>
       </c>
       <c r="J274" t="n">
-        <v>10.632</v>
+        <v>10.833</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.8</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2521</v>
+        <v>-0.2627</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.563</v>
+        <v>-7.881</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.78</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2719</v>
+        <v>-0.2823</v>
       </c>
       <c r="J276" t="n">
-        <v>-8.157</v>
+        <v>-8.468999999999999</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.27</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8015</v>
+        <v>0.7458</v>
       </c>
       <c r="J277" t="n">
-        <v>24.045</v>
+        <v>22.374</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.06</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2302</v>
+        <v>0.2313</v>
       </c>
       <c r="J278" t="n">
-        <v>6.906</v>
+        <v>6.939</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.97</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1291</v>
+        <v>-0.1348</v>
       </c>
       <c r="J279" t="n">
-        <v>-3.873</v>
+        <v>-4.044</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5142</v>
+        <v>-0.4923</v>
       </c>
       <c r="J280" t="n">
-        <v>-15.426</v>
+        <v>-14.769</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.84</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5142</v>
+        <v>-0.4923</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.426</v>
+        <v>-14.769</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.49</v>
       </c>
       <c r="I282" t="n">
-        <v>0.6379</v>
+        <v>0.6343</v>
       </c>
       <c r="J282" t="n">
-        <v>17.8612</v>
+        <v>17.7604</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.2</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2942</v>
+        <v>0.3084</v>
       </c>
       <c r="J283" t="n">
-        <v>8.2376</v>
+        <v>8.635199999999999</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.13</v>
       </c>
       <c r="I284" t="n">
-        <v>0.2034</v>
+        <v>0.219</v>
       </c>
       <c r="J284" t="n">
-        <v>5.6952</v>
+        <v>6.132</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.89</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1556</v>
+        <v>-0.1663</v>
       </c>
       <c r="J285" t="n">
-        <v>-4.3568</v>
+        <v>-4.6564</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.76</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2888</v>
+        <v>-0.2994</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.086399999999999</v>
+        <v>-8.3832</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.45</v>
       </c>
       <c r="I287" t="n">
-        <v>0.668</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="J287" t="n">
-        <v>18.704</v>
+        <v>18.1356</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.25</v>
       </c>
       <c r="I288" t="n">
-        <v>0.406</v>
+        <v>0.4058</v>
       </c>
       <c r="J288" t="n">
-        <v>11.368</v>
+        <v>11.3624</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.95</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0755</v>
+        <v>-0.0858</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.114</v>
+        <v>-2.4024</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.71</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3263</v>
+        <v>-0.3381</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.1364</v>
+        <v>-9.466799999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.62</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4105</v>
+        <v>-0.4193</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.494</v>
+        <v>-11.7404</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.11</v>
       </c>
       <c r="I292" t="n">
-        <v>0.276</v>
+        <v>0.2787</v>
       </c>
       <c r="J292" t="n">
-        <v>9.66</v>
+        <v>9.7545</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.09</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2347</v>
+        <v>0.2391</v>
       </c>
       <c r="J293" t="n">
-        <v>8.214499999999999</v>
+        <v>8.368499999999999</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.0476</v>
+        <v>-0.0564</v>
       </c>
       <c r="J294" t="n">
-        <v>-1.666</v>
+        <v>-1.974</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.85</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.184</v>
+        <v>-0.1984</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.44</v>
+        <v>-6.944</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2249</v>
+        <v>-0.2393</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.8715</v>
+        <v>-8.375500000000001</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.26</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7401</v>
+        <v>0.6984</v>
       </c>
       <c r="J297" t="n">
-        <v>25.9035</v>
+        <v>24.444</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.12</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3819</v>
+        <v>0.3775</v>
       </c>
       <c r="J298" t="n">
-        <v>13.3665</v>
+        <v>13.2125</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.1152</v>
+        <v>0.1254</v>
       </c>
       <c r="J299" t="n">
-        <v>4.032</v>
+        <v>4.389</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.01</v>
       </c>
       <c r="I300" t="n">
-        <v>0.0379</v>
+        <v>0.0482</v>
       </c>
       <c r="J300" t="n">
-        <v>1.3265</v>
+        <v>1.687</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.96</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.1844</v>
+        <v>-0.1826</v>
       </c>
       <c r="J301" t="n">
-        <v>-6.454</v>
+        <v>-6.391</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>0.93</v>
       </c>
       <c r="I302" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.029</v>
       </c>
       <c r="J302" t="n">
-        <v>0.1824</v>
+        <v>-0.551</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.65</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.3205</v>
+        <v>-0.3444</v>
       </c>
       <c r="J303" t="n">
-        <v>-6.0895</v>
+        <v>-6.5436</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.62</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.35</v>
+        <v>-0.3723</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.65</v>
+        <v>-7.0737</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.38</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.5732</v>
+        <v>-0.5813</v>
       </c>
       <c r="J305" t="n">
-        <v>-10.8908</v>
+        <v>-11.0447</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.26</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6901</v>
+        <v>-0.6882</v>
       </c>
       <c r="J306" t="n">
-        <v>-13.1119</v>
+        <v>-13.0758</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>2.22</v>
       </c>
       <c r="I307" t="n">
-        <v>1.8338</v>
+        <v>1.9073</v>
       </c>
       <c r="J307" t="n">
-        <v>34.8422</v>
+        <v>36.2387</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.69</v>
       </c>
       <c r="I308" t="n">
-        <v>1.3063</v>
+        <v>1.2931</v>
       </c>
       <c r="J308" t="n">
-        <v>24.8197</v>
+        <v>24.5689</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.59</v>
       </c>
       <c r="I309" t="n">
-        <v>1.1927</v>
+        <v>1.171</v>
       </c>
       <c r="J309" t="n">
-        <v>22.6613</v>
+        <v>22.249</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.13</v>
       </c>
       <c r="I310" t="n">
-        <v>0.3086</v>
+        <v>0.3327</v>
       </c>
       <c r="J310" t="n">
-        <v>5.8634</v>
+        <v>6.3213</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>1.13</v>
       </c>
       <c r="I311" t="n">
-        <v>0.3086</v>
+        <v>0.3327</v>
       </c>
       <c r="J311" t="n">
-        <v>5.8634</v>
+        <v>6.3213</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>0.98</v>
       </c>
       <c r="I312" t="n">
-        <v>-0.0002</v>
+        <v>-0.0149</v>
       </c>
       <c r="J312" t="n">
-        <v>-0.004</v>
+        <v>-0.298</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.83</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1822</v>
+        <v>-0.2019</v>
       </c>
       <c r="J313" t="n">
-        <v>-3.644</v>
+        <v>-4.038</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.74</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2686</v>
+        <v>-0.2875</v>
       </c>
       <c r="J314" t="n">
-        <v>-5.372</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.67</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3345</v>
+        <v>-0.3516</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.69</v>
+        <v>-7.032</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.63</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3722</v>
+        <v>-0.3877</v>
       </c>
       <c r="J316" t="n">
-        <v>-7.444</v>
+        <v>-7.754</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.65</v>
       </c>
       <c r="I317" t="n">
-        <v>1.29</v>
+        <v>1.2699</v>
       </c>
       <c r="J317" t="n">
-        <v>25.8</v>
+        <v>25.398</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.41</v>
       </c>
       <c r="I318" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9372</v>
       </c>
       <c r="J318" t="n">
-        <v>19.748</v>
+        <v>18.744</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.32</v>
       </c>
       <c r="I319" t="n">
-        <v>0.8069</v>
+        <v>0.771</v>
       </c>
       <c r="J319" t="n">
-        <v>16.138</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.26</v>
       </c>
       <c r="I320" t="n">
-        <v>0.6711</v>
+        <v>0.6509</v>
       </c>
       <c r="J320" t="n">
-        <v>13.422</v>
+        <v>13.018</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>1.19</v>
       </c>
       <c r="I321" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5004</v>
       </c>
       <c r="J321" t="n">
-        <v>10.05</v>
+        <v>10.008</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.61</v>
       </c>
       <c r="I322" t="n">
-        <v>0.7269</v>
+        <v>0.7235</v>
       </c>
       <c r="J322" t="n">
-        <v>19.6263</v>
+        <v>19.5345</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.23</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3117</v>
+        <v>0.3299</v>
       </c>
       <c r="J323" t="n">
-        <v>8.415900000000001</v>
+        <v>8.907299999999999</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.2</v>
       </c>
       <c r="I324" t="n">
-        <v>0.2755</v>
+        <v>0.2945</v>
       </c>
       <c r="J324" t="n">
-        <v>7.4385</v>
+        <v>7.9515</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.17</v>
       </c>
       <c r="I325" t="n">
-        <v>0.238</v>
+        <v>0.2576</v>
       </c>
       <c r="J325" t="n">
-        <v>6.426</v>
+        <v>6.9552</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.14</v>
       </c>
       <c r="I326" t="n">
-        <v>0.1989</v>
+        <v>0.219</v>
       </c>
       <c r="J326" t="n">
-        <v>5.3703</v>
+        <v>5.913</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.25</v>
       </c>
       <c r="I327" t="n">
-        <v>0.4594</v>
+        <v>0.4462</v>
       </c>
       <c r="J327" t="n">
-        <v>12.4038</v>
+        <v>12.0474</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.9</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1184</v>
+        <v>-0.1348</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.1968</v>
+        <v>-3.6396</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.85</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1712</v>
+        <v>-0.1886</v>
       </c>
       <c r="J329" t="n">
-        <v>-4.6224</v>
+        <v>-5.0922</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.73</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.288</v>
+        <v>-0.3045</v>
       </c>
       <c r="J330" t="n">
-        <v>-7.776</v>
+        <v>-8.221500000000001</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.49</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5121</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="J331" t="n">
-        <v>-13.8267</v>
+        <v>-14.0022</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.06</v>
       </c>
       <c r="I332" t="n">
-        <v>0.1866</v>
+        <v>0.1882</v>
       </c>
       <c r="J332" t="n">
-        <v>4.8516</v>
+        <v>4.8932</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1</v>
       </c>
       <c r="I333" t="n">
-        <v>0.0185</v>
+        <v>0.0133</v>
       </c>
       <c r="J333" t="n">
-        <v>0.481</v>
+        <v>0.3458</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.96</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.0551</v>
+        <v>-0.0663</v>
       </c>
       <c r="J334" t="n">
-        <v>-1.4326</v>
+        <v>-1.7238</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.85</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.1772</v>
+        <v>-0.1932</v>
       </c>
       <c r="J335" t="n">
-        <v>-4.6072</v>
+        <v>-5.0232</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.67</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3536</v>
+        <v>-0.3665</v>
       </c>
       <c r="J336" t="n">
-        <v>-9.1936</v>
+        <v>-9.529</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.65</v>
       </c>
       <c r="I337" t="n">
-        <v>1.3135</v>
+        <v>1.2907</v>
       </c>
       <c r="J337" t="n">
-        <v>34.151</v>
+        <v>33.5582</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.54</v>
       </c>
       <c r="I338" t="n">
-        <v>1.1776</v>
+        <v>1.1458</v>
       </c>
       <c r="J338" t="n">
-        <v>30.6176</v>
+        <v>29.7908</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.15</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4235</v>
+        <v>0.4243</v>
       </c>
       <c r="J339" t="n">
-        <v>11.011</v>
+        <v>11.0318</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.12</v>
       </c>
       <c r="I340" t="n">
-        <v>0.3435</v>
+        <v>0.3513</v>
       </c>
       <c r="J340" t="n">
-        <v>8.930999999999999</v>
+        <v>9.133800000000001</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.85</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5578</v>
+        <v>-0.5175</v>
       </c>
       <c r="J341" t="n">
-        <v>-14.5028</v>
+        <v>-13.455</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3703/event_3703_evp_summary.xlsx
+++ b/database/event/3703/event_3703_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.312200000000001</v>
+        <v>8.104900000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2181</v>
+        <v>2.1628</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1597</v>
+        <v>3.0864</v>
       </c>
       <c r="E2" t="n">
-        <v>8.312200000000001</v>
+        <v>8.104900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.895</v>
+        <v>2.9148</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4172</v>
+        <v>5.1901</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6575</v>
+        <v>4.5009</v>
       </c>
       <c r="I2" t="n">
-        <v>2.515</v>
+        <v>2.5271</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4172</v>
+        <v>5.1901</v>
       </c>
       <c r="K2" t="n">
         <v>132</v>
@@ -529,7 +529,7 @@
         <v>178</v>
       </c>
       <c r="M2" t="n">
-        <v>7.9322</v>
+        <v>7.7172</v>
       </c>
       <c r="N2" t="n">
         <v>310</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5076</v>
+        <v>5.5138</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4697</v>
+        <v>1.4714</v>
       </c>
       <c r="D3" t="n">
-        <v>1.883</v>
+        <v>1.906</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5076</v>
+        <v>5.5138</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8237</v>
+        <v>2.8188</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6839</v>
+        <v>2.695</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4223</v>
+        <v>4.1404</v>
       </c>
       <c r="I3" t="n">
-        <v>2.388</v>
+        <v>2.3247</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6839</v>
+        <v>2.695</v>
       </c>
       <c r="K3" t="n">
         <v>158</v>
@@ -575,7 +575,7 @@
         <v>192</v>
       </c>
       <c r="M3" t="n">
-        <v>5.071899999999999</v>
+        <v>5.0197</v>
       </c>
       <c r="N3" t="n">
         <v>350</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4158</v>
+        <v>5.335</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4452</v>
+        <v>1.4237</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8412</v>
+        <v>1.8246</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4158</v>
+        <v>5.335</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9803</v>
+        <v>3.0045</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4355</v>
+        <v>2.3305</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9388</v>
+        <v>4.8375</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6669</v>
+        <v>2.7161</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4355</v>
+        <v>2.3305</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>178</v>
       </c>
       <c r="M4" t="n">
-        <v>5.1024</v>
+        <v>5.0466</v>
       </c>
       <c r="N4" t="n">
         <v>310</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3039</v>
+        <v>5.166</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4154</v>
+        <v>1.3786</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7902</v>
+        <v>1.7476</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3039</v>
+        <v>5.166</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5811</v>
+        <v>3.4728</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7228</v>
+        <v>1.6932</v>
       </c>
       <c r="H5" t="n">
-        <v>6.921</v>
+        <v>6.5959</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7373</v>
+        <v>3.7034</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7228</v>
+        <v>1.6932</v>
       </c>
       <c r="K5" t="n">
         <v>158</v>
@@ -667,7 +667,7 @@
         <v>192</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4601</v>
+        <v>5.396599999999999</v>
       </c>
       <c r="N5" t="n">
         <v>350</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8806</v>
+        <v>4.939</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3024</v>
+        <v>1.318</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5975</v>
+        <v>1.6442</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8806</v>
+        <v>4.939</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9631</v>
+        <v>2.9723</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9175</v>
+        <v>1.9667</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8823</v>
+        <v>4.7167</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6364</v>
+        <v>2.6483</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9175</v>
+        <v>1.9667</v>
       </c>
       <c r="K6" t="n">
         <v>158</v>
@@ -713,7 +713,7 @@
         <v>192</v>
       </c>
       <c r="M6" t="n">
-        <v>4.553900000000001</v>
+        <v>4.615</v>
       </c>
       <c r="N6" t="n">
         <v>350</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.8371</v>
+        <v>4.6524</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2908</v>
+        <v>1.2415</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5777</v>
+        <v>1.5136</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8371</v>
+        <v>4.6524</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2927</v>
+        <v>3.2423</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5444</v>
+        <v>1.4101</v>
       </c>
       <c r="H7" t="n">
-        <v>5.9697</v>
+        <v>5.7303</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2236</v>
+        <v>3.2174</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5444</v>
+        <v>1.4101</v>
       </c>
       <c r="K7" t="n">
         <v>132</v>
@@ -759,7 +759,7 @@
         <v>178</v>
       </c>
       <c r="M7" t="n">
-        <v>4.768</v>
+        <v>4.6275</v>
       </c>
       <c r="N7" t="n">
         <v>310</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5403</v>
+        <v>4.4507</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2116</v>
+        <v>1.1877</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4426</v>
+        <v>1.4217</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5403</v>
+        <v>4.4507</v>
       </c>
       <c r="F8" t="n">
-        <v>3.821</v>
+        <v>3.7208</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.7299</v>
       </c>
       <c r="H8" t="n">
-        <v>7.7127</v>
+        <v>7.527</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1648</v>
+        <v>4.2262</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.7299</v>
       </c>
       <c r="K8" t="n">
         <v>132</v>
@@ -805,7 +805,7 @@
         <v>178</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8841</v>
+        <v>4.9561</v>
       </c>
       <c r="N8" t="n">
         <v>310</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1602</v>
+        <v>4.0709</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1102</v>
+        <v>1.0863</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2696</v>
+        <v>1.2487</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1602</v>
+        <v>4.0709</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7117</v>
+        <v>2.7463</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4485</v>
+        <v>1.3246</v>
       </c>
       <c r="H9" t="n">
-        <v>4.0527</v>
+        <v>3.8681</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1884</v>
+        <v>2.1718</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4485</v>
+        <v>1.3246</v>
       </c>
       <c r="K9" t="n">
         <v>132</v>
@@ -851,7 +851,7 @@
         <v>178</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6369</v>
+        <v>3.4964</v>
       </c>
       <c r="N9" t="n">
         <v>310</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6378</v>
+        <v>3.4551</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9708</v>
+        <v>0.922</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0318</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6378</v>
+        <v>3.4551</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6092</v>
+        <v>3.4553</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0286</v>
+        <v>-0.0002</v>
       </c>
       <c r="H10" t="n">
-        <v>7.0138</v>
+        <v>6.5302</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7874</v>
+        <v>3.6665</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0286</v>
+        <v>-0.0002</v>
       </c>
       <c r="K10" t="n">
         <v>205</v>
@@ -897,7 +897,7 @@
         <v>55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.816</v>
+        <v>3.6663</v>
       </c>
       <c r="N10" t="n">
         <v>260</v>
@@ -906,139 +906,139 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0734</v>
+        <v>2.9617</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.7903</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7749</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0734</v>
+        <v>2.9617</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7632</v>
+        <v>2.4958</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6898</v>
+        <v>0.4659</v>
       </c>
       <c r="H11" t="n">
-        <v>7.522</v>
+        <v>2.9279</v>
       </c>
       <c r="I11" t="n">
-        <v>4.0618</v>
+        <v>1.6439</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6898</v>
+        <v>0.4659</v>
       </c>
       <c r="K11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L11" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.372</v>
+        <v>2.1098</v>
       </c>
       <c r="N11" t="n">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0143</v>
+        <v>2.9227</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8044</v>
+        <v>0.7799</v>
       </c>
       <c r="D12" t="n">
-        <v>0.748</v>
+        <v>0.7256</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0143</v>
+        <v>2.9227</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0143</v>
+        <v>3.591</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.6683</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8725</v>
+        <v>7.0394</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8725</v>
+        <v>3.9524</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.6683</v>
       </c>
       <c r="K12" t="n">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8725</v>
+        <v>3.2841</v>
       </c>
       <c r="N12" t="n">
-        <v>177</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9952</v>
+        <v>2.8767</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7993</v>
+        <v>0.7677</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7393</v>
+        <v>0.7047</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9952</v>
+        <v>2.8767</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4381</v>
+        <v>2.8767</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5571</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1499</v>
+        <v>3.6424</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7009</v>
+        <v>3.6424</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5571</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="L13" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.258</v>
+        <v>3.6424</v>
       </c>
       <c r="N13" t="n">
-        <v>260</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7804</v>
+        <v>2.7843</v>
       </c>
       <c r="C14" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6415</v>
+        <v>0.6626</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7804</v>
+        <v>2.7843</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3967</v>
+        <v>1.4505</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3837</v>
+        <v>1.3338</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3967</v>
+        <v>1.4505</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7542</v>
+        <v>0.8144</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3837</v>
+        <v>1.3338</v>
       </c>
       <c r="K14" t="n">
         <v>158</v>
@@ -1081,7 +1081,7 @@
         <v>192</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1379</v>
+        <v>2.1482</v>
       </c>
       <c r="N14" t="n">
         <v>350</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5928</v>
+        <v>2.5557</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6919</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5561</v>
+        <v>0.5585</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5928</v>
+        <v>2.5557</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0867</v>
+        <v>3.0296</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4939</v>
+        <v>-0.4739</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2901</v>
+        <v>4.9319</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8566</v>
+        <v>2.7691</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4939</v>
+        <v>-0.4739</v>
       </c>
       <c r="K15" t="n">
         <v>206</v>
@@ -1127,7 +1127,7 @@
         <v>41</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3627</v>
+        <v>2.2952</v>
       </c>
       <c r="N15" t="n">
         <v>247</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3364</v>
+        <v>2.5306</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.6753</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4394</v>
+        <v>0.547</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3364</v>
+        <v>2.5306</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3482</v>
+        <v>2.4415</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0118</v>
+        <v>0.0891</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8534</v>
+        <v>2.7239</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5408</v>
+        <v>1.5294</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0118</v>
+        <v>0.0891</v>
       </c>
       <c r="K16" t="n">
         <v>158</v>
@@ -1173,7 +1173,7 @@
         <v>192</v>
       </c>
       <c r="M16" t="n">
-        <v>1.529</v>
+        <v>1.6185</v>
       </c>
       <c r="N16" t="n">
         <v>350</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0601</v>
+        <v>1.8587</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5497</v>
+        <v>0.496</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3136</v>
+        <v>0.2409</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0601</v>
+        <v>1.8587</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0601</v>
+        <v>1.8587</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0601</v>
+        <v>1.8587</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0601</v>
+        <v>1.8587</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0601</v>
+        <v>1.8587</v>
       </c>
       <c r="N17" t="n">
         <v>141</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8235</v>
+        <v>1.5901</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4866</v>
+        <v>0.4243</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2059</v>
+        <v>0.1186</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8235</v>
+        <v>1.5901</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0347</v>
+        <v>1.809</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2112</v>
+        <v>-0.2189</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0347</v>
+        <v>1.809</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0987</v>
+        <v>1.0157</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2112</v>
+        <v>-0.2189</v>
       </c>
       <c r="K18" t="n">
         <v>205</v>
@@ -1265,7 +1265,7 @@
         <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8875</v>
+        <v>0.7968000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>260</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6167</v>
+        <v>1.5166</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4314</v>
+        <v>0.4047</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1118</v>
+        <v>0.0851</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6167</v>
+        <v>1.5166</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6167</v>
+        <v>1.5166</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6167</v>
+        <v>1.5166</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6167</v>
+        <v>1.5166</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6167</v>
+        <v>1.5166</v>
       </c>
       <c r="N19" t="n">
         <v>192</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4102</v>
+        <v>1.4143</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3763</v>
+        <v>0.3774</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0177</v>
+        <v>0.0385</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4102</v>
+        <v>1.4143</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4102</v>
+        <v>1.4143</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4102</v>
+        <v>1.4143</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4102</v>
+        <v>1.4143</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4102</v>
+        <v>1.4143</v>
       </c>
       <c r="N20" t="n">
-        <v>141</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3747</v>
+        <v>1.2793</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3668</v>
+        <v>0.3414</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0016</v>
+        <v>-0.023</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3747</v>
+        <v>1.2793</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3747</v>
+        <v>1.2793</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3747</v>
+        <v>1.2793</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3747</v>
+        <v>1.2793</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3747</v>
+        <v>1.2793</v>
       </c>
       <c r="N21" t="n">
-        <v>177</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2574</v>
+        <v>1.2356</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3355</v>
+        <v>0.3297</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0518</v>
+        <v>-0.0429</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2574</v>
+        <v>1.2356</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2574</v>
+        <v>1.2356</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2574</v>
+        <v>1.2356</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2574</v>
+        <v>1.2356</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2574</v>
+        <v>1.2356</v>
       </c>
       <c r="N22" t="n">
         <v>177</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8026</v>
+        <v>0.7006</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2142</v>
+        <v>0.187</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2588</v>
+        <v>-0.2866</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8026</v>
+        <v>0.7006</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6145</v>
+        <v>1.505</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8119</v>
+        <v>-0.8044</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6145</v>
+        <v>1.505</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8718</v>
+        <v>0.845</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8119</v>
+        <v>-0.8044</v>
       </c>
       <c r="K23" t="n">
         <v>206</v>
@@ -1495,7 +1495,7 @@
         <v>41</v>
       </c>
       <c r="M23" t="n">
-        <v>0.05990000000000006</v>
+        <v>0.04059999999999997</v>
       </c>
       <c r="N23" t="n">
         <v>247</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.6249</v>
       </c>
       <c r="C24" t="n">
-        <v>0.168</v>
+        <v>0.1668</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3376</v>
+        <v>-0.3211</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.6249</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.6249</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.6249</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.6249</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.6249</v>
       </c>
       <c r="N24" t="n">
         <v>192</v>
@@ -1550,124 +1550,124 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6163</v>
+        <v>0.4895</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1645</v>
+        <v>0.1306</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3437</v>
+        <v>-0.3828</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6163</v>
+        <v>0.4895</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6163</v>
+        <v>0.4895</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6163</v>
+        <v>0.4895</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6163</v>
+        <v>0.4895</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6163</v>
+        <v>0.4895</v>
       </c>
       <c r="N25" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5876</v>
+        <v>0.4814</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1568</v>
+        <v>0.1285</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3567</v>
+        <v>-0.3865</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5876</v>
+        <v>0.4814</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5876</v>
+        <v>0.4814</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5876</v>
+        <v>0.4814</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5876</v>
+        <v>0.4814</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5876</v>
+        <v>0.4814</v>
       </c>
       <c r="N26" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5788</v>
+        <v>0.4557</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1545</v>
+        <v>0.1216</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3607</v>
+        <v>-0.3982</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5788</v>
+        <v>0.4557</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5788</v>
+        <v>0.4557</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5788</v>
+        <v>0.4557</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5788</v>
+        <v>0.4557</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5788</v>
+        <v>0.4557</v>
       </c>
       <c r="N27" t="n">
         <v>141</v>
@@ -1688,78 +1688,78 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3371</v>
+        <v>0.222</v>
       </c>
       <c r="C28" t="n">
-        <v>0.09</v>
+        <v>0.0592</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4707</v>
+        <v>-0.5047</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3371</v>
+        <v>0.222</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3371</v>
+        <v>1.043</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.821</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3371</v>
+        <v>1.043</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3371</v>
+        <v>0.5856</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.821</v>
       </c>
       <c r="K28" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3371</v>
+        <v>-0.2353999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>192</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1972</v>
+        <v>0.1531</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0526</v>
+        <v>0.0409</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5344</v>
+        <v>-0.536</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1972</v>
+        <v>0.1531</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1972</v>
+        <v>0.1531</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1972</v>
+        <v>0.1531</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1972</v>
+        <v>0.1531</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1972</v>
+        <v>0.1531</v>
       </c>
       <c r="N29" t="n">
         <v>192</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0731</v>
+        <v>0.1126</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0195</v>
+        <v>0.03</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5909</v>
+        <v>-0.5545</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0731</v>
+        <v>0.1126</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0731</v>
+        <v>0.1126</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0731</v>
+        <v>0.1126</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0731</v>
+        <v>0.1126</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0731</v>
+        <v>0.1126</v>
       </c>
       <c r="N30" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0659</v>
+        <v>0.0941</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0176</v>
+        <v>0.0251</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5942</v>
+        <v>-0.5629</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0659</v>
+        <v>0.0941</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9006</v>
+        <v>0.0941</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.8347</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9006</v>
+        <v>0.0941</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4863</v>
+        <v>0.0941</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8347</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="L31" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3484</v>
+        <v>0.0941</v>
       </c>
       <c r="N31" t="n">
-        <v>247</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0532</v>
+        <v>0.0221</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0142</v>
+        <v>0.0059</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6</v>
+        <v>-0.5957</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0532</v>
+        <v>0.0221</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0532</v>
+        <v>0.0221</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0532</v>
+        <v>0.0221</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0532</v>
+        <v>0.0221</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0532</v>
+        <v>0.0221</v>
       </c>
       <c r="N32" t="n">
         <v>177</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0524</v>
+        <v>-0.1134</v>
       </c>
       <c r="C33" t="n">
-        <v>0.014</v>
+        <v>-0.0303</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.6574</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0524</v>
+        <v>-0.1134</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0524</v>
+        <v>-0.1134</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0524</v>
+        <v>-0.1134</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0524</v>
+        <v>-0.1134</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0524</v>
+        <v>-0.1134</v>
       </c>
       <c r="N33" t="n">
         <v>129</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2449</v>
+        <v>-0.2878</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0654</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7357</v>
+        <v>-0.7369</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2449</v>
+        <v>-0.2878</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2449</v>
+        <v>-0.2878</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2449</v>
+        <v>-0.2878</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2449</v>
+        <v>-0.2878</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2449</v>
+        <v>-0.2878</v>
       </c>
       <c r="N34" t="n">
         <v>129</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4259</v>
+        <v>-0.4805</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1137</v>
+        <v>-0.1282</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8181</v>
+        <v>-0.8247</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4259</v>
+        <v>-0.4805</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5195</v>
       </c>
       <c r="G35" t="n">
         <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5195</v>
       </c>
       <c r="I35" t="n">
-        <v>0.31</v>
+        <v>0.2917</v>
       </c>
       <c r="J35" t="n">
         <v>-1</v>
@@ -2047,7 +2047,7 @@
         <v>41</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.7082999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>247</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9635</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2571</v>
+        <v>-0.2541</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0628</v>
+        <v>-1.0395</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9635</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9635</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9635</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9635</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9635</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>129</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0749</v>
+        <v>-1.0689</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2868</v>
+        <v>-0.2852</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1135</v>
+        <v>-1.0927</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0749</v>
+        <v>-1.0689</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0749</v>
+        <v>-1.0689</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0749</v>
+        <v>-1.0689</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0749</v>
+        <v>-1.0689</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0749</v>
+        <v>-1.0689</v>
       </c>
       <c r="N37" t="n">
         <v>141</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4446</v>
+        <v>-1.368</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3855</v>
+        <v>-0.3651</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2818</v>
+        <v>-1.229</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4446</v>
+        <v>-1.368</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4446</v>
+        <v>-1.368</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4446</v>
+        <v>-1.368</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4446</v>
+        <v>-1.368</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4446</v>
+        <v>-1.368</v>
       </c>
       <c r="N38" t="n">
         <v>129</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.0338</v>
+        <v>-1.831</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5427</v>
+        <v>-0.4886</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.55</v>
+        <v>-1.4399</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.0338</v>
+        <v>-1.831</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4222</v>
+        <v>-1.2537</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.6116</v>
+        <v>-0.5773</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4222</v>
+        <v>-1.2537</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.768</v>
+        <v>-0.7039</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.6116</v>
+        <v>-0.5773</v>
       </c>
       <c r="K39" t="n">
         <v>205</v>
@@ -2231,7 +2231,7 @@
         <v>55</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3796</v>
+        <v>-1.2812</v>
       </c>
       <c r="N39" t="n">
         <v>260</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3813</v>
+        <v>-2.2288</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6355</v>
+        <v>-0.5948</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7082</v>
+        <v>-1.6211</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3813</v>
+        <v>-2.2288</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.3813</v>
+        <v>-2.2288</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.3813</v>
+        <v>-2.2288</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.3813</v>
+        <v>-2.2288</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.3813</v>
+        <v>-2.2288</v>
       </c>
       <c r="N40" t="n">
         <v>192</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.8513</v>
+        <v>-3.5844</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0277</v>
+        <v>-0.9565</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.3774</v>
+        <v>-2.2387</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.8513</v>
+        <v>-3.5844</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.0662</v>
+        <v>-2.8226</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.7851</v>
+        <v>-0.7618</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.0662</v>
+        <v>-2.8226</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.6557</v>
+        <v>-1.5848</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7851</v>
+        <v>-0.7618</v>
       </c>
       <c r="K41" t="n">
         <v>205</v>
@@ -2323,7 +2323,7 @@
         <v>55</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4408</v>
+        <v>-2.3466</v>
       </c>
       <c r="N41" t="n">
         <v>260</v>
@@ -2429,10 +2429,10 @@
         <v>1.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.849</v>
+        <v>0.8285</v>
       </c>
       <c r="J2" t="n">
-        <v>23.772</v>
+        <v>23.198</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.849</v>
+        <v>0.8285</v>
       </c>
       <c r="J3" t="n">
-        <v>23.772</v>
+        <v>23.198</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6478</v>
+        <v>0.617</v>
       </c>
       <c r="J4" t="n">
-        <v>18.1384</v>
+        <v>17.276</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5436</v>
+        <v>0.5104</v>
       </c>
       <c r="J5" t="n">
-        <v>15.2208</v>
+        <v>14.2912</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2709</v>
+        <v>-0.233</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.5852</v>
+        <v>-6.524</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.43</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8548</v>
+        <v>0.8202</v>
       </c>
       <c r="J7" t="n">
-        <v>23.9344</v>
+        <v>22.9656</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0881</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.4668</v>
+        <v>-2.0944</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.7</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3341</v>
+        <v>-0.3179</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.354799999999999</v>
+        <v>-8.901199999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.66</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3707</v>
+        <v>-0.3569</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.3796</v>
+        <v>-9.9932</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.57</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4508</v>
+        <v>-0.4446</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.6224</v>
+        <v>-12.4488</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1543</v>
+        <v>0.1378</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5489</v>
+        <v>3.1694</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.014</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.322</v>
+        <v>-0.2208</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.86</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1801</v>
+        <v>-0.1615</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.1423</v>
+        <v>-3.7145</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1903</v>
+        <v>-0.1715</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.3769</v>
+        <v>-3.9445</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4169</v>
+        <v>-0.4072</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.588699999999999</v>
+        <v>-9.365600000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.94</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0428</v>
+        <v>0.984</v>
       </c>
       <c r="J17" t="n">
-        <v>23.9844</v>
+        <v>22.632</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.45</v>
       </c>
       <c r="I18" t="n">
-        <v>0.57</v>
+        <v>0.4997</v>
       </c>
       <c r="J18" t="n">
-        <v>13.11</v>
+        <v>11.4931</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0732</v>
+        <v>0.053</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6836</v>
+        <v>1.219</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0599</v>
+        <v>-0.0477</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3777</v>
+        <v>-1.0971</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.72</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3465</v>
+        <v>-0.3341</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.9695</v>
+        <v>-7.6843</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.47</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6663</v>
+        <v>0.7049</v>
       </c>
       <c r="J22" t="n">
-        <v>17.3238</v>
+        <v>18.3274</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.99</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0259</v>
+        <v>-0.0185</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6734</v>
+        <v>-0.481</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0435</v>
+        <v>-0.0329</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.131</v>
+        <v>-0.8554</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1</v>
+        <v>-0.0829</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.6</v>
+        <v>-2.1554</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.68</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.367</v>
+        <v>-0.3539</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.542</v>
+        <v>-9.2014</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.44</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5923</v>
+        <v>0.5229</v>
       </c>
       <c r="J27" t="n">
-        <v>15.3998</v>
+        <v>13.5954</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2774</v>
+        <v>0.224</v>
       </c>
       <c r="J28" t="n">
-        <v>7.2124</v>
+        <v>5.824</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.12</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2107</v>
+        <v>0.1653</v>
       </c>
       <c r="J29" t="n">
-        <v>5.4782</v>
+        <v>4.2978</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.03</v>
       </c>
       <c r="I30" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0507</v>
       </c>
       <c r="J30" t="n">
-        <v>1.859</v>
+        <v>1.3182</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.45</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5674</v>
+        <v>-0.5798</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.7524</v>
+        <v>-15.0748</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5881</v>
+        <v>0.5504</v>
       </c>
       <c r="J32" t="n">
-        <v>21.1716</v>
+        <v>19.8144</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2771</v>
+        <v>0.2369</v>
       </c>
       <c r="J33" t="n">
-        <v>9.9756</v>
+        <v>8.5284</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2474</v>
+        <v>0.2087</v>
       </c>
       <c r="J34" t="n">
-        <v>8.9064</v>
+        <v>7.5132</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.67</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8583</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-30.8988</v>
+        <v>-30.1392</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.67</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8583</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>-30.8988</v>
+        <v>-30.1392</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.53</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9002</v>
+        <v>0.85</v>
       </c>
       <c r="J37" t="n">
-        <v>32.4072</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.18</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3769</v>
+        <v>0.3241</v>
       </c>
       <c r="J38" t="n">
-        <v>13.5684</v>
+        <v>11.6676</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.08</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1981</v>
+        <v>0.1613</v>
       </c>
       <c r="J39" t="n">
-        <v>7.1316</v>
+        <v>5.8068</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0963</v>
+        <v>-0.0794</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.4668</v>
+        <v>-2.8584</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1577</v>
+        <v>-0.1378</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.6772</v>
+        <v>-4.9608</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.65</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3969</v>
+        <v>1.4327</v>
       </c>
       <c r="J42" t="n">
-        <v>33.5256</v>
+        <v>34.3848</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.45</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0346</v>
+        <v>1.0309</v>
       </c>
       <c r="J43" t="n">
-        <v>24.8304</v>
+        <v>24.7416</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.33</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8047</v>
+        <v>0.7824</v>
       </c>
       <c r="J44" t="n">
-        <v>19.3128</v>
+        <v>18.7776</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.98</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1425</v>
+        <v>-0.1158</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.42</v>
+        <v>-2.7792</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6095</v>
+        <v>-0.576</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.628</v>
+        <v>-13.824</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.22</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4874</v>
+        <v>0.4303</v>
       </c>
       <c r="J47" t="n">
-        <v>11.6976</v>
+        <v>10.3272</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.06</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1836</v>
+        <v>0.144</v>
       </c>
       <c r="J48" t="n">
-        <v>4.4064</v>
+        <v>3.456</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1608</v>
+        <v>0.1242</v>
       </c>
       <c r="J49" t="n">
-        <v>3.8592</v>
+        <v>2.9808</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.82</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2257</v>
+        <v>-0.2055</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.4168</v>
+        <v>-4.932</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.49</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5259</v>
+        <v>-0.5303</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.6216</v>
+        <v>-12.7272</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.84</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3422</v>
+        <v>1.3474</v>
       </c>
       <c r="J52" t="n">
-        <v>29.5284</v>
+        <v>29.6428</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.6</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0469</v>
+        <v>1.0387</v>
       </c>
       <c r="J53" t="n">
-        <v>23.0318</v>
+        <v>22.8514</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.44</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8421</v>
+        <v>0.8331</v>
       </c>
       <c r="J54" t="n">
-        <v>18.5262</v>
+        <v>18.3282</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.26</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5869</v>
+        <v>0.5841</v>
       </c>
       <c r="J55" t="n">
-        <v>12.9118</v>
+        <v>12.8502</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.1</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2711</v>
+        <v>0.2383</v>
       </c>
       <c r="J56" t="n">
-        <v>5.9642</v>
+        <v>5.2426</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.91</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0837</v>
       </c>
       <c r="J57" t="n">
-        <v>-2.189</v>
+        <v>-1.8414</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.79</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2333</v>
+        <v>-0.2184</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.1326</v>
+        <v>-4.8048</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.67</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3441</v>
+        <v>-0.3307</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.5702</v>
+        <v>-7.2754</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.353</v>
+        <v>-0.3398</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.766</v>
+        <v>-7.4756</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.49</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5033</v>
+        <v>-0.502</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.0726</v>
+        <v>-11.044</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.23</v>
       </c>
       <c r="I62" t="n">
-        <v>1.7659</v>
+        <v>1.8095</v>
       </c>
       <c r="J62" t="n">
-        <v>33.5521</v>
+        <v>34.3805</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.8</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2745</v>
+        <v>1.2773</v>
       </c>
       <c r="J63" t="n">
-        <v>24.2155</v>
+        <v>24.2687</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.33</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6783</v>
+        <v>0.6743</v>
       </c>
       <c r="J64" t="n">
-        <v>12.8877</v>
+        <v>12.8117</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.33</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6783</v>
+        <v>0.6743</v>
       </c>
       <c r="J65" t="n">
-        <v>12.8877</v>
+        <v>12.8117</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.19</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4617</v>
+        <v>0.4395</v>
       </c>
       <c r="J66" t="n">
-        <v>8.7723</v>
+        <v>8.3505</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.63</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.3457</v>
+        <v>-0.3376</v>
       </c>
       <c r="J67" t="n">
-        <v>-6.5683</v>
+        <v>-6.4144</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.58</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3944</v>
+        <v>-0.3902</v>
       </c>
       <c r="J68" t="n">
-        <v>-7.4936</v>
+        <v>-7.4138</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.48</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4817</v>
+        <v>-0.4812</v>
       </c>
       <c r="J69" t="n">
-        <v>-9.1523</v>
+        <v>-9.142799999999999</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.43</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5249</v>
+        <v>-0.5269</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.973100000000001</v>
+        <v>-10.0111</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.37</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5786</v>
+        <v>-0.586</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.9934</v>
+        <v>-11.134</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.79</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3515</v>
+        <v>1.3637</v>
       </c>
       <c r="J72" t="n">
-        <v>37.842</v>
+        <v>38.1836</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7215</v>
+        <v>0.7064</v>
       </c>
       <c r="J73" t="n">
-        <v>20.202</v>
+        <v>19.7792</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4355</v>
+        <v>0.4019</v>
       </c>
       <c r="J74" t="n">
-        <v>12.194</v>
+        <v>11.2532</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.78</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6647</v>
+        <v>-0.6324</v>
       </c>
       <c r="J75" t="n">
-        <v>-18.6116</v>
+        <v>-17.7072</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.77</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6871</v>
+        <v>-0.6564</v>
       </c>
       <c r="J76" t="n">
-        <v>-19.2388</v>
+        <v>-18.3792</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.09</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2541</v>
+        <v>0.2076</v>
       </c>
       <c r="J77" t="n">
-        <v>7.1148</v>
+        <v>5.8128</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2332</v>
+        <v>0.1886</v>
       </c>
       <c r="J78" t="n">
-        <v>6.5296</v>
+        <v>5.2808</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.02</v>
       </c>
       <c r="I79" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="J79" t="n">
-        <v>2.5172</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.71</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3292</v>
+        <v>-0.3126</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.217599999999999</v>
+        <v>-8.752800000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.61</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4197</v>
+        <v>-0.4105</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.7516</v>
+        <v>-11.494</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.61</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0907</v>
+        <v>1.0816</v>
       </c>
       <c r="J82" t="n">
-        <v>29.4489</v>
+        <v>29.2032</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.29</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.6388</v>
       </c>
       <c r="J83" t="n">
-        <v>17.5149</v>
+        <v>17.2476</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.27</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6194</v>
+        <v>0.6109</v>
       </c>
       <c r="J84" t="n">
-        <v>16.7238</v>
+        <v>16.4943</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.25</v>
       </c>
       <c r="I85" t="n">
-        <v>0.59</v>
+        <v>0.583</v>
       </c>
       <c r="J85" t="n">
-        <v>15.93</v>
+        <v>15.741</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.9</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.391</v>
+        <v>-0.3516</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.557</v>
+        <v>-9.4932</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3239</v>
+        <v>0.2773</v>
       </c>
       <c r="J87" t="n">
-        <v>8.7453</v>
+        <v>7.4871</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2255</v>
+        <v>-0.2078</v>
       </c>
       <c r="J88" t="n">
-        <v>-6.0885</v>
+        <v>-5.6106</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.75</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2824</v>
+        <v>-0.2647</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.6248</v>
+        <v>-7.1469</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.73</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3011</v>
+        <v>-0.2839</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.1297</v>
+        <v>-7.6653</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.66</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3654</v>
+        <v>-0.3513</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.8658</v>
+        <v>-9.485099999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.31</v>
       </c>
       <c r="I92" t="n">
-        <v>0.806</v>
+        <v>0.7798</v>
       </c>
       <c r="J92" t="n">
-        <v>28.21</v>
+        <v>27.293</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.3</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7851</v>
+        <v>0.7573</v>
       </c>
       <c r="J93" t="n">
-        <v>27.4785</v>
+        <v>26.5055</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0104</v>
+        <v>-0.0067</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.364</v>
+        <v>-0.2345</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.99</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0506</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.45</v>
+        <v>-1.771</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.75</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7144</v>
+        <v>-0.6835</v>
       </c>
       <c r="J96" t="n">
-        <v>-25.004</v>
+        <v>-23.9225</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.22</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4592</v>
+        <v>0.4009</v>
       </c>
       <c r="J97" t="n">
-        <v>16.072</v>
+        <v>14.0315</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2466</v>
+        <v>0.2014</v>
       </c>
       <c r="J98" t="n">
-        <v>8.631</v>
+        <v>7.049</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.227</v>
+        <v>0.1839</v>
       </c>
       <c r="J99" t="n">
-        <v>7.945</v>
+        <v>6.4365</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.08</v>
       </c>
       <c r="I100" t="n">
-        <v>0.207</v>
+        <v>0.1661</v>
       </c>
       <c r="J100" t="n">
-        <v>7.245</v>
+        <v>5.8135</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3599</v>
+        <v>-0.3464</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.5965</v>
+        <v>-12.124</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.46</v>
       </c>
       <c r="I102" t="n">
-        <v>1.071</v>
+        <v>1.0802</v>
       </c>
       <c r="J102" t="n">
-        <v>28.917</v>
+        <v>29.1654</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.796</v>
+        <v>0.7691</v>
       </c>
       <c r="J103" t="n">
-        <v>21.492</v>
+        <v>20.7657</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1208</v>
+        <v>0.0985</v>
       </c>
       <c r="J104" t="n">
-        <v>3.2616</v>
+        <v>2.6595</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.88</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4147</v>
+        <v>-0.372</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.1969</v>
+        <v>-10.044</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.84</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5141</v>
+        <v>-0.4731</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.8807</v>
+        <v>-12.7737</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.61</v>
       </c>
       <c r="I107" t="n">
-        <v>1.028</v>
+        <v>1.0026</v>
       </c>
       <c r="J107" t="n">
-        <v>27.756</v>
+        <v>27.0702</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2463</v>
+        <v>0.2012</v>
       </c>
       <c r="J108" t="n">
-        <v>6.6501</v>
+        <v>5.4324</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2067</v>
+        <v>0.166</v>
       </c>
       <c r="J109" t="n">
-        <v>5.5809</v>
+        <v>4.482</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.78</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2755</v>
+        <v>-0.2566</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.4385</v>
+        <v>-6.9282</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.62</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4227</v>
+        <v>-0.4153</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.4129</v>
+        <v>-11.2131</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7167</v>
+        <v>0.6605</v>
       </c>
       <c r="J112" t="n">
-        <v>19.3509</v>
+        <v>17.8335</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.04</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1228</v>
+        <v>0.0931</v>
       </c>
       <c r="J113" t="n">
-        <v>3.3156</v>
+        <v>2.5137</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1248</v>
+        <v>-0.1061</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.3696</v>
+        <v>-2.8647</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.89</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1594</v>
+        <v>-0.1393</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.3038</v>
+        <v>-3.7611</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2132</v>
+        <v>-0.1925</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.7564</v>
+        <v>-5.1975</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.42</v>
       </c>
       <c r="I117" t="n">
-        <v>1.016</v>
+        <v>1.0166</v>
       </c>
       <c r="J117" t="n">
-        <v>27.432</v>
+        <v>27.4482</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.25</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6757</v>
+        <v>0.641</v>
       </c>
       <c r="J118" t="n">
-        <v>18.2439</v>
+        <v>17.307</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1496</v>
+        <v>-0.1188</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.0392</v>
+        <v>-3.2076</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.89</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3842</v>
+        <v>-0.3413</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.3734</v>
+        <v>-9.2151</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4355</v>
+        <v>-0.3926</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.7585</v>
+        <v>-10.6002</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.35</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6889</v>
+        <v>0.6341</v>
       </c>
       <c r="J122" t="n">
-        <v>20.667</v>
+        <v>19.023</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.99</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0229</v>
+        <v>-0.0169</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.507</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.98</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0405</v>
+        <v>-0.0314</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.215</v>
+        <v>-0.9419999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.82</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2285</v>
+        <v>-0.2082</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.855</v>
+        <v>-6.246</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.65</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3893</v>
+        <v>-0.3777</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.679</v>
+        <v>-11.331</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.39</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9542</v>
+        <v>0.9431</v>
       </c>
       <c r="J127" t="n">
-        <v>28.626</v>
+        <v>28.293</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.17</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4909</v>
+        <v>0.4515</v>
       </c>
       <c r="J128" t="n">
-        <v>14.727</v>
+        <v>13.545</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.14</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4207</v>
+        <v>0.3817</v>
       </c>
       <c r="J129" t="n">
-        <v>12.621</v>
+        <v>11.451</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0175</v>
+        <v>-0.0127</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.525</v>
+        <v>-0.381</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.85</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4909</v>
+        <v>-0.4494</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.727</v>
+        <v>-13.482</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.13</v>
       </c>
       <c r="I132" t="n">
-        <v>0.461</v>
+        <v>0.4431</v>
       </c>
       <c r="J132" t="n">
-        <v>9.680999999999999</v>
+        <v>9.305099999999999</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.58</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.4153</v>
+        <v>-0.4066</v>
       </c>
       <c r="J133" t="n">
-        <v>-8.721299999999999</v>
+        <v>-8.538600000000001</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.52</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4681</v>
+        <v>-0.463</v>
       </c>
       <c r="J134" t="n">
-        <v>-9.8301</v>
+        <v>-9.723000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.5</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4857</v>
+        <v>-0.4823</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.1997</v>
+        <v>-10.1283</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.46</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5208</v>
+        <v>-0.5213</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.9368</v>
+        <v>-10.9473</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.01</v>
       </c>
       <c r="I137" t="n">
-        <v>1.6752</v>
+        <v>1.7205</v>
       </c>
       <c r="J137" t="n">
-        <v>35.1792</v>
+        <v>36.1305</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.64</v>
       </c>
       <c r="I138" t="n">
-        <v>1.2351</v>
+        <v>1.2555</v>
       </c>
       <c r="J138" t="n">
-        <v>25.9371</v>
+        <v>26.3655</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.55</v>
       </c>
       <c r="I139" t="n">
-        <v>1.1237</v>
+        <v>1.1425</v>
       </c>
       <c r="J139" t="n">
-        <v>23.5977</v>
+        <v>23.9925</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5865</v>
+        <v>0.5616</v>
       </c>
       <c r="J140" t="n">
-        <v>12.3165</v>
+        <v>11.7936</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.18</v>
       </c>
       <c r="I141" t="n">
-        <v>0.4547</v>
+        <v>0.4238</v>
       </c>
       <c r="J141" t="n">
-        <v>9.5487</v>
+        <v>8.899800000000001</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5157</v>
+        <v>0.4579</v>
       </c>
       <c r="J142" t="n">
-        <v>14.9553</v>
+        <v>13.2791</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.1</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2635</v>
+        <v>0.2157</v>
       </c>
       <c r="J143" t="n">
-        <v>7.6415</v>
+        <v>6.2553</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.85</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1966</v>
+        <v>-0.1763</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.7014</v>
+        <v>-5.1127</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2374</v>
+        <v>-0.2173</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.8846</v>
+        <v>-6.3017</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3148</v>
+        <v>-0.2975</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.129200000000001</v>
+        <v>-8.6275</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.49</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0962</v>
+        <v>1.1072</v>
       </c>
       <c r="J147" t="n">
-        <v>31.7898</v>
+        <v>32.1088</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.32</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7988</v>
+        <v>0.7735</v>
       </c>
       <c r="J148" t="n">
-        <v>23.1652</v>
+        <v>22.4315</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.16</v>
       </c>
       <c r="I149" t="n">
-        <v>0.46</v>
+        <v>0.424</v>
       </c>
       <c r="J149" t="n">
-        <v>13.34</v>
+        <v>12.296</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.05</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1739</v>
+        <v>0.1474</v>
       </c>
       <c r="J150" t="n">
-        <v>5.0431</v>
+        <v>4.2746</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.85</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5027</v>
+        <v>-0.4627</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.5783</v>
+        <v>-13.4183</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.48</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6127</v>
+        <v>0.5414</v>
       </c>
       <c r="J152" t="n">
-        <v>16.5429</v>
+        <v>14.6178</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.26</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3731</v>
+        <v>0.3124</v>
       </c>
       <c r="J153" t="n">
-        <v>10.0737</v>
+        <v>8.434799999999999</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0975</v>
+        <v>0.0727</v>
       </c>
       <c r="J154" t="n">
-        <v>2.6325</v>
+        <v>1.9629</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0108</v>
+        <v>-0.0083</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.2916</v>
+        <v>-0.2241</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0557</v>
       </c>
       <c r="J156" t="n">
-        <v>-1.89</v>
+        <v>-1.5039</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.13</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2734</v>
+        <v>0.2625</v>
       </c>
       <c r="J157" t="n">
-        <v>7.3818</v>
+        <v>7.0875</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0738</v>
+        <v>-0.0617</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.9926</v>
+        <v>-1.6659</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.8</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2384</v>
+        <v>-0.2194</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.4368</v>
+        <v>-5.9238</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.277</v>
+        <v>-0.2585</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.479</v>
+        <v>-6.9795</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.62</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4058</v>
+        <v>-0.3949</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.9566</v>
+        <v>-10.6623</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.81</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2295</v>
+        <v>1.2245</v>
       </c>
       <c r="J162" t="n">
-        <v>33.1965</v>
+        <v>33.0615</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.22</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4579</v>
+        <v>0.3997</v>
       </c>
       <c r="J163" t="n">
-        <v>12.3633</v>
+        <v>10.7919</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1839</v>
+        <v>-0.1633</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.9653</v>
+        <v>-4.4091</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.76</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2951</v>
+        <v>-0.2772</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.9677</v>
+        <v>-7.4844</v>
       </c>
     </row>
     <row r="166">
@@ -9029,10 +9029,10 @@
         <v>1.29</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7571</v>
+        <v>0.7274</v>
       </c>
       <c r="J167" t="n">
-        <v>20.4417</v>
+        <v>19.6398</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.22</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6067</v>
+        <v>0.5692</v>
       </c>
       <c r="J168" t="n">
-        <v>16.3809</v>
+        <v>15.3684</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.2</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5622</v>
+        <v>0.5234</v>
       </c>
       <c r="J169" t="n">
-        <v>15.1794</v>
+        <v>14.1318</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0146</v>
+        <v>-0.0102</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.3942</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.76</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6968</v>
+        <v>-0.6651</v>
       </c>
       <c r="J171" t="n">
-        <v>-18.8136</v>
+        <v>-17.9577</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.11</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3958</v>
+        <v>0.3684</v>
       </c>
       <c r="J172" t="n">
-        <v>8.707599999999999</v>
+        <v>8.104799999999999</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.79</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2272</v>
+        <v>-0.2126</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.9984</v>
+        <v>-4.6772</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.66</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3494</v>
+        <v>-0.3374</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.6868</v>
+        <v>-7.4228</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.45</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5339</v>
+        <v>-0.5363</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.7458</v>
+        <v>-11.7986</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.34</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6296</v>
+        <v>-0.6471</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.8512</v>
+        <v>-14.2362</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.44</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9881</v>
+        <v>0.9882</v>
       </c>
       <c r="J177" t="n">
-        <v>21.7382</v>
+        <v>21.7404</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.43</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9717</v>
+        <v>0.9695</v>
       </c>
       <c r="J178" t="n">
-        <v>21.3774</v>
+        <v>21.329</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.36</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8469</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>18.6318</v>
+        <v>18.3304</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.32</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7713</v>
+        <v>0.7532</v>
       </c>
       <c r="J180" t="n">
-        <v>16.9686</v>
+        <v>16.5704</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.27</v>
       </c>
       <c r="I181" t="n">
-        <v>0.6717</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="J181" t="n">
-        <v>14.7774</v>
+        <v>14.2714</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.11</v>
       </c>
       <c r="I182" t="n">
-        <v>0.28</v>
+        <v>0.2308</v>
       </c>
       <c r="J182" t="n">
-        <v>10.08</v>
+        <v>8.3088</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.1</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2604</v>
+        <v>0.2128</v>
       </c>
       <c r="J183" t="n">
-        <v>9.3744</v>
+        <v>7.6608</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.99</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.023</v>
+        <v>-0.017</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.828</v>
+        <v>-0.612</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1204</v>
+        <v>-0.1027</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.3344</v>
+        <v>-3.6972</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.68</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3624</v>
+        <v>-0.3484</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.0464</v>
+        <v>-12.5424</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.14</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4289</v>
+        <v>0.3876</v>
       </c>
       <c r="J187" t="n">
-        <v>15.4404</v>
+        <v>13.9536</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.13</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4045</v>
+        <v>0.3634</v>
       </c>
       <c r="J188" t="n">
-        <v>14.562</v>
+        <v>13.0824</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3797</v>
+        <v>0.3391</v>
       </c>
       <c r="J189" t="n">
-        <v>13.6692</v>
+        <v>12.2076</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.98</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1102</v>
+        <v>-0.0843</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.9672</v>
+        <v>-3.0348</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.95</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2121</v>
+        <v>-0.1757</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.6356</v>
+        <v>-6.3252</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.38</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8094</v>
+        <v>0.7801</v>
       </c>
       <c r="J192" t="n">
-        <v>20.235</v>
+        <v>19.5025</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.78</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2528</v>
+        <v>-0.2353</v>
       </c>
       <c r="J193" t="n">
-        <v>-6.32</v>
+        <v>-5.8825</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.7</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3273</v>
+        <v>-0.3113</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.182499999999999</v>
+        <v>-7.7825</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.61</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4088</v>
+        <v>-0.398</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.22</v>
+        <v>-9.949999999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.52</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.488</v>
+        <v>-0.4856</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.2</v>
+        <v>-12.14</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.65</v>
       </c>
       <c r="I197" t="n">
-        <v>1.2898</v>
+        <v>1.3087</v>
       </c>
       <c r="J197" t="n">
-        <v>32.245</v>
+        <v>32.7175</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.27</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6561</v>
       </c>
       <c r="J198" t="n">
-        <v>17.075</v>
+        <v>16.4025</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.27</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6561</v>
       </c>
       <c r="J199" t="n">
-        <v>17.075</v>
+        <v>16.4025</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.14</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3998</v>
+        <v>0.3672</v>
       </c>
       <c r="J200" t="n">
-        <v>9.994999999999999</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.0449</v>
+        <v>-0.0398</v>
       </c>
       <c r="J201" t="n">
-        <v>-1.1225</v>
+        <v>-0.995</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.61</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2389</v>
+        <v>1.2553</v>
       </c>
       <c r="J202" t="n">
-        <v>28.4947</v>
+        <v>28.8719</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.57</v>
       </c>
       <c r="I203" t="n">
-        <v>1.1861</v>
+        <v>1.2004</v>
       </c>
       <c r="J203" t="n">
-        <v>27.2803</v>
+        <v>27.6092</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.47</v>
       </c>
       <c r="I204" t="n">
-        <v>1.0505</v>
+        <v>1.0567</v>
       </c>
       <c r="J204" t="n">
-        <v>24.1615</v>
+        <v>24.3041</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.87</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4678</v>
+        <v>-0.4291</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.7594</v>
+        <v>-9.869300000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.78</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6804</v>
+        <v>-0.6518</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.6492</v>
+        <v>-14.9914</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.14</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3734</v>
+        <v>0.3229</v>
       </c>
       <c r="J207" t="n">
-        <v>8.588200000000001</v>
+        <v>7.4267</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.99</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0045</v>
       </c>
       <c r="J208" t="n">
-        <v>-0.2024</v>
+        <v>-0.1035</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.79</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2468</v>
+        <v>-0.2282</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.6764</v>
+        <v>-5.2486</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.76</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2755</v>
+        <v>-0.2573</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.3365</v>
+        <v>-5.9179</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.51</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5008</v>
+        <v>-0.5004</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.5184</v>
+        <v>-11.5092</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.57</v>
       </c>
       <c r="I212" t="n">
-        <v>1.1741</v>
+        <v>1.1885</v>
       </c>
       <c r="J212" t="n">
-        <v>28.1784</v>
+        <v>28.524</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.37</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8694</v>
+        <v>0.855</v>
       </c>
       <c r="J213" t="n">
-        <v>20.8656</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.26</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6566</v>
+        <v>0.6315</v>
       </c>
       <c r="J214" t="n">
-        <v>15.7584</v>
+        <v>15.156</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.25</v>
       </c>
       <c r="I215" t="n">
-        <v>0.636</v>
+        <v>0.61</v>
       </c>
       <c r="J215" t="n">
-        <v>15.264</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.17</v>
       </c>
       <c r="I216" t="n">
-        <v>0.4613</v>
+        <v>0.4303</v>
       </c>
       <c r="J216" t="n">
-        <v>11.0712</v>
+        <v>10.3272</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.31</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6483</v>
+        <v>0.5958</v>
       </c>
       <c r="J217" t="n">
-        <v>15.5592</v>
+        <v>14.2992</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.18</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4275</v>
+        <v>0.3725</v>
       </c>
       <c r="J218" t="n">
-        <v>10.26</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2327</v>
+        <v>-0.2129</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.5848</v>
+        <v>-5.1096</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.61</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4191</v>
+        <v>-0.4098</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.0584</v>
+        <v>-9.8352</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.57</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4543</v>
+        <v>-0.4488</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.9032</v>
+        <v>-10.7712</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8343</v>
+        <v>0.7696</v>
       </c>
       <c r="J222" t="n">
-        <v>30.0348</v>
+        <v>27.7056</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.06</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1207</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="J223" t="n">
-        <v>4.3452</v>
+        <v>3.2544</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.02</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0493</v>
+        <v>0.0343</v>
       </c>
       <c r="J224" t="n">
-        <v>1.7748</v>
+        <v>1.2348</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.9</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1531</v>
+        <v>-0.1331</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.5116</v>
+        <v>-4.7916</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.7</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3537</v>
+        <v>-0.3401</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.7332</v>
+        <v>-12.2436</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.5</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6732</v>
+        <v>0.7096</v>
       </c>
       <c r="J227" t="n">
-        <v>24.2352</v>
+        <v>25.5456</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.33</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4808</v>
+        <v>0.4872</v>
       </c>
       <c r="J228" t="n">
-        <v>17.3088</v>
+        <v>17.5392</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.17</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2825</v>
+        <v>0.2714</v>
       </c>
       <c r="J229" t="n">
-        <v>10.17</v>
+        <v>9.7704</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2121</v>
+        <v>-0.1919</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.6356</v>
+        <v>-6.9084</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.77</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2922</v>
+        <v>-0.2749</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.5192</v>
+        <v>-9.8964</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.03</v>
       </c>
       <c r="I232" t="n">
-        <v>0.1098</v>
+        <v>0.081</v>
       </c>
       <c r="J232" t="n">
-        <v>2.8548</v>
+        <v>2.106</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>0.0078</v>
+        <v>0.0047</v>
       </c>
       <c r="J233" t="n">
-        <v>0.2028</v>
+        <v>0.1222</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.98</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0389</v>
+        <v>-0.0304</v>
       </c>
       <c r="J234" t="n">
-        <v>-1.0114</v>
+        <v>-0.7904</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.93</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.107</v>
+        <v>-0.0907</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.782</v>
+        <v>-2.3582</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.75</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2951</v>
+        <v>-0.2768</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.6726</v>
+        <v>-7.1968</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.55</v>
       </c>
       <c r="I237" t="n">
-        <v>1.188</v>
+        <v>1.2037</v>
       </c>
       <c r="J237" t="n">
-        <v>30.888</v>
+        <v>31.2962</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.18</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5089</v>
+        <v>0.4711</v>
       </c>
       <c r="J238" t="n">
-        <v>13.2314</v>
+        <v>12.2486</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.11</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3453</v>
+        <v>0.3094</v>
       </c>
       <c r="J239" t="n">
-        <v>8.9778</v>
+        <v>8.0444</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.99</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0823</v>
+        <v>-0.0615</v>
       </c>
       <c r="J240" t="n">
-        <v>-2.1398</v>
+        <v>-1.599</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.86</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4716</v>
+        <v>-0.43</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.2616</v>
+        <v>-11.18</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>0.86</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.1315</v>
+        <v>-0.1103</v>
       </c>
       <c r="J242" t="n">
-        <v>-2.63</v>
+        <v>-2.206</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.72</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2834</v>
+        <v>-0.2712</v>
       </c>
       <c r="J243" t="n">
-        <v>-5.668</v>
+        <v>-5.424</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.61</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3857</v>
+        <v>-0.3775</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.714</v>
+        <v>-7.55</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4277</v>
+        <v>-0.4207</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.554</v>
+        <v>-8.414</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.25</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7006</v>
+        <v>-0.7309</v>
       </c>
       <c r="J246" t="n">
-        <v>-14.012</v>
+        <v>-14.618</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.81</v>
       </c>
       <c r="I247" t="n">
-        <v>1.4415</v>
+        <v>1.4699</v>
       </c>
       <c r="J247" t="n">
-        <v>28.83</v>
+        <v>29.398</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>1.2602</v>
+        <v>1.281</v>
       </c>
       <c r="J248" t="n">
-        <v>25.204</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.51</v>
       </c>
       <c r="I249" t="n">
-        <v>1.0743</v>
+        <v>1.0913</v>
       </c>
       <c r="J249" t="n">
-        <v>21.486</v>
+        <v>21.826</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.33</v>
       </c>
       <c r="I250" t="n">
-        <v>0.7702</v>
+        <v>0.757</v>
       </c>
       <c r="J250" t="n">
-        <v>15.404</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>1.29</v>
       </c>
       <c r="I251" t="n">
-        <v>0.6906</v>
+        <v>0.672</v>
       </c>
       <c r="J251" t="n">
-        <v>13.812</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.31</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6034</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="J252" t="n">
-        <v>17.4986</v>
+        <v>15.7731</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.19</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4088</v>
+        <v>0.3523</v>
       </c>
       <c r="J253" t="n">
-        <v>11.8552</v>
+        <v>10.2167</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.05</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1435</v>
+        <v>0.1112</v>
       </c>
       <c r="J254" t="n">
-        <v>4.1615</v>
+        <v>3.2248</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1725</v>
+        <v>-0.152</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.0025</v>
+        <v>-4.408</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.75</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3041</v>
+        <v>-0.2867</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.818899999999999</v>
+        <v>-8.314299999999999</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.46</v>
       </c>
       <c r="I257" t="n">
-        <v>1.0662</v>
+        <v>1.0745</v>
       </c>
       <c r="J257" t="n">
-        <v>30.9198</v>
+        <v>31.1605</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.22</v>
       </c>
       <c r="I258" t="n">
-        <v>0.6005</v>
+        <v>0.5637</v>
       </c>
       <c r="J258" t="n">
-        <v>17.4145</v>
+        <v>16.3473</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1827</v>
+        <v>0.1548</v>
       </c>
       <c r="J259" t="n">
-        <v>5.2983</v>
+        <v>4.4892</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2231</v>
+        <v>-0.186</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.4699</v>
+        <v>-5.394</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.93</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2829</v>
+        <v>-0.2426</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.2041</v>
+        <v>-7.0354</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.61</v>
       </c>
       <c r="I262" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.6368</v>
       </c>
       <c r="J262" t="n">
-        <v>14.8722</v>
+        <v>13.3728</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.56</v>
       </c>
       <c r="I263" t="n">
-        <v>0.6605</v>
+        <v>0.5898</v>
       </c>
       <c r="J263" t="n">
-        <v>13.8705</v>
+        <v>12.3858</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.51</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6122</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="J264" t="n">
-        <v>12.8562</v>
+        <v>11.3988</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.43</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5335</v>
+        <v>0.4674</v>
       </c>
       <c r="J265" t="n">
-        <v>11.2035</v>
+        <v>9.8154</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.8</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2805</v>
+        <v>-0.2656</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.8905</v>
+        <v>-5.5776</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.05</v>
       </c>
       <c r="I267" t="n">
-        <v>0.1532</v>
+        <v>0.14</v>
       </c>
       <c r="J267" t="n">
-        <v>3.2172</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.95</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0668</v>
+        <v>-0.0549</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.4028</v>
+        <v>-1.1529</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2533</v>
+        <v>-0.2356</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.3193</v>
+        <v>-4.9476</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.7</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.328</v>
+        <v>-0.3119</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.888</v>
+        <v>-6.5499</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.54</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4712</v>
+        <v>-0.4668</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.895200000000001</v>
+        <v>-9.8028</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.64</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0381</v>
+        <v>1.0106</v>
       </c>
       <c r="J272" t="n">
-        <v>31.143</v>
+        <v>30.318</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.21</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4275</v>
+        <v>0.3717</v>
       </c>
       <c r="J273" t="n">
-        <v>12.825</v>
+        <v>11.151</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.17</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3611</v>
+        <v>0.3091</v>
       </c>
       <c r="J274" t="n">
-        <v>10.833</v>
+        <v>9.273</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.8</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2627</v>
+        <v>-0.2438</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.881</v>
+        <v>-7.314</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.78</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2823</v>
+        <v>-0.2643</v>
       </c>
       <c r="J276" t="n">
-        <v>-8.468999999999999</v>
+        <v>-7.929</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.27</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7458</v>
+        <v>0.716</v>
       </c>
       <c r="J277" t="n">
-        <v>22.374</v>
+        <v>21.48</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.06</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2313</v>
+        <v>0.1944</v>
       </c>
       <c r="J278" t="n">
-        <v>6.939</v>
+        <v>5.832</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.97</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1348</v>
+        <v>-0.1072</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.044</v>
+        <v>-3.216</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4923</v>
+        <v>-0.45</v>
       </c>
       <c r="J280" t="n">
-        <v>-14.769</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.84</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4923</v>
+        <v>-0.45</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.769</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.49</v>
       </c>
       <c r="I282" t="n">
-        <v>0.6343</v>
+        <v>0.5637</v>
       </c>
       <c r="J282" t="n">
-        <v>17.7604</v>
+        <v>15.7836</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.2</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3084</v>
+        <v>0.2526</v>
       </c>
       <c r="J283" t="n">
-        <v>8.635199999999999</v>
+        <v>7.0728</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.13</v>
       </c>
       <c r="I284" t="n">
-        <v>0.219</v>
+        <v>0.1735</v>
       </c>
       <c r="J284" t="n">
-        <v>6.132</v>
+        <v>4.858</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.89</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1663</v>
+        <v>-0.146</v>
       </c>
       <c r="J285" t="n">
-        <v>-4.6564</v>
+        <v>-4.088</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.76</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2994</v>
+        <v>-0.2822</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.3832</v>
+        <v>-7.9016</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.45</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.6835</v>
       </c>
       <c r="J287" t="n">
-        <v>18.1356</v>
+        <v>19.138</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.25</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4058</v>
+        <v>0.4036</v>
       </c>
       <c r="J288" t="n">
-        <v>11.3624</v>
+        <v>11.3008</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.95</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0858</v>
+        <v>-0.0702</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.4024</v>
+        <v>-1.9656</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.71</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3381</v>
+        <v>-0.3226</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.466799999999999</v>
+        <v>-9.0328</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.62</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4193</v>
+        <v>-0.411</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.7404</v>
+        <v>-11.508</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.11</v>
       </c>
       <c r="I292" t="n">
-        <v>0.2787</v>
+        <v>0.2296</v>
       </c>
       <c r="J292" t="n">
-        <v>9.7545</v>
+        <v>8.036</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.09</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2391</v>
+        <v>0.1935</v>
       </c>
       <c r="J293" t="n">
-        <v>8.368499999999999</v>
+        <v>6.7725</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.0564</v>
+        <v>-0.0447</v>
       </c>
       <c r="J294" t="n">
-        <v>-1.974</v>
+        <v>-1.5645</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.85</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1984</v>
+        <v>-0.1779</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.944</v>
+        <v>-6.2265</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2393</v>
+        <v>-0.2191</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.375500000000001</v>
+        <v>-7.6685</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.26</v>
       </c>
       <c r="I297" t="n">
-        <v>0.6984</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="J297" t="n">
-        <v>24.444</v>
+        <v>23.268</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.12</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3775</v>
+        <v>0.3375</v>
       </c>
       <c r="J298" t="n">
-        <v>13.2125</v>
+        <v>11.8125</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.1254</v>
+        <v>0.102</v>
       </c>
       <c r="J299" t="n">
-        <v>4.389</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.01</v>
       </c>
       <c r="I300" t="n">
-        <v>0.0482</v>
+        <v>0.0362</v>
       </c>
       <c r="J300" t="n">
-        <v>1.687</v>
+        <v>1.267</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.96</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.1826</v>
+        <v>-0.1485</v>
       </c>
       <c r="J301" t="n">
-        <v>-6.391</v>
+        <v>-5.1975</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>0.93</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.029</v>
+        <v>0.0015</v>
       </c>
       <c r="J302" t="n">
-        <v>-0.551</v>
+        <v>0.0285</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.65</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.3444</v>
+        <v>-0.3358</v>
       </c>
       <c r="J303" t="n">
-        <v>-6.5436</v>
+        <v>-6.3802</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.62</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3723</v>
+        <v>-0.365</v>
       </c>
       <c r="J304" t="n">
-        <v>-7.0737</v>
+        <v>-6.935</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.38</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.5813</v>
+        <v>-0.5894</v>
       </c>
       <c r="J305" t="n">
-        <v>-11.0447</v>
+        <v>-11.1986</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.26</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6882</v>
+        <v>-0.7153</v>
       </c>
       <c r="J306" t="n">
-        <v>-13.0758</v>
+        <v>-13.5907</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>2.22</v>
       </c>
       <c r="I307" t="n">
-        <v>1.9073</v>
+        <v>1.9761</v>
       </c>
       <c r="J307" t="n">
-        <v>36.2387</v>
+        <v>37.5459</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.69</v>
       </c>
       <c r="I308" t="n">
-        <v>1.2931</v>
+        <v>1.3157</v>
       </c>
       <c r="J308" t="n">
-        <v>24.5689</v>
+        <v>24.9983</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.59</v>
       </c>
       <c r="I309" t="n">
-        <v>1.171</v>
+        <v>1.1912</v>
       </c>
       <c r="J309" t="n">
-        <v>22.249</v>
+        <v>22.6328</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.13</v>
       </c>
       <c r="I310" t="n">
-        <v>0.3327</v>
+        <v>0.2982</v>
       </c>
       <c r="J310" t="n">
-        <v>6.3213</v>
+        <v>5.6658</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>1.13</v>
       </c>
       <c r="I311" t="n">
-        <v>0.3327</v>
+        <v>0.2982</v>
       </c>
       <c r="J311" t="n">
-        <v>6.3213</v>
+        <v>5.6658</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>0.98</v>
       </c>
       <c r="I312" t="n">
-        <v>-0.0149</v>
+        <v>-0.0068</v>
       </c>
       <c r="J312" t="n">
-        <v>-0.298</v>
+        <v>-0.136</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.83</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.2019</v>
+        <v>-0.1857</v>
       </c>
       <c r="J313" t="n">
-        <v>-4.038</v>
+        <v>-3.714</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.74</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2875</v>
+        <v>-0.271</v>
       </c>
       <c r="J314" t="n">
-        <v>-5.75</v>
+        <v>-5.42</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.67</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3516</v>
+        <v>-0.337</v>
       </c>
       <c r="J315" t="n">
-        <v>-7.032</v>
+        <v>-6.74</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.63</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3877</v>
+        <v>-0.3753</v>
       </c>
       <c r="J316" t="n">
-        <v>-7.754</v>
+        <v>-7.506</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.65</v>
       </c>
       <c r="I317" t="n">
-        <v>1.2699</v>
+        <v>1.288</v>
       </c>
       <c r="J317" t="n">
-        <v>25.398</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.41</v>
       </c>
       <c r="I318" t="n">
-        <v>0.9372</v>
+        <v>0.9307</v>
       </c>
       <c r="J318" t="n">
-        <v>18.744</v>
+        <v>18.614</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.32</v>
       </c>
       <c r="I319" t="n">
-        <v>0.771</v>
+        <v>0.7531</v>
       </c>
       <c r="J319" t="n">
-        <v>15.42</v>
+        <v>15.062</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.26</v>
       </c>
       <c r="I320" t="n">
-        <v>0.6509</v>
+        <v>0.627</v>
       </c>
       <c r="J320" t="n">
-        <v>13.018</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>1.19</v>
       </c>
       <c r="I321" t="n">
-        <v>0.5004</v>
+        <v>0.4709</v>
       </c>
       <c r="J321" t="n">
-        <v>10.008</v>
+        <v>9.417999999999999</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.61</v>
       </c>
       <c r="I322" t="n">
-        <v>0.7235</v>
+        <v>0.6513</v>
       </c>
       <c r="J322" t="n">
-        <v>19.5345</v>
+        <v>17.5851</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.23</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3299</v>
+        <v>0.276</v>
       </c>
       <c r="J323" t="n">
-        <v>8.907299999999999</v>
+        <v>7.452</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.2</v>
       </c>
       <c r="I324" t="n">
-        <v>0.2945</v>
+        <v>0.2442</v>
       </c>
       <c r="J324" t="n">
-        <v>7.9515</v>
+        <v>6.5934</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.17</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2576</v>
+        <v>0.2112</v>
       </c>
       <c r="J325" t="n">
-        <v>6.9552</v>
+        <v>5.7024</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.14</v>
       </c>
       <c r="I326" t="n">
-        <v>0.219</v>
+        <v>0.1769</v>
       </c>
       <c r="J326" t="n">
-        <v>5.913</v>
+        <v>4.7763</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.25</v>
       </c>
       <c r="I327" t="n">
-        <v>0.4462</v>
+        <v>0.4561</v>
       </c>
       <c r="J327" t="n">
-        <v>12.0474</v>
+        <v>12.3147</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.9</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1348</v>
+        <v>-0.1189</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.6396</v>
+        <v>-3.2103</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.85</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1886</v>
+        <v>-0.1706</v>
       </c>
       <c r="J329" t="n">
-        <v>-5.0922</v>
+        <v>-4.6062</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.73</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3045</v>
+        <v>-0.287</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.221500000000001</v>
+        <v>-7.749</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.49</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="J331" t="n">
-        <v>-14.0022</v>
+        <v>-14.0589</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.06</v>
       </c>
       <c r="I332" t="n">
-        <v>0.1882</v>
+        <v>0.1482</v>
       </c>
       <c r="J332" t="n">
-        <v>4.8932</v>
+        <v>3.8532</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1</v>
       </c>
       <c r="I333" t="n">
-        <v>0.0133</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J333" t="n">
-        <v>0.3458</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.96</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.0663</v>
+        <v>-0.0545</v>
       </c>
       <c r="J334" t="n">
-        <v>-1.7238</v>
+        <v>-1.417</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.85</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.1932</v>
+        <v>-0.1735</v>
       </c>
       <c r="J335" t="n">
-        <v>-5.0232</v>
+        <v>-4.511</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.67</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3665</v>
+        <v>-0.3525</v>
       </c>
       <c r="J336" t="n">
-        <v>-9.529</v>
+        <v>-9.164999999999999</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.65</v>
       </c>
       <c r="I337" t="n">
-        <v>1.2907</v>
+        <v>1.3096</v>
       </c>
       <c r="J337" t="n">
-        <v>33.5582</v>
+        <v>34.0496</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.54</v>
       </c>
       <c r="I338" t="n">
-        <v>1.1458</v>
+        <v>1.1588</v>
       </c>
       <c r="J338" t="n">
-        <v>29.7908</v>
+        <v>30.1288</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.15</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4243</v>
+        <v>0.3916</v>
       </c>
       <c r="J339" t="n">
-        <v>11.0318</v>
+        <v>10.1816</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.12</v>
       </c>
       <c r="I340" t="n">
-        <v>0.3513</v>
+        <v>0.3188</v>
       </c>
       <c r="J340" t="n">
-        <v>9.133800000000001</v>
+        <v>8.2888</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.85</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5175</v>
+        <v>-0.4803</v>
       </c>
       <c r="J341" t="n">
-        <v>-13.455</v>
+        <v>-12.4878</v>
       </c>
     </row>
   </sheetData>
